--- a/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
+++ b/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,10 +448,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Transfer time [days]</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Trajectory</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Launch day</t>
         </is>
@@ -464,12 +469,15 @@
       <c r="B2" t="n">
         <v>4014.055087892199</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>2549.197173461811</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>49660</v>
       </c>
     </row>
@@ -480,12 +488,15 @@
       <c r="B3" t="n">
         <v>4523.892183728227</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" t="n">
+        <v>2147.545541491706</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>49689</v>
       </c>
     </row>
@@ -496,12 +507,15 @@
       <c r="B4" t="n">
         <v>8320.05782540196</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" t="n">
+        <v>1809.792870170805</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>49690</v>
       </c>
     </row>
@@ -512,12 +526,15 @@
       <c r="B5" t="n">
         <v>15733.06231858284</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" t="n">
+        <v>2547.676656267437</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>49691</v>
       </c>
     </row>
@@ -528,12 +545,15 @@
       <c r="B6" t="n">
         <v>2792.099258051032</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>2418.694728996602</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>49720</v>
       </c>
     </row>
@@ -544,12 +564,15 @@
       <c r="B7" t="n">
         <v>3892.33910341701</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="C7" t="n">
+        <v>1844.148747400495</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>49721</v>
       </c>
     </row>
@@ -560,12 +583,15 @@
       <c r="B8" t="n">
         <v>3548.383114334327</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
+      <c r="C8" t="n">
+        <v>2165.408933062228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>49731</v>
       </c>
     </row>
@@ -576,12 +602,15 @@
       <c r="B9" t="n">
         <v>2194.094353055985</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>2421.177020672218</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>49749</v>
       </c>
     </row>
@@ -592,12 +621,15 @@
       <c r="B10" t="n">
         <v>4188.738280471291</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" t="n">
+        <v>2147.355498823109</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>49751</v>
       </c>
     </row>
@@ -608,12 +640,15 @@
       <c r="B11" t="n">
         <v>2870.027924414046</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
+      <c r="C11" t="n">
+        <v>2014.283765730962</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>49757</v>
       </c>
     </row>
@@ -624,12 +659,15 @@
       <c r="B12" t="n">
         <v>2158.958570207707</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>2408.818487025273</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>49761</v>
       </c>
     </row>
@@ -640,12 +678,15 @@
       <c r="B13" t="n">
         <v>6804.731680469064</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
+      <c r="C13" t="n">
+        <v>2192.457482160421</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>49780</v>
       </c>
     </row>
@@ -656,12 +697,15 @@
       <c r="B14" t="n">
         <v>2384.103297490123</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>2381.87425132062</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>49781</v>
       </c>
     </row>
@@ -672,12 +716,15 @@
       <c r="B15" t="n">
         <v>3439.530765537691</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
+      <c r="C15" t="n">
+        <v>2150.8566228381</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>49810</v>
       </c>
     </row>
@@ -688,12 +735,15 @@
       <c r="B16" t="n">
         <v>1923.275363787801</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
+      <c r="C16" t="n">
+        <v>2192.151036208945</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>49811</v>
       </c>
     </row>
@@ -704,12 +754,15 @@
       <c r="B17" t="n">
         <v>3425.211385385666</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
+      <c r="C17" t="n">
+        <v>1882.657672009366</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>49812</v>
       </c>
     </row>
@@ -720,12 +773,15 @@
       <c r="B18" t="n">
         <v>1685.813591970005</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
+      <c r="C18" t="n">
+        <v>2247.865780317195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>49825</v>
       </c>
     </row>
@@ -736,12 +792,15 @@
       <c r="B19" t="n">
         <v>1749.397915201365</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
+      <c r="C19" t="n">
+        <v>2259.602661185481</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>49839</v>
       </c>
     </row>
@@ -752,12 +811,15 @@
       <c r="B20" t="n">
         <v>1754.051220948018</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
+      <c r="C20" t="n">
+        <v>2268.734154436177</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>49842</v>
       </c>
     </row>
@@ -768,12 +830,15 @@
       <c r="B21" t="n">
         <v>3073.580033918888</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
+      <c r="C21" t="n">
+        <v>2696.115575550588</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>49873</v>
       </c>
     </row>
@@ -784,12 +849,15 @@
       <c r="B22" t="n">
         <v>6218.415188723526</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="n">
+        <v>2278.24115398949</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>49902</v>
       </c>
     </row>
@@ -800,12 +868,15 @@
       <c r="B23" t="n">
         <v>5311.268775563029</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
+      <c r="C23" t="n">
+        <v>2659.159209492987</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>49904</v>
       </c>
     </row>
@@ -816,12 +887,15 @@
       <c r="B24" t="n">
         <v>10352.60012788985</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
+      <c r="C24" t="n">
+        <v>2221.323010622914</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>49934</v>
       </c>
     </row>
@@ -832,12 +906,15 @@
       <c r="B25" t="n">
         <v>11517.21402762166</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
+      <c r="C25" t="n">
+        <v>2106.161208597895</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>49964</v>
       </c>
     </row>
@@ -848,12 +925,15 @@
       <c r="B26" t="n">
         <v>11831.27101635916</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
+      <c r="C26" t="n">
+        <v>1932.617816417112</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>49965</v>
       </c>
     </row>
@@ -864,12 +944,15 @@
       <c r="B27" t="n">
         <v>7485.582718456546</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
+      <c r="C27" t="n">
+        <v>2172.44536459794</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>49994</v>
       </c>
     </row>
@@ -880,12 +963,15 @@
       <c r="B28" t="n">
         <v>11013.20471000736</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
+      <c r="C28" t="n">
+        <v>1887.323313268829</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>49995</v>
       </c>
     </row>
@@ -896,12 +982,15 @@
       <c r="B29" t="n">
         <v>7441.556565931416</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
+      <c r="C29" t="n">
+        <v>2174.470689458123</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>50002</v>
       </c>
     </row>
@@ -912,12 +1001,15 @@
       <c r="B30" t="n">
         <v>10531.56442559575</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
+      <c r="C30" t="n">
+        <v>1875.708955842925</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>50005</v>
       </c>
     </row>
@@ -928,12 +1020,15 @@
       <c r="B31" t="n">
         <v>14690.15501630144</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="n">
+        <v>2203.12341552909</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>50023</v>
       </c>
     </row>
@@ -944,12 +1039,15 @@
       <c r="B32" t="n">
         <v>12593.87390044965</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
+      <c r="C32" t="n">
+        <v>1871.796680734057</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>50026</v>
       </c>
     </row>
@@ -960,12 +1058,15 @@
       <c r="B33" t="n">
         <v>5258.898560609356</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
+      <c r="C33" t="n">
+        <v>2189.646206298512</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>50044</v>
       </c>
     </row>
@@ -976,12 +1077,15 @@
       <c r="B34" t="n">
         <v>12566.94131364906</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="n">
+        <v>2566.345794266159</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>50055</v>
       </c>
     </row>
@@ -992,12 +1096,15 @@
       <c r="B35" t="n">
         <v>5606.03318477464</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
+      <c r="C35" t="n">
+        <v>2209.142463769347</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>50057</v>
       </c>
     </row>
@@ -1008,12 +1115,15 @@
       <c r="B36" t="n">
         <v>10502.98879667432</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="n">
+        <v>2912.530806627877</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>50086</v>
       </c>
     </row>
@@ -1024,12 +1134,15 @@
       <c r="B37" t="n">
         <v>7310.898772067319</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
+      <c r="C37" t="n">
+        <v>1828.005909077775</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
         <v>50087</v>
       </c>
     </row>
@@ -1040,12 +1153,15 @@
       <c r="B38" t="n">
         <v>5903.189955385513</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
+      <c r="C38" t="n">
+        <v>2327.717433949053</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>50103</v>
       </c>
     </row>
@@ -1056,12 +1172,15 @@
       <c r="B39" t="n">
         <v>4157.216501496716</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
+      <c r="C39" t="n">
+        <v>2102.094217118578</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>50110</v>
       </c>
     </row>
@@ -1072,12 +1191,15 @@
       <c r="B40" t="n">
         <v>9367.025662902255</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
+      <c r="C40" t="n">
+        <v>1897.593923002144</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>50114</v>
       </c>
     </row>
@@ -1088,12 +1210,15 @@
       <c r="B41" t="n">
         <v>4212.766195050981</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
+      <c r="C41" t="n">
+        <v>2198.372332482092</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>50116</v>
       </c>
     </row>
@@ -1104,12 +1229,15 @@
       <c r="B42" t="n">
         <v>7282.00165318889</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
+      <c r="C42" t="n">
+        <v>1933.902771551656</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>50145</v>
       </c>
     </row>
@@ -1120,12 +1248,15 @@
       <c r="B43" t="n">
         <v>9333.512282055686</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
+      <c r="C43" t="n">
+        <v>2340.215568356512</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>50146</v>
       </c>
     </row>
@@ -1136,12 +1267,15 @@
       <c r="B44" t="n">
         <v>8432.632128542213</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="n">
+        <v>2829.503091028412</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>50147</v>
       </c>
     </row>
@@ -1152,12 +1286,15 @@
       <c r="B45" t="n">
         <v>6423.185268220112</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
+      <c r="C45" t="n">
+        <v>1941.768095325454</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>50175</v>
       </c>
     </row>
@@ -1168,12 +1305,15 @@
       <c r="B46" t="n">
         <v>4097.357354962637</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
+      <c r="C46" t="n">
+        <v>1790.01084031046</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>50176</v>
       </c>
     </row>
@@ -1184,12 +1324,15 @@
       <c r="B47" t="n">
         <v>8669.81700802522</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" t="n">
+        <v>2790.23979448662</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>50177</v>
       </c>
     </row>
@@ -1200,12 +1343,15 @@
       <c r="B48" t="n">
         <v>2623.484723817457</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
+      <c r="C48" t="n">
+        <v>2242.7733766652</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
         <v>50206</v>
       </c>
     </row>
@@ -1216,12 +1362,15 @@
       <c r="B49" t="n">
         <v>2993.960184637568</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
+      <c r="C49" t="n">
+        <v>1924.94898001043</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
         <v>50209</v>
       </c>
     </row>
@@ -1232,12 +1381,15 @@
       <c r="B50" t="n">
         <v>1904.095767382581</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
+      <c r="C50" t="n">
+        <v>2308.295145207988</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
         <v>50236</v>
       </c>
     </row>
@@ -1248,12 +1400,15 @@
       <c r="B51" t="n">
         <v>3176.9239440372</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
+      <c r="C51" t="n">
+        <v>2144.099730097068</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
         <v>50238</v>
       </c>
     </row>
@@ -1264,12 +1419,15 @@
       <c r="B52" t="n">
         <v>5896.513043619248</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
+      <c r="C52" t="n">
+        <v>1962.10821264015</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
         <v>50247</v>
       </c>
     </row>
@@ -1280,12 +1438,15 @@
       <c r="B53" t="n">
         <v>1612.872369061143</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
+      <c r="C53" t="n">
+        <v>2324.356202279828</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>50266</v>
       </c>
     </row>
@@ -1296,12 +1457,15 @@
       <c r="B54" t="n">
         <v>3929.322283618183</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
+      <c r="C54" t="n">
+        <v>2305.072877103079</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
         <v>50269</v>
       </c>
     </row>
@@ -1312,12 +1476,15 @@
       <c r="B55" t="n">
         <v>8639.123786193522</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="n">
+        <v>2575.685791325593</v>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>50285</v>
       </c>
     </row>
@@ -1328,12 +1495,15 @@
       <c r="B56" t="n">
         <v>1281.140028060378</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
+      <c r="C56" t="n">
+        <v>2263.218591481248</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
         <v>50298</v>
       </c>
     </row>
@@ -1344,12 +1514,15 @@
       <c r="B57" t="n">
         <v>1226.643527751176</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
+      <c r="C57" t="n">
+        <v>2246.59451785385</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
         <v>50312</v>
       </c>
     </row>
@@ -1360,12 +1533,15 @@
       <c r="B58" t="n">
         <v>4025.626151603145</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="n">
+        <v>2461.587991409666</v>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>50328</v>
       </c>
     </row>
@@ -1376,12 +1552,15 @@
       <c r="B59" t="n">
         <v>1304.435073724873</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
+      <c r="C59" t="n">
+        <v>2269.400354333155</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
         <v>50330</v>
       </c>
     </row>
@@ -1392,12 +1571,15 @@
       <c r="B60" t="n">
         <v>5489.657222481161</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
+      <c r="C60" t="n">
+        <v>1733.562603245736</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>50331</v>
       </c>
     </row>
@@ -1408,12 +1590,15 @@
       <c r="B61" t="n">
         <v>7433.167367619011</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" t="n">
+        <v>2526.645998924158</v>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>50346</v>
       </c>
     </row>
@@ -1424,12 +1609,15 @@
       <c r="B62" t="n">
         <v>5730.655802558076</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
+      <c r="C62" t="n">
+        <v>1887.823034859797</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>50359</v>
       </c>
     </row>
@@ -1440,12 +1628,15 @@
       <c r="B63" t="n">
         <v>2061.400631155953</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
+      <c r="C63" t="n">
+        <v>2076.551135953471</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>50360</v>
       </c>
     </row>
@@ -1456,12 +1647,15 @@
       <c r="B64" t="n">
         <v>3483.180135969717</v>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
+      <c r="C64" t="n">
+        <v>2297.972682958062</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>50391</v>
       </c>
     </row>
@@ -1472,12 +1666,15 @@
       <c r="B65" t="n">
         <v>10050.49417410825</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
+      <c r="C65" t="n">
+        <v>1866.170420320066</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>50422</v>
       </c>
     </row>
@@ -1488,12 +1685,15 @@
       <c r="B66" t="n">
         <v>13143.42643058428</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
+      <c r="C66" t="n">
+        <v>2136.34057749607</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>50450</v>
       </c>
     </row>
@@ -1504,12 +1704,15 @@
       <c r="B67" t="n">
         <v>17605.21103145456</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
+      <c r="C67" t="n">
+        <v>1472.972774393054</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
         <v>50452</v>
       </c>
     </row>
@@ -1520,12 +1723,15 @@
       <c r="B68" t="n">
         <v>7953.704450992684</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" t="n">
+        <v>2313.811109122985</v>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>50479</v>
       </c>
     </row>
@@ -1536,12 +1742,15 @@
       <c r="B69" t="n">
         <v>10374.61620937778</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n">
+      <c r="C69" t="n">
+        <v>2086.714298284358</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>50480</v>
       </c>
     </row>
@@ -1552,12 +1761,15 @@
       <c r="B70" t="n">
         <v>10691.16272220942</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" t="n">
+        <v>2381.751828698761</v>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="E70" s="3" t="n">
         <v>50502</v>
       </c>
     </row>
@@ -1568,12 +1780,15 @@
       <c r="B71" t="n">
         <v>9533.710982477673</v>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
+      <c r="C71" t="n">
+        <v>2432.63302981191</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
         <v>50510</v>
       </c>
     </row>
@@ -1584,12 +1799,15 @@
       <c r="B72" t="n">
         <v>10125.14591720093</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
+      <c r="C72" t="n">
+        <v>1756.452140534336</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
         <v>50511</v>
       </c>
     </row>
@@ -1600,12 +1818,15 @@
       <c r="B73" t="n">
         <v>9314.139912326753</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
+      <c r="C73" t="n">
+        <v>2451.70808029176</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
         <v>50523</v>
       </c>
     </row>
@@ -1616,12 +1837,15 @@
       <c r="B74" t="n">
         <v>9501.685650544772</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
+      <c r="C74" t="n">
+        <v>2226.430164437737</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
         <v>50540</v>
       </c>
     </row>
@@ -1632,12 +1856,15 @@
       <c r="B75" t="n">
         <v>11190.77427650684</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
+      <c r="C75" t="n">
+        <v>2434.966342797619</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
         <v>50542</v>
       </c>
     </row>
@@ -1648,12 +1875,15 @@
       <c r="B76" t="n">
         <v>8914.921738761195</v>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="n">
+      <c r="C76" t="n">
+        <v>1982.754346460781</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
         <v>50571</v>
       </c>
     </row>
@@ -1664,12 +1894,15 @@
       <c r="B77" t="n">
         <v>4970.409846064256</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
+      <c r="C77" t="n">
+        <v>1868.19844205007</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
         <v>50572</v>
       </c>
     </row>
@@ -1680,12 +1913,15 @@
       <c r="B78" t="n">
         <v>4926.09731237362</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="n">
+      <c r="C78" t="n">
+        <v>1911.973287358774</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
         <v>50577</v>
       </c>
     </row>
@@ -1696,12 +1932,15 @@
       <c r="B79" t="n">
         <v>5504.271794751188</v>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="n">
+      <c r="C79" t="n">
+        <v>2285.51146039578</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
         <v>50584</v>
       </c>
     </row>
@@ -1712,12 +1951,15 @@
       <c r="B80" t="n">
         <v>7411.010111142448</v>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="n">
+      <c r="C80" t="n">
+        <v>2192.791410556332</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
         <v>50601</v>
       </c>
     </row>
@@ -1728,12 +1970,15 @@
       <c r="B81" t="n">
         <v>5419.024794353403</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
+      <c r="C81" t="n">
+        <v>2334.570352736235</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
         <v>50603</v>
       </c>
     </row>
@@ -1744,12 +1989,15 @@
       <c r="B82" t="n">
         <v>15592.91114340716</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" t="n">
+        <v>2182.623987649073</v>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="E82" s="3" t="n">
         <v>50609</v>
       </c>
     </row>
@@ -1760,12 +2008,15 @@
       <c r="B83" t="n">
         <v>8623.181127884431</v>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
+      <c r="C83" t="n">
+        <v>1979.60111981427</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
         <v>50625</v>
       </c>
     </row>
@@ -1776,12 +2027,15 @@
       <c r="B84" t="n">
         <v>6087.053671843214</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
+      <c r="C84" t="n">
+        <v>2154.938259939948</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
         <v>50632</v>
       </c>
     </row>
@@ -1792,12 +2046,15 @@
       <c r="B85" t="n">
         <v>8636.15812024055</v>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
+      <c r="C85" t="n">
+        <v>2006.613786012682</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
         <v>50634</v>
       </c>
     </row>
@@ -1808,12 +2065,15 @@
       <c r="B86" t="n">
         <v>10082.12352184699</v>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
+      <c r="C86" t="n">
+        <v>2210.291767919855</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
         <v>50662</v>
       </c>
     </row>
@@ -1824,12 +2084,15 @@
       <c r="B87" t="n">
         <v>16317.29067598553</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" t="n">
+        <v>2576.497418381885</v>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>50663</v>
       </c>
     </row>
@@ -1840,12 +2103,15 @@
       <c r="B88" t="n">
         <v>6971.32766144599</v>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
+      <c r="C88" t="n">
+        <v>2656.521348767914</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
         <v>50664</v>
       </c>
     </row>
@@ -1856,12 +2122,15 @@
       <c r="B89" t="n">
         <v>5724.401290286592</v>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
+      <c r="C89" t="n">
+        <v>1855.304974749868</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
         <v>50693</v>
       </c>
     </row>
@@ -1872,12 +2141,15 @@
       <c r="B90" t="n">
         <v>14053.35985024147</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" t="n">
+        <v>2510.539464482986</v>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="E90" s="3" t="n">
         <v>50694</v>
       </c>
     </row>
@@ -1888,12 +2160,15 @@
       <c r="B91" t="n">
         <v>8400.739992649806</v>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="n">
+      <c r="C91" t="n">
+        <v>1440.375654276172</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
         <v>50701</v>
       </c>
     </row>
@@ -1904,12 +2179,15 @@
       <c r="B92" t="n">
         <v>8991.286452426157</v>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
+      <c r="C92" t="n">
+        <v>2197.513254430934</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>50722</v>
       </c>
     </row>
@@ -1920,12 +2198,15 @@
       <c r="B93" t="n">
         <v>8528.383512543847</v>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
+      <c r="C93" t="n">
+        <v>1809.368534275456</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
         <v>50724</v>
       </c>
     </row>
@@ -1936,12 +2217,15 @@
       <c r="B94" t="n">
         <v>8994.47945288652</v>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
+      <c r="C94" t="n">
+        <v>2184.748565254792</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
         <v>50725</v>
       </c>
     </row>
@@ -1952,12 +2236,15 @@
       <c r="B95" t="n">
         <v>8420.998416839837</v>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C95" t="n">
+        <v>1859.526083568553</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
         <v>50740</v>
       </c>
     </row>
@@ -1968,12 +2255,15 @@
       <c r="B96" t="n">
         <v>7120.708598626936</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" t="n">
+        <v>2358.281446849489</v>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="E96" s="3" t="n">
         <v>50754</v>
       </c>
     </row>
@@ -1984,12 +2274,15 @@
       <c r="B97" t="n">
         <v>8450.061692567881</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
+      <c r="C97" t="n">
+        <v>1878.852391323249</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
         <v>50756</v>
       </c>
     </row>
@@ -2000,12 +2293,15 @@
       <c r="B98" t="n">
         <v>6423.328891556714</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" t="n">
+        <v>2339.467481898279</v>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="E98" s="3" t="n">
         <v>50785</v>
       </c>
     </row>
@@ -2016,12 +2312,15 @@
       <c r="B99" t="n">
         <v>8629.505628092676</v>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
+      <c r="C99" t="n">
+        <v>1916.702946955712</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
         <v>50787</v>
       </c>
     </row>
@@ -2032,12 +2331,15 @@
       <c r="B100" t="n">
         <v>8910.971937618671</v>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
+      <c r="C100" t="n">
+        <v>1998.110807810896</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
         <v>50815</v>
       </c>
     </row>
@@ -2048,12 +2350,15 @@
       <c r="B101" t="n">
         <v>4325.631370845627</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" t="n">
+        <v>2308.635154570006</v>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="E101" s="3" t="n">
         <v>50817</v>
       </c>
     </row>
@@ -2064,12 +2369,15 @@
       <c r="B102" t="n">
         <v>4167.977572363327</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" t="n">
+        <v>2294.505975461052</v>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="E102" s="3" t="n">
         <v>50835</v>
       </c>
     </row>
@@ -2080,12 +2388,15 @@
       <c r="B103" t="n">
         <v>13786.93976366671</v>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
+      <c r="C103" t="n">
+        <v>1737.000470174526</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
         <v>50845</v>
       </c>
     </row>
@@ -2096,12 +2407,15 @@
       <c r="B104" t="n">
         <v>13625.64212755976</v>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
+      <c r="C104" t="n">
+        <v>2607.479208896762</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
         <v>50853</v>
       </c>
     </row>
@@ -2112,12 +2426,15 @@
       <c r="B105" t="n">
         <v>3678.106718036061</v>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
+      <c r="C105" t="n">
+        <v>2058.479935469316</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
         <v>50875</v>
       </c>
     </row>
@@ -2128,12 +2445,15 @@
       <c r="B106" t="n">
         <v>8492.148314168053</v>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
+      <c r="C106" t="n">
+        <v>1761.84468458551</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
         <v>50876</v>
       </c>
     </row>
@@ -2144,12 +2464,15 @@
       <c r="B107" t="n">
         <v>3055.610235271717</v>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
+      <c r="C107" t="n">
+        <v>2127.739365076152</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
         <v>50905</v>
       </c>
     </row>
@@ -2160,12 +2483,15 @@
       <c r="B108" t="n">
         <v>4358.456162985729</v>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
+      <c r="C108" t="n">
+        <v>1797.95349274327</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
         <v>50906</v>
       </c>
     </row>
@@ -2176,12 +2502,15 @@
       <c r="B109" t="n">
         <v>14756.49360791315</v>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
+      <c r="C109" t="n">
+        <v>2513.306697699584</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
         <v>50907</v>
       </c>
     </row>
@@ -2192,12 +2521,15 @@
       <c r="B110" t="n">
         <v>2958.267430990622</v>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
+      <c r="C110" t="n">
+        <v>2107.226474707514</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
         <v>50914</v>
       </c>
     </row>
@@ -2208,12 +2540,15 @@
       <c r="B111" t="n">
         <v>3086.75257694494</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" t="n">
+        <v>2194.507348288722</v>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="E111" s="3" t="n">
         <v>50925</v>
       </c>
     </row>
@@ -2224,12 +2559,15 @@
       <c r="B112" t="n">
         <v>3067.572901237036</v>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
+      <c r="C112" t="n">
+        <v>1849.279973934608</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
         <v>50937</v>
       </c>
     </row>
@@ -2240,12 +2578,15 @@
       <c r="B113" t="n">
         <v>3043.963355083282</v>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
+      <c r="C113" t="n">
+        <v>1865.492957054876</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
         <v>50943</v>
       </c>
     </row>
@@ -2256,12 +2597,15 @@
       <c r="B114" t="n">
         <v>3294.552202643603</v>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
+      <c r="C114" t="n">
+        <v>1908.095096532966</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
         <v>50968</v>
       </c>
     </row>
@@ -2272,12 +2616,15 @@
       <c r="B115" t="n">
         <v>2217.618581364153</v>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
+      <c r="C115" t="n">
+        <v>2096.524316736547</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
         <v>50997</v>
       </c>
     </row>
@@ -2288,12 +2635,15 @@
       <c r="B116" t="n">
         <v>4384.749504158795</v>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
+      <c r="C116" t="n">
+        <v>1651.155113152701</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
         <v>50999</v>
       </c>
     </row>
@@ -2304,12 +2654,15 @@
       <c r="B117" t="n">
         <v>1970.306025961567</v>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
+      <c r="C117" t="n">
+        <v>2147.985921787038</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
         <v>51011</v>
       </c>
     </row>
@@ -2320,12 +2673,15 @@
       <c r="B118" t="n">
         <v>11366.03409128407</v>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
+      <c r="C118" t="n">
+        <v>1805.289709263106</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
         <v>51028</v>
       </c>
     </row>
@@ -2336,12 +2692,15 @@
       <c r="B119" t="n">
         <v>2257.433812141382</v>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="n">
+      <c r="C119" t="n">
+        <v>2237.352871344337</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
         <v>51029</v>
       </c>
     </row>
@@ -2352,12 +2711,15 @@
       <c r="B120" t="n">
         <v>7663.33484616197</v>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" t="n">
+        <v>2052.915523865457</v>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="E120" s="3" t="n">
         <v>51058</v>
       </c>
     </row>
@@ -2368,12 +2730,15 @@
       <c r="B121" t="n">
         <v>3544.412487819436</v>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
+      <c r="C121" t="n">
+        <v>2645.08074555508</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
         <v>51060</v>
       </c>
     </row>
@@ -2384,12 +2749,15 @@
       <c r="B122" t="n">
         <v>7342.952185329328</v>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" t="n">
+        <v>2051.336211315354</v>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>51069</v>
       </c>
     </row>
@@ -2400,12 +2768,15 @@
       <c r="B123" t="n">
         <v>5657.110791458814</v>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
+      <c r="C123" t="n">
+        <v>2671.03893029319</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
         <v>51090</v>
       </c>
     </row>
@@ -2416,12 +2787,15 @@
       <c r="B124" t="n">
         <v>12147.09815144838</v>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
+      <c r="C124" t="n">
+        <v>1484.060331592765</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
         <v>51119</v>
       </c>
     </row>
@@ -2432,12 +2806,15 @@
       <c r="B125" t="n">
         <v>10601.52856780689</v>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
+      <c r="C125" t="n">
+        <v>2255.959917207415</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
         <v>51121</v>
       </c>
     </row>
@@ -2448,12 +2825,15 @@
       <c r="B126" t="n">
         <v>12071.0963142543</v>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
+      <c r="C126" t="n">
+        <v>1515.439451014626</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
         <v>51127</v>
       </c>
     </row>
@@ -2464,12 +2844,15 @@
       <c r="B127" t="n">
         <v>10071.22019405535</v>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
+      <c r="C127" t="n">
+        <v>2023.289853973595</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
         <v>51151</v>
       </c>
     </row>
@@ -2480,12 +2863,15 @@
       <c r="B128" t="n">
         <v>11154.48227417286</v>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
+      <c r="C128" t="n">
+        <v>1876.041014803024</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
         <v>51152</v>
       </c>
     </row>
@@ -2496,12 +2882,15 @@
       <c r="B129" t="n">
         <v>14368.57004452504</v>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
+      <c r="C129" t="n">
+        <v>1263.445915302427</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
         <v>51176</v>
       </c>
     </row>
@@ -2512,12 +2901,15 @@
       <c r="B130" t="n">
         <v>7983.122407120793</v>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
+      <c r="C130" t="n">
+        <v>1941.527793650004</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
         <v>51181</v>
       </c>
     </row>
@@ -2528,12 +2920,15 @@
       <c r="B131" t="n">
         <v>5764.511135484176</v>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
+      <c r="C131" t="n">
+        <v>1913.464708496148</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
         <v>51206</v>
       </c>
     </row>
@@ -2544,12 +2939,15 @@
       <c r="B132" t="n">
         <v>6838.981769905186</v>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
+      <c r="C132" t="n">
+        <v>1715.41481908141</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
         <v>51210</v>
       </c>
     </row>
@@ -2560,12 +2958,15 @@
       <c r="B133" t="n">
         <v>11838.75159857189</v>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
+      <c r="C133" t="n">
+        <v>1872.287025476858</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
         <v>51211</v>
       </c>
     </row>
@@ -2576,12 +2977,15 @@
       <c r="B134" t="n">
         <v>5841.571117616584</v>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
+      <c r="C134" t="n">
+        <v>1914.51759334634</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
         <v>51212</v>
       </c>
     </row>
@@ -2592,12 +2996,15 @@
       <c r="B135" t="n">
         <v>11688.32501834102</v>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
+      <c r="C135" t="n">
+        <v>1873.63602175968</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
         <v>51213</v>
       </c>
     </row>
@@ -2608,12 +3015,15 @@
       <c r="B136" t="n">
         <v>6834.030789400924</v>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
+      <c r="C136" t="n">
+        <v>1730.046319127933</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
         <v>51215</v>
       </c>
     </row>
@@ -2624,12 +3034,15 @@
       <c r="B137" t="n">
         <v>7048.574004383088</v>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
+      <c r="C137" t="n">
+        <v>1875.004604960936</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
         <v>51242</v>
       </c>
     </row>
@@ -2640,12 +3053,15 @@
       <c r="B138" t="n">
         <v>8999.343024112595</v>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" t="n">
+        <v>2767.170753541317</v>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="E138" s="3" t="n">
         <v>51271</v>
       </c>
     </row>
@@ -2656,12 +3072,15 @@
       <c r="B139" t="n">
         <v>6160.902376060669</v>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
+      <c r="C139" t="n">
+        <v>2077.232967848855</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
         <v>51272</v>
       </c>
     </row>
@@ -2672,12 +3091,15 @@
       <c r="B140" t="n">
         <v>13802.05950121409</v>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
+      <c r="C140" t="n">
+        <v>1753.441528391346</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
         <v>51273</v>
       </c>
     </row>
@@ -2688,12 +3110,15 @@
       <c r="B141" t="n">
         <v>6085.499301724671</v>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
+      <c r="C141" t="n">
+        <v>2056.691656881615</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
         <v>51291</v>
       </c>
     </row>
@@ -2704,12 +3129,15 @@
       <c r="B142" t="n">
         <v>4437.260464211735</v>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
+      <c r="C142" t="n">
+        <v>1903.770259245576</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
         <v>51297</v>
       </c>
     </row>
@@ -2720,12 +3148,15 @@
       <c r="B143" t="n">
         <v>7745.327282133348</v>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" t="n">
+        <v>2906.838043117208</v>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="E143" s="3" t="n">
         <v>51302</v>
       </c>
     </row>
@@ -2736,12 +3167,15 @@
       <c r="B144" t="n">
         <v>4482.402297961162</v>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="n">
+      <c r="C144" t="n">
+        <v>1993.749598666359</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
         <v>51303</v>
       </c>
     </row>
@@ -2752,12 +3186,15 @@
       <c r="B145" t="n">
         <v>7094.944445968797</v>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" t="n">
+        <v>2863.615621671772</v>
+      </c>
+      <c r="D145" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D145" s="3" t="n">
+      <c r="E145" s="3" t="n">
         <v>51332</v>
       </c>
     </row>
@@ -2768,12 +3205,15 @@
       <c r="B146" t="n">
         <v>7094.636431274392</v>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" t="n">
+        <v>2862.254079842318</v>
+      </c>
+      <c r="D146" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="E146" s="3" t="n">
         <v>51334</v>
       </c>
     </row>
@@ -2784,12 +3224,15 @@
       <c r="B147" t="n">
         <v>5911.622384470073</v>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="n">
+      <c r="C147" t="n">
+        <v>1819.916866058876</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
         <v>51363</v>
       </c>
     </row>
@@ -2800,12 +3243,15 @@
       <c r="B148" t="n">
         <v>4465.214398931872</v>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
+      <c r="C148" t="n">
+        <v>1733.667913607321</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
         <v>51364</v>
       </c>
     </row>
@@ -2816,12 +3262,15 @@
       <c r="B149" t="n">
         <v>3893.471959826318</v>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="n">
+      <c r="C149" t="n">
+        <v>1900.715527992519</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
         <v>51382</v>
       </c>
     </row>
@@ -2832,12 +3281,15 @@
       <c r="B150" t="n">
         <v>5430.201724213552</v>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="n">
+      <c r="C150" t="n">
+        <v>1824.395794517174</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
         <v>51394</v>
       </c>
     </row>
@@ -2848,12 +3300,15 @@
       <c r="B151" t="n">
         <v>8673.523402327844</v>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="n">
+      <c r="C151" t="n">
+        <v>1912.886113091268</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
         <v>51406</v>
       </c>
     </row>
@@ -2864,12 +3319,15 @@
       <c r="B152" t="n">
         <v>4925.629969372643</v>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
+      <c r="C152" t="n">
+        <v>1794.353813492281</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
         <v>51424</v>
       </c>
     </row>
@@ -2880,12 +3338,15 @@
       <c r="B153" t="n">
         <v>4838.401851720791</v>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
+      <c r="C153" t="n">
+        <v>1497.051854036048</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
         <v>51425</v>
       </c>
     </row>
@@ -2896,12 +3357,15 @@
       <c r="B154" t="n">
         <v>4747.815848525037</v>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="n">
+      <c r="C154" t="n">
+        <v>1492.148476618927</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
         <v>51448</v>
       </c>
     </row>
@@ -2912,12 +3376,15 @@
       <c r="B155" t="n">
         <v>6673.66417421671</v>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" t="n">
+        <v>3111.483151901069</v>
+      </c>
+      <c r="D155" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="E155" s="3" t="n">
         <v>51451</v>
       </c>
     </row>
@@ -2928,12 +3395,15 @@
       <c r="B156" t="n">
         <v>4359.614289158751</v>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
+      <c r="C156" t="n">
+        <v>1763.357256622755</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
         <v>51455</v>
       </c>
     </row>
@@ -2944,12 +3414,15 @@
       <c r="B157" t="n">
         <v>6815.264730643279</v>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" t="n">
+        <v>3104.127903474942</v>
+      </c>
+      <c r="D157" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="E157" s="3" t="n">
         <v>51456</v>
       </c>
     </row>
@@ -2960,12 +3433,15 @@
       <c r="B158" t="n">
         <v>4206.084386503846</v>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n">
+      <c r="C158" t="n">
+        <v>1760.696471569028</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
         <v>51469</v>
       </c>
     </row>
@@ -2976,12 +3452,15 @@
       <c r="B159" t="n">
         <v>4158.79451060994</v>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="n">
+      <c r="C159" t="n">
+        <v>2291.944157574213</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
         <v>51481</v>
       </c>
     </row>
@@ -2992,12 +3471,15 @@
       <c r="B160" t="n">
         <v>7775.376842015268</v>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="n">
+      <c r="C160" t="n">
+        <v>1820.303756623213</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
         <v>51485</v>
       </c>
     </row>
@@ -3008,12 +3490,15 @@
       <c r="B161" t="n">
         <v>4402.253579838487</v>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="n">
+      <c r="C161" t="n">
+        <v>1794.078508457931</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
         <v>51487</v>
       </c>
     </row>
@@ -3024,12 +3509,15 @@
       <c r="B162" t="n">
         <v>4328.987903602823</v>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="n">
+      <c r="C162" t="n">
+        <v>1433.875216269168</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
         <v>51494</v>
       </c>
     </row>
@@ -3040,12 +3528,15 @@
       <c r="B163" t="n">
         <v>4576.852752518196</v>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="n">
+      <c r="C163" t="n">
+        <v>1447.981894652621</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
         <v>51518</v>
       </c>
     </row>
@@ -3056,12 +3547,15 @@
       <c r="B164" t="n">
         <v>9091.995045373107</v>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" t="n">
+        <v>2497.99240773169</v>
+      </c>
+      <c r="D164" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="E164" s="3" t="n">
         <v>51533</v>
       </c>
     </row>
@@ -3072,12 +3566,15 @@
       <c r="B165" t="n">
         <v>6118.997150021129</v>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="n">
+      <c r="C165" t="n">
+        <v>1673.359166696871</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
         <v>51546</v>
       </c>
     </row>
@@ -3088,12 +3585,15 @@
       <c r="B166" t="n">
         <v>7687.808394090487</v>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C166" t="n">
+        <v>2987.847521297687</v>
+      </c>
+      <c r="D166" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="E166" s="3" t="n">
         <v>51565</v>
       </c>
     </row>
@@ -3104,12 +3604,15 @@
       <c r="B167" t="n">
         <v>6333.644871412651</v>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
+      <c r="C167" t="n">
+        <v>2602.662485126461</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
         <v>51577</v>
       </c>
     </row>
@@ -3120,12 +3623,15 @@
       <c r="B168" t="n">
         <v>11174.07466119963</v>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="n">
+      <c r="C168" t="n">
+        <v>1727.75762192567</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
         <v>51607</v>
       </c>
     </row>
@@ -3136,12 +3642,15 @@
       <c r="B169" t="n">
         <v>13400.82492276121</v>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="n">
+      <c r="C169" t="n">
+        <v>1855.37059417736</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
         <v>51637</v>
       </c>
     </row>
@@ -3152,12 +3661,15 @@
       <c r="B170" t="n">
         <v>14818.16816193844</v>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" t="n">
+        <v>2386.592059523776</v>
+      </c>
+      <c r="D170" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D170" s="3" t="n">
+      <c r="E170" s="3" t="n">
         <v>51638</v>
       </c>
     </row>
@@ -3168,12 +3680,15 @@
       <c r="B171" t="n">
         <v>8595.854713828858</v>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="n">
+      <c r="C171" t="n">
+        <v>2269.847351243972</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
         <v>51668</v>
       </c>
     </row>
@@ -3184,12 +3699,15 @@
       <c r="B172" t="n">
         <v>8174.799290456387</v>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="n">
+      <c r="C172" t="n">
+        <v>2147.048345614171</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
         <v>51676</v>
       </c>
     </row>
@@ -3200,12 +3718,15 @@
       <c r="B173" t="n">
         <v>12589.47391303317</v>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="n">
+      <c r="C173" t="n">
+        <v>1766.874580164999</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
         <v>51697</v>
       </c>
     </row>
@@ -3216,12 +3737,15 @@
       <c r="B174" t="n">
         <v>13244.04560644157</v>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="n">
+      <c r="C174" t="n">
+        <v>1253.13956098957</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
         <v>51698</v>
       </c>
     </row>
@@ -3232,12 +3756,15 @@
       <c r="B175" t="n">
         <v>8417.86957078581</v>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="n">
+      <c r="C175" t="n">
+        <v>2119.936475248867</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
         <v>51699</v>
       </c>
     </row>
@@ -3248,12 +3775,15 @@
       <c r="B176" t="n">
         <v>10307.17498628802</v>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="n">
+      <c r="C176" t="n">
+        <v>1783.731604454192</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
         <v>51728</v>
       </c>
     </row>
@@ -3264,12 +3794,15 @@
       <c r="B177" t="n">
         <v>8386.667339931269</v>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="n">
+      <c r="C177" t="n">
+        <v>1694.371215488655</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
         <v>51729</v>
       </c>
     </row>
@@ -3280,12 +3813,15 @@
       <c r="B178" t="n">
         <v>9603.091550642604</v>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="n">
+      <c r="C178" t="n">
+        <v>2255.459081668909</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
         <v>51730</v>
       </c>
     </row>
@@ -3296,12 +3832,15 @@
       <c r="B179" t="n">
         <v>11962.03353547625</v>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C179" t="n">
+        <v>2576.640101658458</v>
+      </c>
+      <c r="D179" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="E179" s="3" t="n">
         <v>51747</v>
       </c>
     </row>
@@ -3312,12 +3851,15 @@
       <c r="B180" t="n">
         <v>9149.5894193731</v>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="n">
+      <c r="C180" t="n">
+        <v>1820.616279033955</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
         <v>51759</v>
       </c>
     </row>
@@ -3328,12 +3870,15 @@
       <c r="B181" t="n">
         <v>5217.781460159387</v>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="n">
+      <c r="C181" t="n">
+        <v>1740.323955440265</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
         <v>51760</v>
       </c>
     </row>
@@ -3344,12 +3889,15 @@
       <c r="B182" t="n">
         <v>11955.48384887483</v>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" t="n">
+        <v>2647.033489853027</v>
+      </c>
+      <c r="D182" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="E182" s="3" t="n">
         <v>51761</v>
       </c>
     </row>
@@ -3360,12 +3908,15 @@
       <c r="B183" t="n">
         <v>4959.499203369423</v>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="n">
+      <c r="C183" t="n">
+        <v>1841.758754749442</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
         <v>51774</v>
       </c>
     </row>
@@ -3376,12 +3927,15 @@
       <c r="B184" t="n">
         <v>8701.851897132716</v>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="n">
+      <c r="C184" t="n">
+        <v>1812.700041785187</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
         <v>51789</v>
       </c>
     </row>
@@ -3392,12 +3946,15 @@
       <c r="B185" t="n">
         <v>5109.841622116415</v>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="n">
+      <c r="C185" t="n">
+        <v>2060.588057001461</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
         <v>51791</v>
       </c>
     </row>
@@ -3408,12 +3965,15 @@
       <c r="B186" t="n">
         <v>8632.435231159749</v>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="n">
+      <c r="C186" t="n">
+        <v>1928.327733718712</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
         <v>51820</v>
       </c>
     </row>
@@ -3424,12 +3984,15 @@
       <c r="B187" t="n">
         <v>5555.719344187441</v>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="n">
+      <c r="C187" t="n">
+        <v>2359.423833415058</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
         <v>51821</v>
       </c>
     </row>
@@ -3440,12 +4003,15 @@
       <c r="B188" t="n">
         <v>8101.327848764682</v>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="n">
+      <c r="C188" t="n">
+        <v>1795.13517768021</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
         <v>51836</v>
       </c>
     </row>
@@ -3456,12 +4022,15 @@
       <c r="B189" t="n">
         <v>17947.89344728675</v>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C189" t="n">
+        <v>2180.610321908989</v>
+      </c>
+      <c r="D189" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D189" s="3" t="n">
+      <c r="E189" s="3" t="n">
         <v>51848</v>
       </c>
     </row>
@@ -3472,12 +4041,15 @@
       <c r="B190" t="n">
         <v>8302.85283539742</v>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="n">
+      <c r="C190" t="n">
+        <v>1884.475366379848</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
         <v>51850</v>
       </c>
     </row>
@@ -3488,12 +4060,15 @@
       <c r="B191" t="n">
         <v>8172.299834228948</v>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="n">
+      <c r="C191" t="n">
+        <v>1793.203126330457</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
         <v>51852</v>
       </c>
     </row>
@@ -3504,12 +4079,15 @@
       <c r="B192" t="n">
         <v>8184.561488697273</v>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="n">
+      <c r="C192" t="n">
+        <v>1954.711375936169</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
         <v>51881</v>
       </c>
     </row>
@@ -3520,12 +4098,15 @@
       <c r="B193" t="n">
         <v>6801.565396357986</v>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="n">
+      <c r="C193" t="n">
+        <v>2696.224711731692</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
         <v>51883</v>
       </c>
     </row>
@@ -3536,12 +4117,15 @@
       <c r="B194" t="n">
         <v>10690.08752622132</v>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="n">
+      <c r="C194" t="n">
+        <v>1346.469347817178</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
         <v>51911</v>
       </c>
     </row>
@@ -3552,12 +4136,15 @@
       <c r="B195" t="n">
         <v>8170.110263856261</v>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="n">
+      <c r="C195" t="n">
+        <v>2107.502407154942</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
         <v>51912</v>
       </c>
     </row>
@@ -3568,12 +4155,15 @@
       <c r="B196" t="n">
         <v>9002.132336029576</v>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" t="n">
+        <v>2404.091572796985</v>
+      </c>
+      <c r="D196" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="E196" s="3" t="n">
         <v>51913</v>
       </c>
     </row>
@@ -3584,12 +4174,15 @@
       <c r="B197" t="n">
         <v>7063.264596286135</v>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="n">
+      <c r="C197" t="n">
+        <v>1678.720672300867</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
         <v>51940</v>
       </c>
     </row>
@@ -3600,12 +4193,15 @@
       <c r="B198" t="n">
         <v>12732.04175631553</v>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="n">
+      <c r="C198" t="n">
+        <v>1873.953440938902</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
         <v>51942</v>
       </c>
     </row>
@@ -3616,12 +4212,15 @@
       <c r="B199" t="n">
         <v>8985.930435077384</v>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="n">
+      <c r="C199" t="n">
+        <v>2154.350767216609</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
         <v>51965</v>
       </c>
     </row>
@@ -3632,12 +4231,15 @@
       <c r="B200" t="n">
         <v>4245.040192377093</v>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="n">
+      <c r="C200" t="n">
+        <v>1562.305014415081</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
         <v>51971</v>
       </c>
     </row>
@@ -3648,12 +4250,15 @@
       <c r="B201" t="n">
         <v>8996.077598308617</v>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="n">
+      <c r="C201" t="n">
+        <v>2196.026308181693</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
         <v>51972</v>
       </c>
     </row>
@@ -3664,12 +4269,15 @@
       <c r="B202" t="n">
         <v>6602.746473415586</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" t="n">
+        <v>2367.993808065424</v>
+      </c>
+      <c r="D202" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="E202" s="3" t="n">
         <v>51989</v>
       </c>
     </row>
@@ -3680,12 +4288,15 @@
       <c r="B203" t="n">
         <v>3474.088463728765</v>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="n">
+      <c r="C203" t="n">
+        <v>1582.239134339926</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
         <v>52001</v>
       </c>
     </row>
@@ -3696,12 +4307,15 @@
       <c r="B204" t="n">
         <v>5318.997219292112</v>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="n">
+      <c r="C204" t="n">
+        <v>2613.025891260736</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
         <v>52026</v>
       </c>
     </row>
@@ -3712,12 +4326,15 @@
       <c r="B205" t="n">
         <v>3281.63139456409</v>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="n">
+      <c r="C205" t="n">
+        <v>1616.374875243894</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
         <v>52030</v>
       </c>
     </row>
@@ -3728,12 +4345,15 @@
       <c r="B206" t="n">
         <v>6248.994217109315</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" t="n">
+        <v>2335.021897195306</v>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="E206" s="3" t="n">
         <v>52032</v>
       </c>
     </row>
@@ -3744,12 +4364,15 @@
       <c r="B207" t="n">
         <v>5460.419012866729</v>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="n">
+      <c r="C207" t="n">
+        <v>2607.507344891367</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
         <v>52033</v>
       </c>
     </row>
@@ -3760,12 +4383,15 @@
       <c r="B208" t="n">
         <v>2662.762400757572</v>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="n">
+      <c r="C208" t="n">
+        <v>1453.27603483726</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
         <v>52062</v>
       </c>
     </row>
@@ -3776,12 +4402,15 @@
       <c r="B209" t="n">
         <v>12157.68494198515</v>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="n">
+      <c r="C209" t="n">
+        <v>1669.099467127853</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
         <v>52063</v>
       </c>
     </row>
@@ -3792,12 +4421,15 @@
       <c r="B210" t="n">
         <v>9589.910969484126</v>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="n">
+      <c r="C210" t="n">
+        <v>2594.16229788462</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
         <v>52064</v>
       </c>
     </row>
@@ -3808,12 +4440,15 @@
       <c r="B211" t="n">
         <v>2982.346290770933</v>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="n">
+      <c r="C211" t="n">
+        <v>1521.374395463072</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="n">
         <v>52079</v>
       </c>
     </row>
@@ -3824,12 +4459,15 @@
       <c r="B212" t="n">
         <v>5327.966029084346</v>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" t="n">
+        <v>2263.091849961549</v>
+      </c>
+      <c r="D212" t="inlineStr">
         <is>
           <t>VVEE</t>
         </is>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="E212" s="3" t="n">
         <v>52091</v>
       </c>
     </row>
@@ -3840,12 +4478,15 @@
       <c r="B213" t="n">
         <v>7060.364129485844</v>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="n">
+      <c r="C213" t="n">
+        <v>1690.777989434964</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="n">
         <v>52094</v>
       </c>
     </row>
@@ -3856,12 +4497,15 @@
       <c r="B214" t="n">
         <v>2754.266213292111</v>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="n">
+      <c r="C214" t="n">
+        <v>1394.445712241474</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="n">
         <v>52095</v>
       </c>
     </row>
@@ -3872,12 +4516,15 @@
       <c r="B215" t="n">
         <v>4251.892339816433</v>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="n">
+      <c r="C215" t="n">
+        <v>1722.473549711632</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="n">
         <v>52125</v>
       </c>
     </row>
@@ -3888,12 +4535,15 @@
       <c r="B216" t="n">
         <v>2876.125446409285</v>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n">
+      <c r="C216" t="n">
+        <v>1420.691732440396</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="n">
         <v>52147</v>
       </c>
     </row>
@@ -3904,12 +4554,15 @@
       <c r="B217" t="n">
         <v>3797.821856234557</v>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="n">
+      <c r="C217" t="n">
+        <v>1728.052982365612</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="n">
         <v>52148</v>
       </c>
     </row>
@@ -3920,12 +4573,15 @@
       <c r="B218" t="n">
         <v>2984.841193517434</v>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="n">
+      <c r="C218" t="n">
+        <v>1356.671507069931</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n">
         <v>52156</v>
       </c>
     </row>
@@ -3936,12 +4592,15 @@
       <c r="B219" t="n">
         <v>13974.2104387975</v>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="n">
+      <c r="C219" t="n">
+        <v>1708.923615653014</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n">
         <v>52185</v>
       </c>
     </row>
@@ -3952,12 +4611,15 @@
       <c r="B220" t="n">
         <v>4871.403299368685</v>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="n">
+      <c r="C220" t="n">
+        <v>1744.167896890056</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="n">
         <v>52186</v>
       </c>
     </row>
@@ -3968,12 +4630,15 @@
       <c r="B221" t="n">
         <v>13765.57767700441</v>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="n">
+      <c r="C221" t="n">
+        <v>1733.507453040056</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="n">
         <v>52201</v>
       </c>
     </row>
@@ -3984,12 +4649,15 @@
       <c r="B222" t="n">
         <v>2398.934475802898</v>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="n">
+      <c r="C222" t="n">
+        <v>2120.004128953637</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
         <v>52213</v>
       </c>
     </row>

--- a/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
+++ b/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,14 +505,14 @@
         <v>49690</v>
       </c>
       <c r="B4" t="n">
-        <v>8320.05782540196</v>
+        <v>5574.182698411758</v>
       </c>
       <c r="C4" t="n">
-        <v>1809.792870170805</v>
+        <v>1570.903935695926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -540,89 +540,89 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>49720.99999999999</v>
+        <v>49710.08281537286</v>
       </c>
       <c r="B6" t="n">
-        <v>2792.099258051032</v>
+        <v>22548.65179511749</v>
       </c>
       <c r="C6" t="n">
-        <v>2418.694728996602</v>
+        <v>2206.852229933696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>49720</v>
+        <v>49710</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>49721</v>
+        <v>49720.99999999999</v>
       </c>
       <c r="B7" t="n">
-        <v>3892.33910341701</v>
+        <v>2792.099258051032</v>
       </c>
       <c r="C7" t="n">
-        <v>1844.148747400495</v>
+        <v>2418.694728996602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>49721</v>
+        <v>49720</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>49731.25362246132</v>
+        <v>49721</v>
       </c>
       <c r="B8" t="n">
-        <v>3548.383114334327</v>
+        <v>3892.33910341701</v>
       </c>
       <c r="C8" t="n">
-        <v>2165.408933062228</v>
+        <v>1844.148747400495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>49731</v>
+        <v>49721</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>49749.99999999996</v>
+        <v>49723.33359799321</v>
       </c>
       <c r="B9" t="n">
-        <v>2194.094353055985</v>
+        <v>3538.71047544195</v>
       </c>
       <c r="C9" t="n">
-        <v>2421.177020672218</v>
+        <v>2804.248895545649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>49749</v>
+        <v>49723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>49751</v>
+        <v>49731.25362246132</v>
       </c>
       <c r="B10" t="n">
-        <v>4188.738280471291</v>
+        <v>3548.383114334327</v>
       </c>
       <c r="C10" t="n">
-        <v>2147.355498823109</v>
+        <v>2165.408933062228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>49751</v>
+        <v>49731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>49757.01719981766</v>
+        <v>49744.36466248559</v>
       </c>
       <c r="B11" t="n">
-        <v>2870.027924414046</v>
+        <v>4562.331529096375</v>
       </c>
       <c r="C11" t="n">
-        <v>2014.283765730962</v>
+        <v>1514.426464254979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>49757</v>
+        <v>49744</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>49761.76064081514</v>
+        <v>49749.99999999996</v>
       </c>
       <c r="B12" t="n">
-        <v>2158.958570207707</v>
+        <v>2194.094353055985</v>
       </c>
       <c r="C12" t="n">
-        <v>2408.818487025273</v>
+        <v>2421.177020672218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -668,132 +668,132 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>49761</v>
+        <v>49749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>49780.99999999945</v>
+        <v>49751</v>
       </c>
       <c r="B13" t="n">
-        <v>6804.731680469064</v>
+        <v>4188.738280471291</v>
       </c>
       <c r="C13" t="n">
-        <v>2192.457482160421</v>
+        <v>2147.355498823109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>49780</v>
+        <v>49751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>49781.00000000004</v>
+        <v>49757.01719981766</v>
       </c>
       <c r="B14" t="n">
-        <v>2384.103297490123</v>
+        <v>2870.027924414046</v>
       </c>
       <c r="C14" t="n">
-        <v>2381.87425132062</v>
+        <v>2014.283765730962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>49781</v>
+        <v>49757</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>49810.99999999933</v>
+        <v>49761.76064081514</v>
       </c>
       <c r="B15" t="n">
-        <v>3439.530765537691</v>
+        <v>2158.958570207707</v>
       </c>
       <c r="C15" t="n">
-        <v>2150.8566228381</v>
+        <v>2408.818487025273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>49810</v>
+        <v>49761</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>49811</v>
+        <v>49766.05782967587</v>
       </c>
       <c r="B16" t="n">
-        <v>1923.275363787801</v>
+        <v>11585.45252226174</v>
       </c>
       <c r="C16" t="n">
-        <v>2192.151036208945</v>
+        <v>2808.476606443856</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>49811</v>
+        <v>49766</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>49812</v>
+        <v>49780.99999999945</v>
       </c>
       <c r="B17" t="n">
-        <v>3425.211385385666</v>
+        <v>6804.731680469064</v>
       </c>
       <c r="C17" t="n">
-        <v>1882.657672009366</v>
+        <v>2192.457482160421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>49812</v>
+        <v>49780</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>49825.10000955164</v>
+        <v>49781.00000000004</v>
       </c>
       <c r="B18" t="n">
-        <v>1685.813591970005</v>
+        <v>2384.103297490123</v>
       </c>
       <c r="C18" t="n">
-        <v>2247.865780317195</v>
+        <v>2381.87425132062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>49825</v>
+        <v>49781</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>49839.89255517384</v>
+        <v>49810.99999999933</v>
       </c>
       <c r="B19" t="n">
-        <v>1749.397915201365</v>
+        <v>3439.530765537691</v>
       </c>
       <c r="C19" t="n">
-        <v>2259.602661185481</v>
+        <v>2150.8566228381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -801,94 +801,94 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>49839</v>
+        <v>49810</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>49842.00000009518</v>
+        <v>49811</v>
       </c>
       <c r="B20" t="n">
-        <v>1754.051220948018</v>
+        <v>1923.275363787801</v>
       </c>
       <c r="C20" t="n">
-        <v>2268.734154436177</v>
+        <v>2192.151036208945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>49842</v>
+        <v>49811</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>49873</v>
+        <v>49812</v>
       </c>
       <c r="B21" t="n">
-        <v>3073.580033918888</v>
+        <v>3425.211385385666</v>
       </c>
       <c r="C21" t="n">
-        <v>2696.115575550588</v>
+        <v>1882.657672009366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>49873</v>
+        <v>49812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>49902.99995380095</v>
+        <v>49813.60627184991</v>
       </c>
       <c r="B22" t="n">
-        <v>6218.415188723526</v>
+        <v>10840.3768196267</v>
       </c>
       <c r="C22" t="n">
-        <v>2278.24115398949</v>
+        <v>2250.53344306063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>49902</v>
+        <v>49813</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>49904</v>
+        <v>49821.82756801447</v>
       </c>
       <c r="B23" t="n">
-        <v>5311.268775563029</v>
+        <v>7868.761597339126</v>
       </c>
       <c r="C23" t="n">
-        <v>2659.159209492987</v>
+        <v>3468.567676979959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>49904</v>
+        <v>49821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>49934.00000067957</v>
+        <v>49825.10000955164</v>
       </c>
       <c r="B24" t="n">
-        <v>10352.60012788985</v>
+        <v>1685.813591970005</v>
       </c>
       <c r="C24" t="n">
-        <v>2221.323010622914</v>
+        <v>2247.865780317195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -896,18 +896,18 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>49934</v>
+        <v>49825</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>49964</v>
+        <v>49839.89255517384</v>
       </c>
       <c r="B25" t="n">
-        <v>11517.21402762166</v>
+        <v>1749.397915201365</v>
       </c>
       <c r="C25" t="n">
-        <v>2106.161208597895</v>
+        <v>2259.602661185481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>49964</v>
+        <v>49839</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>49965.00000000778</v>
+        <v>49841.99999999999</v>
       </c>
       <c r="B26" t="n">
-        <v>11831.27101635916</v>
+        <v>21684.59244720977</v>
       </c>
       <c r="C26" t="n">
-        <v>1932.617816417112</v>
+        <v>1709.611666412952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>49965</v>
+        <v>49841</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>49994.99999999999</v>
+        <v>49842.00000009518</v>
       </c>
       <c r="B27" t="n">
-        <v>7485.582718456546</v>
+        <v>1754.051220948018</v>
       </c>
       <c r="C27" t="n">
-        <v>2172.44536459794</v>
+        <v>2268.734154436177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -953,569 +953,569 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>49994</v>
+        <v>49842</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>49995</v>
+        <v>49853.02976850328</v>
       </c>
       <c r="B28" t="n">
-        <v>11013.20471000736</v>
+        <v>6651.154258845489</v>
       </c>
       <c r="C28" t="n">
-        <v>1887.323313268829</v>
+        <v>2186.94724723481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>49995</v>
+        <v>49853</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>50002.96941057956</v>
+        <v>49872</v>
       </c>
       <c r="B29" t="n">
-        <v>7441.556565931416</v>
+        <v>17936.98856312278</v>
       </c>
       <c r="C29" t="n">
-        <v>2174.470689458123</v>
+        <v>1702.941218955582</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>50002</v>
+        <v>49872</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>50005.26187652576</v>
+        <v>49873</v>
       </c>
       <c r="B30" t="n">
-        <v>10531.56442559575</v>
+        <v>3073.580033918888</v>
       </c>
       <c r="C30" t="n">
-        <v>1875.708955842925</v>
+        <v>2696.115575550588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>50005</v>
+        <v>49873</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>50023.46139567861</v>
+        <v>49891.81756594559</v>
       </c>
       <c r="B31" t="n">
-        <v>14690.15501630144</v>
+        <v>15773.40257667917</v>
       </c>
       <c r="C31" t="n">
-        <v>2203.12341552909</v>
+        <v>1881.862612150232</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>50023</v>
+        <v>49891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>50026</v>
+        <v>49902.99995380095</v>
       </c>
       <c r="B32" t="n">
-        <v>12593.87390044965</v>
+        <v>6218.415188723526</v>
       </c>
       <c r="C32" t="n">
-        <v>1871.796680734057</v>
+        <v>2278.24115398949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>50026</v>
+        <v>49902</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>50044.77211893302</v>
+        <v>49903</v>
       </c>
       <c r="B33" t="n">
-        <v>5258.898560609356</v>
+        <v>14090.71200845656</v>
       </c>
       <c r="C33" t="n">
-        <v>2189.646206298512</v>
+        <v>3374.723899076333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>50044</v>
+        <v>49903</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>50055.99999999996</v>
+        <v>49904</v>
       </c>
       <c r="B34" t="n">
-        <v>12566.94131364906</v>
+        <v>5311.268775563029</v>
       </c>
       <c r="C34" t="n">
-        <v>2566.345794266159</v>
+        <v>2659.159209492987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>50055</v>
+        <v>49904</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>50057.00000000001</v>
+        <v>49914.67676055161</v>
       </c>
       <c r="B35" t="n">
-        <v>5606.03318477464</v>
+        <v>10411.76454476436</v>
       </c>
       <c r="C35" t="n">
-        <v>2209.142463769347</v>
+        <v>2288.481099556781</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>50057</v>
+        <v>49914</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>50086.99999999976</v>
+        <v>49934.00000067957</v>
       </c>
       <c r="B36" t="n">
-        <v>10502.98879667432</v>
+        <v>10352.60012788985</v>
       </c>
       <c r="C36" t="n">
-        <v>2912.530806627877</v>
+        <v>2221.323010622914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>50086</v>
+        <v>49934</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>50087</v>
+        <v>49964</v>
       </c>
       <c r="B37" t="n">
-        <v>7310.898772067319</v>
+        <v>10964.5367508746</v>
       </c>
       <c r="C37" t="n">
-        <v>1828.005909077775</v>
+        <v>2582.386020586953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>50087</v>
+        <v>49964</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>50103.0400619114</v>
+        <v>49965.00000000778</v>
       </c>
       <c r="B38" t="n">
-        <v>5903.189955385513</v>
+        <v>11831.27101635916</v>
       </c>
       <c r="C38" t="n">
-        <v>2327.717433949053</v>
+        <v>1932.617816417112</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>50103</v>
+        <v>49965</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>50110.53642349604</v>
+        <v>49994.99999999999</v>
       </c>
       <c r="B39" t="n">
-        <v>4157.216501496716</v>
+        <v>7485.582718456546</v>
       </c>
       <c r="C39" t="n">
-        <v>2102.094217118578</v>
+        <v>2172.44536459794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>50110</v>
+        <v>49994</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>50114.99999999979</v>
+        <v>49995</v>
       </c>
       <c r="B40" t="n">
-        <v>9367.025662902255</v>
+        <v>9995.347835216377</v>
       </c>
       <c r="C40" t="n">
-        <v>1897.593923002144</v>
+        <v>2532.592657404448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>50114</v>
+        <v>49995</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>50116.00000000002</v>
+        <v>50002.96941057956</v>
       </c>
       <c r="B41" t="n">
-        <v>4212.766195050981</v>
+        <v>7441.556565931416</v>
       </c>
       <c r="C41" t="n">
-        <v>2198.372332482092</v>
+        <v>2174.470689458123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>50116</v>
+        <v>50002</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>50145.99999997555</v>
+        <v>50005.26187652576</v>
       </c>
       <c r="B42" t="n">
-        <v>7282.00165318889</v>
+        <v>10531.56442559575</v>
       </c>
       <c r="C42" t="n">
-        <v>1933.902771551656</v>
+        <v>1875.708955842925</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>50145</v>
+        <v>50005</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>50146.00000000001</v>
+        <v>50015.86390355966</v>
       </c>
       <c r="B43" t="n">
-        <v>9333.512282055686</v>
+        <v>10642.43244101867</v>
       </c>
       <c r="C43" t="n">
-        <v>2340.215568356512</v>
+        <v>2134.918706918362</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>50146</v>
+        <v>50015</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>50147.10927236939</v>
+        <v>50021.42664137657</v>
       </c>
       <c r="B44" t="n">
-        <v>8432.632128542213</v>
+        <v>5313.822739752384</v>
       </c>
       <c r="C44" t="n">
-        <v>2829.503091028412</v>
+        <v>2380.964803250717</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>50147</v>
+        <v>50021</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>50175.9999999703</v>
+        <v>50023.46139567861</v>
       </c>
       <c r="B45" t="n">
-        <v>6423.185268220112</v>
+        <v>14690.15501630144</v>
       </c>
       <c r="C45" t="n">
-        <v>1941.768095325454</v>
+        <v>2203.12341552909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>50175</v>
+        <v>50023</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>50176</v>
+        <v>50024.99999999838</v>
       </c>
       <c r="B46" t="n">
-        <v>4097.357354962637</v>
+        <v>9435.362722413349</v>
       </c>
       <c r="C46" t="n">
-        <v>1790.01084031046</v>
+        <v>2384.079915802404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>50176</v>
+        <v>50024</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>50177.00000000028</v>
+        <v>50026.00000000012</v>
       </c>
       <c r="B47" t="n">
-        <v>8669.81700802522</v>
+        <v>5819.677980780902</v>
       </c>
       <c r="C47" t="n">
-        <v>2790.23979448662</v>
+        <v>2378.225107137991</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>50177</v>
+        <v>50026</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>50206.99999999988</v>
+        <v>50042.39476538876</v>
       </c>
       <c r="B48" t="n">
-        <v>2623.484723817457</v>
+        <v>9286.08096615166</v>
       </c>
       <c r="C48" t="n">
-        <v>2242.7733766652</v>
+        <v>2379.239917366832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>50206</v>
+        <v>50042</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>50209.53045489201</v>
+        <v>50044.77211893302</v>
       </c>
       <c r="B49" t="n">
-        <v>2993.960184637568</v>
+        <v>5258.898560609356</v>
       </c>
       <c r="C49" t="n">
-        <v>1924.94898001043</v>
+        <v>2189.646206298512</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>50209</v>
+        <v>50044</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>50236.99999999499</v>
+        <v>50049.98000851885</v>
       </c>
       <c r="B50" t="n">
-        <v>1904.095767382581</v>
+        <v>7864.044291973189</v>
       </c>
       <c r="C50" t="n">
-        <v>2308.295145207988</v>
+        <v>2069.066236965054</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>50236</v>
+        <v>50049</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>50238.00000000002</v>
+        <v>50055.99999999996</v>
       </c>
       <c r="B51" t="n">
-        <v>3176.9239440372</v>
+        <v>12566.94131364906</v>
       </c>
       <c r="C51" t="n">
-        <v>2144.099730097068</v>
+        <v>2566.345794266159</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>50238</v>
+        <v>50055</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>50247.5041517035</v>
+        <v>50057.00000000001</v>
       </c>
       <c r="B52" t="n">
-        <v>5896.513043619248</v>
+        <v>5606.03318477464</v>
       </c>
       <c r="C52" t="n">
-        <v>1962.10821264015</v>
+        <v>2209.142463769347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>50247</v>
+        <v>50057</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>50266.0191658948</v>
+        <v>50079.9190491689</v>
       </c>
       <c r="B53" t="n">
-        <v>1612.872369061143</v>
+        <v>8157.214439713516</v>
       </c>
       <c r="C53" t="n">
-        <v>2324.356202279828</v>
+        <v>2285.009186311193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>50266</v>
+        <v>50079</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>50269.00000000001</v>
+        <v>50086.99999999976</v>
       </c>
       <c r="B54" t="n">
-        <v>3929.322283618183</v>
+        <v>10502.98879667432</v>
       </c>
       <c r="C54" t="n">
-        <v>2305.072877103079</v>
+        <v>2912.530806627877</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>50269</v>
+        <v>50086</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>50285.6616809397</v>
+        <v>50087</v>
       </c>
       <c r="B55" t="n">
-        <v>8639.123786193522</v>
+        <v>7233.711950821164</v>
       </c>
       <c r="C55" t="n">
-        <v>2575.685791325593</v>
+        <v>2046.419984796273</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>50285</v>
+        <v>50087</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>50298.99999955763</v>
+        <v>50093.00150678644</v>
       </c>
       <c r="B56" t="n">
-        <v>1281.140028060378</v>
+        <v>11233.5790675634</v>
       </c>
       <c r="C56" t="n">
-        <v>2263.218591481248</v>
+        <v>3769.952455647157</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>50298</v>
+        <v>50093</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>50312.67921365725</v>
+        <v>50103.0400619114</v>
       </c>
       <c r="B57" t="n">
-        <v>1226.643527751176</v>
+        <v>5903.189955385513</v>
       </c>
       <c r="C57" t="n">
-        <v>2246.59451785385</v>
+        <v>2327.717433949053</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1523,246 +1523,246 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>50312</v>
+        <v>50103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>50328.98916874855</v>
+        <v>50110.53642349604</v>
       </c>
       <c r="B58" t="n">
-        <v>4025.626151603145</v>
+        <v>4157.216501496716</v>
       </c>
       <c r="C58" t="n">
-        <v>2461.587991409666</v>
+        <v>2102.094217118578</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>50328</v>
+        <v>50110</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>50330.00000114757</v>
+        <v>50114.99999953134</v>
       </c>
       <c r="B59" t="n">
-        <v>1304.435073724873</v>
+        <v>7688.004535077018</v>
       </c>
       <c r="C59" t="n">
-        <v>2269.400354333155</v>
+        <v>2251.903359779681</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>50330</v>
+        <v>50114</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>50331.04250198191</v>
+        <v>50115</v>
       </c>
       <c r="B60" t="n">
-        <v>5489.657222481161</v>
+        <v>6992.242352608417</v>
       </c>
       <c r="C60" t="n">
-        <v>1733.562603245736</v>
+        <v>2012.194933905702</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>50331</v>
+        <v>50115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>50346.61002439493</v>
+        <v>50116.00000000002</v>
       </c>
       <c r="B61" t="n">
-        <v>7433.167367619011</v>
+        <v>4212.766195050981</v>
       </c>
       <c r="C61" t="n">
-        <v>2526.645998924158</v>
+        <v>2198.372332482092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>50346</v>
+        <v>50116</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>50359.63914589051</v>
+        <v>50121.15903110583</v>
       </c>
       <c r="B62" t="n">
-        <v>5730.655802558076</v>
+        <v>6965.596437631029</v>
       </c>
       <c r="C62" t="n">
-        <v>1887.823034859797</v>
+        <v>2003.5026359321</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>50359</v>
+        <v>50121</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>50360.00000001179</v>
+        <v>50126.34916076845</v>
       </c>
       <c r="B63" t="n">
-        <v>2061.400631155953</v>
+        <v>7609.650137529759</v>
       </c>
       <c r="C63" t="n">
-        <v>2076.551135953471</v>
+        <v>2244.322415264078</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>50360</v>
+        <v>50126</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>50391.00000098178</v>
+        <v>50145.99999997555</v>
       </c>
       <c r="B64" t="n">
-        <v>3483.180135969717</v>
+        <v>7282.00165318889</v>
       </c>
       <c r="C64" t="n">
-        <v>2297.972682958062</v>
+        <v>1933.902771551656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>50391</v>
+        <v>50145</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>50422.00000000031</v>
+        <v>50146.00000000001</v>
       </c>
       <c r="B65" t="n">
-        <v>10050.49417410825</v>
+        <v>9333.512282055686</v>
       </c>
       <c r="C65" t="n">
-        <v>1866.170420320066</v>
+        <v>2340.215568356512</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>50422</v>
+        <v>50146</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>50450.00000000389</v>
+        <v>50147.10927236939</v>
       </c>
       <c r="B66" t="n">
-        <v>13143.42643058428</v>
+        <v>8432.632128542213</v>
       </c>
       <c r="C66" t="n">
-        <v>2136.34057749607</v>
+        <v>2829.503091028412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>50450</v>
+        <v>50147</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>50452</v>
+        <v>50154.13103458376</v>
       </c>
       <c r="B67" t="n">
-        <v>17605.21103145456</v>
+        <v>14139.69700937306</v>
       </c>
       <c r="C67" t="n">
-        <v>1472.972774393054</v>
+        <v>3707.981291062596</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>50452</v>
+        <v>50154</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>50479.94708688899</v>
+        <v>50175.9999999703</v>
       </c>
       <c r="B68" t="n">
-        <v>7953.704450992684</v>
+        <v>6423.185268220112</v>
       </c>
       <c r="C68" t="n">
-        <v>2313.811109122985</v>
+        <v>1941.768095325454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>50479</v>
+        <v>50175</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>50480</v>
+        <v>50176</v>
       </c>
       <c r="B69" t="n">
-        <v>10374.61620937778</v>
+        <v>4097.357354962637</v>
       </c>
       <c r="C69" t="n">
-        <v>2086.714298284358</v>
+        <v>1790.01084031046</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>50480</v>
+        <v>50176</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>50502.91912981059</v>
+        <v>50177.00000000028</v>
       </c>
       <c r="B70" t="n">
-        <v>10691.16272220942</v>
+        <v>8669.81700802522</v>
       </c>
       <c r="C70" t="n">
-        <v>2381.751828698761</v>
+        <v>2790.23979448662</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1770,18 +1770,18 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50502</v>
+        <v>50177</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>50510.99999999991</v>
+        <v>50206.99999999988</v>
       </c>
       <c r="B71" t="n">
-        <v>9533.710982477673</v>
+        <v>2623.484723817457</v>
       </c>
       <c r="C71" t="n">
-        <v>2432.63302981191</v>
+        <v>2242.7733766652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1789,284 +1789,284 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>50510</v>
+        <v>50206</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>50511</v>
+        <v>50207</v>
       </c>
       <c r="B72" t="n">
-        <v>10125.14591720093</v>
+        <v>6609.106364154404</v>
       </c>
       <c r="C72" t="n">
-        <v>1756.452140534336</v>
+        <v>2439.701384921922</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>50511</v>
+        <v>50207</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>50523.7212014887</v>
+        <v>50209.53045489201</v>
       </c>
       <c r="B73" t="n">
-        <v>9314.139912326753</v>
+        <v>2993.960184637568</v>
       </c>
       <c r="C73" t="n">
-        <v>2451.70808029176</v>
+        <v>1924.94898001043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>50523</v>
+        <v>50209</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>50540.99999985442</v>
+        <v>50236.99999999499</v>
       </c>
       <c r="B74" t="n">
-        <v>9501.685650544772</v>
+        <v>1904.095767382581</v>
       </c>
       <c r="C74" t="n">
-        <v>2226.430164437737</v>
+        <v>2308.295145207988</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>50540</v>
+        <v>50236</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>50542</v>
+        <v>50237</v>
       </c>
       <c r="B75" t="n">
-        <v>11190.77427650684</v>
+        <v>4243.568087026255</v>
       </c>
       <c r="C75" t="n">
-        <v>2434.966342797619</v>
+        <v>2513.135729455395</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>50542</v>
+        <v>50237</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>50571.99999830132</v>
+        <v>50238.00000000002</v>
       </c>
       <c r="B76" t="n">
-        <v>8914.921738761195</v>
+        <v>3176.9239440372</v>
       </c>
       <c r="C76" t="n">
-        <v>1982.754346460781</v>
+        <v>2144.099730097068</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>50571</v>
+        <v>50238</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>50572</v>
+        <v>50247.5041517035</v>
       </c>
       <c r="B77" t="n">
-        <v>4970.409846064256</v>
+        <v>5896.513043619248</v>
       </c>
       <c r="C77" t="n">
-        <v>1868.19844205007</v>
+        <v>1962.10821264015</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>50572</v>
+        <v>50247</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>50577.11842025915</v>
+        <v>50251.26655907223</v>
       </c>
       <c r="B78" t="n">
-        <v>4926.09731237362</v>
+        <v>8147.54288196213</v>
       </c>
       <c r="C78" t="n">
-        <v>1911.973287358774</v>
+        <v>1800.478334979972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>50577</v>
+        <v>50251</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>50584.221441086</v>
+        <v>50266.0191658948</v>
       </c>
       <c r="B79" t="n">
-        <v>5504.271794751188</v>
+        <v>1612.872369061143</v>
       </c>
       <c r="C79" t="n">
-        <v>2285.51146039578</v>
+        <v>2324.356202279828</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50584</v>
+        <v>50266</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>50601.99999790893</v>
+        <v>50267.99999999996</v>
       </c>
       <c r="B80" t="n">
-        <v>7411.010111142448</v>
+        <v>14163.84265530369</v>
       </c>
       <c r="C80" t="n">
-        <v>2192.791410556332</v>
+        <v>2499.181825473205</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>50601</v>
+        <v>50267</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>50603</v>
+        <v>50268</v>
       </c>
       <c r="B81" t="n">
-        <v>5419.024794353403</v>
+        <v>3354.291032396673</v>
       </c>
       <c r="C81" t="n">
-        <v>2334.570352736235</v>
+        <v>2574.580600077766</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>50603</v>
+        <v>50268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>50609.14257518217</v>
+        <v>50269.00000000001</v>
       </c>
       <c r="B82" t="n">
-        <v>15592.91114340716</v>
+        <v>3929.322283618183</v>
       </c>
       <c r="C82" t="n">
-        <v>2182.623987649073</v>
+        <v>2305.072877103079</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>50609</v>
+        <v>50269</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>50625.43303640582</v>
+        <v>50285.6616809397</v>
       </c>
       <c r="B83" t="n">
-        <v>8623.181127884431</v>
+        <v>8639.123786193522</v>
       </c>
       <c r="C83" t="n">
-        <v>1979.60111981427</v>
+        <v>2575.685791325593</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>50625</v>
+        <v>50285</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>50632.99999985303</v>
+        <v>50289.35684409607</v>
       </c>
       <c r="B84" t="n">
-        <v>6087.053671843214</v>
+        <v>3118.389425793209</v>
       </c>
       <c r="C84" t="n">
-        <v>2154.938259939948</v>
+        <v>2583.491862647853</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>50632</v>
+        <v>50289</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>50634.00000111378</v>
+        <v>50294.59984804859</v>
       </c>
       <c r="B85" t="n">
-        <v>8636.15812024055</v>
+        <v>13525.39348879664</v>
       </c>
       <c r="C85" t="n">
-        <v>2006.613786012682</v>
+        <v>2508.878673321225</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>50634</v>
+        <v>50294</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>50662.03480030189</v>
+        <v>50298.99999955763</v>
       </c>
       <c r="B86" t="n">
-        <v>10082.12352184699</v>
+        <v>1281.140028060378</v>
       </c>
       <c r="C86" t="n">
-        <v>2210.291767919855</v>
+        <v>2263.218591481248</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2074,56 +2074,56 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>50662</v>
+        <v>50298</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>50663.99999983652</v>
+        <v>50299</v>
       </c>
       <c r="B87" t="n">
-        <v>16317.29067598553</v>
+        <v>8333.725018807958</v>
       </c>
       <c r="C87" t="n">
-        <v>2576.497418381885</v>
+        <v>1693.779765718234</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>50663</v>
+        <v>50299</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>50664</v>
+        <v>50301.49055553319</v>
       </c>
       <c r="B88" t="n">
-        <v>6971.32766144599</v>
+        <v>8306.902184100338</v>
       </c>
       <c r="C88" t="n">
-        <v>2656.521348767914</v>
+        <v>1698.906019810318</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>50664</v>
+        <v>50301</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>50693.99998353783</v>
+        <v>50312.67921365725</v>
       </c>
       <c r="B89" t="n">
-        <v>5724.401290286592</v>
+        <v>1226.643527751176</v>
       </c>
       <c r="C89" t="n">
-        <v>1855.304974749868</v>
+        <v>2246.59451785385</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2131,455 +2131,455 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>50693</v>
+        <v>50312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>50694</v>
+        <v>50328.99999999993</v>
       </c>
       <c r="B90" t="n">
-        <v>14053.35985024147</v>
+        <v>2826.88191337481</v>
       </c>
       <c r="C90" t="n">
-        <v>2510.539464482986</v>
+        <v>2532.26870766534</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>50694</v>
+        <v>50328</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>50701.86249227352</v>
+        <v>50330.00000114757</v>
       </c>
       <c r="B91" t="n">
-        <v>8400.739992649806</v>
+        <v>1304.435073724873</v>
       </c>
       <c r="C91" t="n">
-        <v>1440.375654276172</v>
+        <v>2269.400354333155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>50701</v>
+        <v>50330</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>50722.18749133358</v>
+        <v>50331.04250198191</v>
       </c>
       <c r="B92" t="n">
-        <v>8991.286452426157</v>
+        <v>5489.657222481161</v>
       </c>
       <c r="C92" t="n">
-        <v>2197.513254430934</v>
+        <v>1733.562603245736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>50722</v>
+        <v>50331</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>50724.99999992725</v>
+        <v>50346.61002439493</v>
       </c>
       <c r="B93" t="n">
-        <v>8528.383512543847</v>
+        <v>7433.167367619011</v>
       </c>
       <c r="C93" t="n">
-        <v>1809.368534275456</v>
+        <v>2526.645998924158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>50724</v>
+        <v>50346</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>50725.00000000196</v>
+        <v>50359.63914589051</v>
       </c>
       <c r="B94" t="n">
-        <v>8994.47945288652</v>
+        <v>5730.655802558076</v>
       </c>
       <c r="C94" t="n">
-        <v>2184.748565254792</v>
+        <v>1887.823034859797</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>50725</v>
+        <v>50359</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>50740.91438029714</v>
+        <v>50360.00000001179</v>
       </c>
       <c r="B95" t="n">
-        <v>8420.998416839837</v>
+        <v>2061.400631155953</v>
       </c>
       <c r="C95" t="n">
-        <v>1859.526083568553</v>
+        <v>2076.551135953471</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>50740</v>
+        <v>50360</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>50754.99999999983</v>
+        <v>50389.99999999916</v>
       </c>
       <c r="B96" t="n">
-        <v>7120.708598626936</v>
+        <v>12872.98439823645</v>
       </c>
       <c r="C96" t="n">
-        <v>2358.281446849489</v>
+        <v>2306.154084060168</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>50754</v>
+        <v>50389</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>50756.00000107639</v>
+        <v>50390</v>
       </c>
       <c r="B97" t="n">
-        <v>8450.061692567881</v>
+        <v>13107.03123856003</v>
       </c>
       <c r="C97" t="n">
-        <v>1878.852391323249</v>
+        <v>2391.652767487162</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>50756</v>
+        <v>50390</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>50785.99999999998</v>
+        <v>50391.00000098178</v>
       </c>
       <c r="B98" t="n">
-        <v>6423.328891556714</v>
+        <v>3483.180135969717</v>
       </c>
       <c r="C98" t="n">
-        <v>2339.467481898279</v>
+        <v>2297.972682958062</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>50785</v>
+        <v>50391</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>50787.00000001583</v>
+        <v>50420.99999999999</v>
       </c>
       <c r="B99" t="n">
-        <v>8629.505628092676</v>
+        <v>10596.44146953104</v>
       </c>
       <c r="C99" t="n">
-        <v>1916.702946955712</v>
+        <v>2286.627814971291</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>50787</v>
+        <v>50420</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>50815.00000000462</v>
+        <v>50421</v>
       </c>
       <c r="B100" t="n">
-        <v>8910.971937618671</v>
+        <v>11845.05729720452</v>
       </c>
       <c r="C100" t="n">
-        <v>1998.110807810896</v>
+        <v>2358.939157881943</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>50815</v>
+        <v>50421</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>50817</v>
+        <v>50422.00000000001</v>
       </c>
       <c r="B101" t="n">
-        <v>4325.631370845627</v>
+        <v>9982.696491826278</v>
       </c>
       <c r="C101" t="n">
-        <v>2308.635154570006</v>
+        <v>1778.967148121145</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>50817</v>
+        <v>50422</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>50835.04666135355</v>
+        <v>50450.00000000389</v>
       </c>
       <c r="B102" t="n">
-        <v>4167.977572363327</v>
+        <v>13143.42643058428</v>
       </c>
       <c r="C102" t="n">
-        <v>2294.505975461052</v>
+        <v>2136.34057749607</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>50835</v>
+        <v>50450</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>50845</v>
+        <v>50451.99999999996</v>
       </c>
       <c r="B103" t="n">
-        <v>13786.93976366671</v>
+        <v>9704.302347306271</v>
       </c>
       <c r="C103" t="n">
-        <v>1737.000470174526</v>
+        <v>2307.568270740891</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>50845</v>
+        <v>50451</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>50853.08998982541</v>
+        <v>50452</v>
       </c>
       <c r="B104" t="n">
-        <v>13625.64212755976</v>
+        <v>8837.206102225651</v>
       </c>
       <c r="C104" t="n">
-        <v>2607.479208896762</v>
+        <v>2348.203702590105</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>50853</v>
+        <v>50452</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>50875.99999999998</v>
+        <v>50460.32559676943</v>
       </c>
       <c r="B105" t="n">
-        <v>3678.106718036061</v>
+        <v>9850.162433164183</v>
       </c>
       <c r="C105" t="n">
-        <v>2058.479935469316</v>
+        <v>1742.12180992899</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>50875</v>
+        <v>50460</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>50876</v>
+        <v>50479.99999999983</v>
       </c>
       <c r="B106" t="n">
-        <v>8492.148314168053</v>
+        <v>7786.285265712975</v>
       </c>
       <c r="C106" t="n">
-        <v>1761.84468458551</v>
+        <v>2321.664737177104</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>50876</v>
+        <v>50479</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>50905.99999999999</v>
+        <v>50480</v>
       </c>
       <c r="B107" t="n">
-        <v>3055.610235271717</v>
+        <v>5268.687397953092</v>
       </c>
       <c r="C107" t="n">
-        <v>2127.739365076152</v>
+        <v>2283.193355093578</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>50905</v>
+        <v>50480</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>50906</v>
+        <v>50481</v>
       </c>
       <c r="B108" t="n">
-        <v>4358.456162985729</v>
+        <v>10830.86496514112</v>
       </c>
       <c r="C108" t="n">
-        <v>1797.95349274327</v>
+        <v>1736.320925338806</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>50906</v>
+        <v>50481</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>50907.00000000006</v>
+        <v>50491.84315109754</v>
       </c>
       <c r="B109" t="n">
-        <v>14756.49360791315</v>
+        <v>19581.81320530766</v>
       </c>
       <c r="C109" t="n">
-        <v>2513.306697699584</v>
+        <v>2208.324463837054</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>50907</v>
+        <v>50491</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>50914.36543559227</v>
+        <v>50502.91912981059</v>
       </c>
       <c r="B110" t="n">
-        <v>2958.267430990622</v>
+        <v>10691.16272220942</v>
       </c>
       <c r="C110" t="n">
-        <v>2107.226474707514</v>
+        <v>2381.751828698761</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>50914</v>
+        <v>50502</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>50925.35648712025</v>
+        <v>50507.57501945825</v>
       </c>
       <c r="B111" t="n">
-        <v>3086.75257694494</v>
+        <v>3568.318274995252</v>
       </c>
       <c r="C111" t="n">
-        <v>2194.507348288722</v>
+        <v>3032.793831148176</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>50925</v>
+        <v>50507</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>50937</v>
+        <v>50510.99999956862</v>
       </c>
       <c r="B112" t="n">
-        <v>3067.572901237036</v>
+        <v>7219.37377569156</v>
       </c>
       <c r="C112" t="n">
-        <v>1849.279973934608</v>
+        <v>2330.895806223752</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>50937</v>
+        <v>50510</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>50943.91832806184</v>
+        <v>50511</v>
       </c>
       <c r="B113" t="n">
-        <v>3043.963355083282</v>
+        <v>10125.14591720093</v>
       </c>
       <c r="C113" t="n">
-        <v>1865.492957054876</v>
+        <v>1756.452140534336</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -2587,75 +2587,75 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>50943</v>
+        <v>50511</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>50968.00000000001</v>
+        <v>50515.5840754594</v>
       </c>
       <c r="B114" t="n">
-        <v>3294.552202643603</v>
+        <v>2810.482497569543</v>
       </c>
       <c r="C114" t="n">
-        <v>1908.095096532966</v>
+        <v>3490.800518794136</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>50968</v>
+        <v>50515</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>50997.99999999999</v>
+        <v>50518.63230988051</v>
       </c>
       <c r="B115" t="n">
-        <v>2217.618581364153</v>
+        <v>7173.682630185289</v>
       </c>
       <c r="C115" t="n">
-        <v>2096.524316736547</v>
+        <v>2352.75211221374</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>50997</v>
+        <v>50518</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>50999</v>
+        <v>50523.7212014887</v>
       </c>
       <c r="B116" t="n">
-        <v>4384.749504158795</v>
+        <v>9314.139912326753</v>
       </c>
       <c r="C116" t="n">
-        <v>1651.155113152701</v>
+        <v>2451.70808029176</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>50999</v>
+        <v>50523</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>51011.29490094929</v>
+        <v>50540.99999985442</v>
       </c>
       <c r="B117" t="n">
-        <v>1970.306025961567</v>
+        <v>9501.685650544772</v>
       </c>
       <c r="C117" t="n">
-        <v>2147.985921787038</v>
+        <v>2226.430164437737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2663,75 +2663,75 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>51011</v>
+        <v>50540</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>51028.48802084431</v>
+        <v>50541</v>
       </c>
       <c r="B118" t="n">
-        <v>11366.03409128407</v>
+        <v>12628.94937866235</v>
       </c>
       <c r="C118" t="n">
-        <v>1805.289709263106</v>
+        <v>2409.938926435361</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>51028</v>
+        <v>50541</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>51029</v>
+        <v>50542</v>
       </c>
       <c r="B119" t="n">
-        <v>2257.433812141382</v>
+        <v>3199.703107083107</v>
       </c>
       <c r="C119" t="n">
-        <v>2237.352871344337</v>
+        <v>3473.347297633192</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>51029</v>
+        <v>50542</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>51058.99999999948</v>
+        <v>50566.13764451738</v>
       </c>
       <c r="B120" t="n">
-        <v>7663.33484616197</v>
+        <v>6479.567001011212</v>
       </c>
       <c r="C120" t="n">
-        <v>2052.915523865457</v>
+        <v>2284.679535932959</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>51058</v>
+        <v>50566</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>51060</v>
+        <v>50571.99999830132</v>
       </c>
       <c r="B121" t="n">
-        <v>3544.412487819436</v>
+        <v>8914.921738761195</v>
       </c>
       <c r="C121" t="n">
-        <v>2645.08074555508</v>
+        <v>1982.754346460781</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2739,303 +2739,303 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>51060</v>
+        <v>50571</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>51069.07298970039</v>
+        <v>50572</v>
       </c>
       <c r="B122" t="n">
-        <v>7342.952185329328</v>
+        <v>4970.409846064256</v>
       </c>
       <c r="C122" t="n">
-        <v>2051.336211315354</v>
+        <v>1868.19844205007</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>51069</v>
+        <v>50572</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>51090</v>
+        <v>50577.11842025915</v>
       </c>
       <c r="B123" t="n">
-        <v>5657.110791458814</v>
+        <v>4926.09731237362</v>
       </c>
       <c r="C123" t="n">
-        <v>2671.03893029319</v>
+        <v>1911.973287358774</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>51090</v>
+        <v>50577</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>51119.99999999999</v>
+        <v>50584.221441086</v>
       </c>
       <c r="B124" t="n">
-        <v>12147.09815144838</v>
+        <v>5504.271794751188</v>
       </c>
       <c r="C124" t="n">
-        <v>1484.060331592765</v>
+        <v>2285.51146039578</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>51119</v>
+        <v>50584</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>51121.00000123936</v>
+        <v>50601.99999790893</v>
       </c>
       <c r="B125" t="n">
-        <v>10601.52856780689</v>
+        <v>7411.010111142448</v>
       </c>
       <c r="C125" t="n">
-        <v>2255.959917207415</v>
+        <v>2192.791410556332</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>51121</v>
+        <v>50601</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>51127.23397537271</v>
+        <v>50602</v>
       </c>
       <c r="B126" t="n">
-        <v>12071.0963142543</v>
+        <v>5781.43062496434</v>
       </c>
       <c r="C126" t="n">
-        <v>1515.439451014626</v>
+        <v>2736.42310817206</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>51127</v>
+        <v>50602</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>51151</v>
+        <v>50603</v>
       </c>
       <c r="B127" t="n">
-        <v>10071.22019405535</v>
+        <v>5419.024794353403</v>
       </c>
       <c r="C127" t="n">
-        <v>2023.289853973595</v>
+        <v>2334.570352736235</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>51151</v>
+        <v>50603</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>51152.00000018143</v>
+        <v>50605.50670848125</v>
       </c>
       <c r="B128" t="n">
-        <v>11154.48227417286</v>
+        <v>10337.15492961544</v>
       </c>
       <c r="C128" t="n">
-        <v>1876.041014803024</v>
+        <v>1614.321697133713</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>51152</v>
+        <v>50605</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>51176.22100097346</v>
+        <v>50609.14257518217</v>
       </c>
       <c r="B129" t="n">
-        <v>14368.57004452504</v>
+        <v>15592.91114340716</v>
       </c>
       <c r="C129" t="n">
-        <v>1263.445915302427</v>
+        <v>2182.623987649073</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>51176</v>
+        <v>50609</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>51181.99999999999</v>
+        <v>50621.72852139705</v>
       </c>
       <c r="B130" t="n">
-        <v>7983.122407120793</v>
+        <v>5812.6615229371</v>
       </c>
       <c r="C130" t="n">
-        <v>1941.527793650004</v>
+        <v>3057.554435756475</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>51181</v>
+        <v>50621</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>51206.33342933965</v>
+        <v>50625.43303640582</v>
       </c>
       <c r="B131" t="n">
-        <v>5764.511135484176</v>
+        <v>8623.181127884431</v>
       </c>
       <c r="C131" t="n">
-        <v>1913.464708496148</v>
+        <v>1979.60111981427</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>51206</v>
+        <v>50625</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>51210.99999997632</v>
+        <v>50632.99999985303</v>
       </c>
       <c r="B132" t="n">
-        <v>6838.981769905186</v>
+        <v>6087.053671843214</v>
       </c>
       <c r="C132" t="n">
-        <v>1715.41481908141</v>
+        <v>2154.938259939948</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>51210</v>
+        <v>50632</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>51211</v>
+        <v>50633</v>
       </c>
       <c r="B133" t="n">
-        <v>11838.75159857189</v>
+        <v>18919.69509095355</v>
       </c>
       <c r="C133" t="n">
-        <v>1872.287025476858</v>
+        <v>1422.779585364556</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>51211</v>
+        <v>50633</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>51212</v>
+        <v>50634.00000111378</v>
       </c>
       <c r="B134" t="n">
-        <v>5841.571117616584</v>
+        <v>8636.15812024055</v>
       </c>
       <c r="C134" t="n">
-        <v>1914.51759334634</v>
+        <v>2006.613786012682</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>51212</v>
+        <v>50634</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>51213.35111040805</v>
+        <v>50662.03480030189</v>
       </c>
       <c r="B135" t="n">
-        <v>11688.32501834102</v>
+        <v>10082.12352184699</v>
       </c>
       <c r="C135" t="n">
-        <v>1873.63602175968</v>
+        <v>2210.291767919855</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>51213</v>
+        <v>50662</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>51215.02113948088</v>
+        <v>50663.99999999996</v>
       </c>
       <c r="B136" t="n">
-        <v>6834.030789400924</v>
+        <v>4828.199283365695</v>
       </c>
       <c r="C136" t="n">
-        <v>1730.046319127933</v>
+        <v>2674.116513745867</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>51215</v>
+        <v>50663</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>51242.00000000002</v>
+        <v>50664</v>
       </c>
       <c r="B137" t="n">
-        <v>7048.574004383088</v>
+        <v>6971.32766144599</v>
       </c>
       <c r="C137" t="n">
-        <v>1875.004604960936</v>
+        <v>2656.521348767914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3043,94 +3043,94 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>51242</v>
+        <v>50664</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>51271.99999999988</v>
+        <v>50685.57120274502</v>
       </c>
       <c r="B138" t="n">
-        <v>8999.343024112595</v>
+        <v>14684.90467579933</v>
       </c>
       <c r="C138" t="n">
-        <v>2767.170753541317</v>
+        <v>1882.899193982422</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>51271</v>
+        <v>50685</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>51272</v>
+        <v>50693.99999999985</v>
       </c>
       <c r="B139" t="n">
-        <v>6160.902376060669</v>
+        <v>4868.171208775317</v>
       </c>
       <c r="C139" t="n">
-        <v>2077.232967848855</v>
+        <v>2908.952672585848</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>51272</v>
+        <v>50693</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>51273.00000000184</v>
+        <v>50694</v>
       </c>
       <c r="B140" t="n">
-        <v>13802.05950121409</v>
+        <v>7492.989064722851</v>
       </c>
       <c r="C140" t="n">
-        <v>1753.441528391346</v>
+        <v>2281.46409750192</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>51273</v>
+        <v>50694</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>51291.31523088403</v>
+        <v>50695.00000000017</v>
       </c>
       <c r="B141" t="n">
-        <v>6085.499301724671</v>
+        <v>5012.24621661172</v>
       </c>
       <c r="C141" t="n">
-        <v>2056.691656881615</v>
+        <v>2686.374933466599</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>51291</v>
+        <v>50695</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>51297.6406234313</v>
+        <v>50701.86249227352</v>
       </c>
       <c r="B142" t="n">
-        <v>4437.260464211735</v>
+        <v>8400.739992649806</v>
       </c>
       <c r="C142" t="n">
-        <v>1903.770259245576</v>
+        <v>1440.375654276172</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3138,284 +3138,284 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>51297</v>
+        <v>50701</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>51302.99999999972</v>
+        <v>50722.18749133358</v>
       </c>
       <c r="B143" t="n">
-        <v>7745.327282133348</v>
+        <v>8991.286452426157</v>
       </c>
       <c r="C143" t="n">
-        <v>2906.838043117208</v>
+        <v>2197.513254430934</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>51302</v>
+        <v>50722</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>51303</v>
+        <v>50724.99999992725</v>
       </c>
       <c r="B144" t="n">
-        <v>4482.402297961162</v>
+        <v>8528.383512543847</v>
       </c>
       <c r="C144" t="n">
-        <v>1993.749598666359</v>
+        <v>1809.368534275456</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>51303</v>
+        <v>50724</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>51332.99999977433</v>
+        <v>50725</v>
       </c>
       <c r="B145" t="n">
-        <v>7094.944445968797</v>
+        <v>7216.362046096285</v>
       </c>
       <c r="C145" t="n">
-        <v>2863.615621671772</v>
+        <v>2213.359127385695</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>51332</v>
+        <v>50725</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>51334.00000001297</v>
+        <v>50740.91438029714</v>
       </c>
       <c r="B146" t="n">
-        <v>7094.636431274392</v>
+        <v>8420.998416839837</v>
       </c>
       <c r="C146" t="n">
-        <v>2862.254079842318</v>
+        <v>1859.526083568553</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>51334</v>
+        <v>50740</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>51363.99999955993</v>
+        <v>50754.99999999983</v>
       </c>
       <c r="B147" t="n">
-        <v>5911.622384470073</v>
+        <v>7120.708598626936</v>
       </c>
       <c r="C147" t="n">
-        <v>1819.916866058876</v>
+        <v>2358.281446849489</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>51363</v>
+        <v>50754</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>51364</v>
+        <v>50755</v>
       </c>
       <c r="B148" t="n">
-        <v>4465.214398931872</v>
+        <v>6868.375544458291</v>
       </c>
       <c r="C148" t="n">
-        <v>1733.667913607321</v>
+        <v>2244.443039589367</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>51364</v>
+        <v>50755</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>51382.48178085611</v>
+        <v>50756.00000107639</v>
       </c>
       <c r="B149" t="n">
-        <v>3893.471959826318</v>
+        <v>8450.061692567881</v>
       </c>
       <c r="C149" t="n">
-        <v>1900.715527992519</v>
+        <v>1878.852391323249</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>51382</v>
+        <v>50756</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>51394.99999919424</v>
+        <v>50773.20048256962</v>
       </c>
       <c r="B150" t="n">
-        <v>5430.201724213552</v>
+        <v>6801.649524793109</v>
       </c>
       <c r="C150" t="n">
-        <v>1824.395794517174</v>
+        <v>2249.03626078746</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>51394</v>
+        <v>50773</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>51406.62837305725</v>
+        <v>50781.64233981581</v>
       </c>
       <c r="B151" t="n">
-        <v>8673.523402327844</v>
+        <v>11647.03276362336</v>
       </c>
       <c r="C151" t="n">
-        <v>1912.886113091268</v>
+        <v>2587.742660506581</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>51406</v>
+        <v>50781</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>51424.99999995252</v>
+        <v>50785.99999999998</v>
       </c>
       <c r="B152" t="n">
-        <v>4925.629969372643</v>
+        <v>6423.328891556714</v>
       </c>
       <c r="C152" t="n">
-        <v>1794.353813492281</v>
+        <v>2339.467481898279</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>51424</v>
+        <v>50785</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>51425</v>
+        <v>50786</v>
       </c>
       <c r="B153" t="n">
-        <v>4838.401851720791</v>
+        <v>14909.16940169667</v>
       </c>
       <c r="C153" t="n">
-        <v>1497.051854036048</v>
+        <v>2358.458201597181</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>51425</v>
+        <v>50786</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>51448.5497201496</v>
+        <v>50787</v>
       </c>
       <c r="B154" t="n">
-        <v>4747.815848525037</v>
+        <v>7094.997010039257</v>
       </c>
       <c r="C154" t="n">
-        <v>1492.148476618927</v>
+        <v>2552.070140975617</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>51448</v>
+        <v>50787</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>51451.37025626643</v>
+        <v>50815.00000000462</v>
       </c>
       <c r="B155" t="n">
-        <v>6673.66417421671</v>
+        <v>8910.971937618671</v>
       </c>
       <c r="C155" t="n">
-        <v>3111.483151901069</v>
+        <v>1998.110807810896</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>51451</v>
+        <v>50815</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>51455.99999993191</v>
+        <v>50816.99986266054</v>
       </c>
       <c r="B156" t="n">
-        <v>4359.614289158751</v>
+        <v>14460.8194490106</v>
       </c>
       <c r="C156" t="n">
-        <v>1763.357256622755</v>
+        <v>2332.717166711212</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>51455</v>
+        <v>50816</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>51456.00000000023</v>
+        <v>50817</v>
       </c>
       <c r="B157" t="n">
-        <v>6815.264730643279</v>
+        <v>4325.631370845627</v>
       </c>
       <c r="C157" t="n">
-        <v>3104.127903474942</v>
+        <v>2308.635154570006</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -3423,151 +3423,151 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>51456</v>
+        <v>50817</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>51469.71754360322</v>
+        <v>50835.04666135355</v>
       </c>
       <c r="B158" t="n">
-        <v>4206.084386503846</v>
+        <v>4167.977572363327</v>
       </c>
       <c r="C158" t="n">
-        <v>1760.696471569028</v>
+        <v>2294.505975461052</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>51469</v>
+        <v>50835</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>51481.4991657808</v>
+        <v>50844.99997356415</v>
       </c>
       <c r="B159" t="n">
-        <v>4158.79451060994</v>
+        <v>12448.49467668997</v>
       </c>
       <c r="C159" t="n">
-        <v>2291.944157574213</v>
+        <v>2413.813922201385</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>51481</v>
+        <v>50844</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>51485.99999999764</v>
+        <v>50845</v>
       </c>
       <c r="B160" t="n">
-        <v>7775.376842015268</v>
+        <v>9159.166873856026</v>
       </c>
       <c r="C160" t="n">
-        <v>1820.303756623213</v>
+        <v>2496.139019515618</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>51485</v>
+        <v>50845</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>51487.00001134702</v>
+        <v>50853.08998982541</v>
       </c>
       <c r="B161" t="n">
-        <v>4402.253579838487</v>
+        <v>13625.64212755976</v>
       </c>
       <c r="C161" t="n">
-        <v>1794.078508457931</v>
+        <v>2607.479208896762</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>51487</v>
+        <v>50853</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>51494.79703281376</v>
+        <v>50857.24737504906</v>
       </c>
       <c r="B162" t="n">
-        <v>4328.987903602823</v>
+        <v>8920.45463557543</v>
       </c>
       <c r="C162" t="n">
-        <v>1433.875216269168</v>
+        <v>2488.307176646301</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>51494</v>
+        <v>50857</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>51518</v>
+        <v>50875.99999999998</v>
       </c>
       <c r="B163" t="n">
-        <v>4576.852752518196</v>
+        <v>3678.106718036061</v>
       </c>
       <c r="C163" t="n">
-        <v>1447.981894652621</v>
+        <v>2058.479935469316</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>51518</v>
+        <v>50875</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>51533.69269643682</v>
+        <v>50876</v>
       </c>
       <c r="B164" t="n">
-        <v>9091.995045373107</v>
+        <v>8492.148314168053</v>
       </c>
       <c r="C164" t="n">
-        <v>2497.99240773169</v>
+        <v>1761.84468458551</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>51533</v>
+        <v>50876</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>51546.00000000903</v>
+        <v>50905.99999999999</v>
       </c>
       <c r="B165" t="n">
-        <v>6118.997150021129</v>
+        <v>3055.610235271717</v>
       </c>
       <c r="C165" t="n">
-        <v>1673.359166696871</v>
+        <v>2127.739365076152</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -3575,56 +3575,56 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>51546</v>
+        <v>50905</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>51565.67127000008</v>
+        <v>50906</v>
       </c>
       <c r="B166" t="n">
-        <v>7687.808394090487</v>
+        <v>4358.456162985729</v>
       </c>
       <c r="C166" t="n">
-        <v>2987.847521297687</v>
+        <v>1797.95349274327</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>51565</v>
+        <v>50906</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>51577</v>
+        <v>50907.00000000004</v>
       </c>
       <c r="B167" t="n">
-        <v>6333.644871412651</v>
+        <v>10270.31016936162</v>
       </c>
       <c r="C167" t="n">
-        <v>2602.662485126461</v>
+        <v>2511.56563370522</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>51577</v>
+        <v>50907</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>51607.00000001583</v>
+        <v>50914.36543559227</v>
       </c>
       <c r="B168" t="n">
-        <v>11174.07466119963</v>
+        <v>2958.267430990622</v>
       </c>
       <c r="C168" t="n">
-        <v>1727.75762192567</v>
+        <v>2107.226474707514</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -3632,37 +3632,37 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>51607</v>
+        <v>50914</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>51637</v>
+        <v>50916.55651249287</v>
       </c>
       <c r="B169" t="n">
-        <v>13400.82492276121</v>
+        <v>8811.345255538041</v>
       </c>
       <c r="C169" t="n">
-        <v>1855.37059417736</v>
+        <v>3739.864962859613</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>51637</v>
+        <v>50916</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>51638.00000033309</v>
+        <v>50925.35648712025</v>
       </c>
       <c r="B170" t="n">
-        <v>14818.16816193844</v>
+        <v>3086.75257694494</v>
       </c>
       <c r="C170" t="n">
-        <v>2386.592059523776</v>
+        <v>2194.507348288722</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -3670,189 +3670,189 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>51638</v>
+        <v>50925</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>51668</v>
+        <v>50937</v>
       </c>
       <c r="B171" t="n">
-        <v>8595.854713828858</v>
+        <v>3067.572901237036</v>
       </c>
       <c r="C171" t="n">
-        <v>2269.847351243972</v>
+        <v>1849.279973934608</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>51668</v>
+        <v>50937</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>51676.488755925</v>
+        <v>50943.91832806184</v>
       </c>
       <c r="B172" t="n">
-        <v>8174.799290456387</v>
+        <v>3043.963355083282</v>
       </c>
       <c r="C172" t="n">
-        <v>2147.048345614171</v>
+        <v>1865.492957054876</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>51676</v>
+        <v>50943</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>51697.99999999622</v>
+        <v>50966.99999999999</v>
       </c>
       <c r="B173" t="n">
-        <v>12589.47391303317</v>
+        <v>10862.80331378875</v>
       </c>
       <c r="C173" t="n">
-        <v>1766.874580164999</v>
+        <v>1959.0920236014</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>51697</v>
+        <v>50966</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>51698</v>
+        <v>50967</v>
       </c>
       <c r="B174" t="n">
-        <v>13244.04560644157</v>
+        <v>15075.88493054071</v>
       </c>
       <c r="C174" t="n">
-        <v>1253.13956098957</v>
+        <v>1763.081728311062</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>51698</v>
+        <v>50967</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>51699.00000000001</v>
+        <v>50968.00000000001</v>
       </c>
       <c r="B175" t="n">
-        <v>8417.86957078581</v>
+        <v>3294.552202643603</v>
       </c>
       <c r="C175" t="n">
-        <v>2119.936475248867</v>
+        <v>1908.095096532966</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>51699</v>
+        <v>50968</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>51728.9999999887</v>
+        <v>50982.81575939839</v>
       </c>
       <c r="B176" t="n">
-        <v>10307.17498628802</v>
+        <v>10459.20506504065</v>
       </c>
       <c r="C176" t="n">
-        <v>1783.731604454192</v>
+        <v>1954.854080764504</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>51728</v>
+        <v>50982</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>51729</v>
+        <v>50997.99999999999</v>
       </c>
       <c r="B177" t="n">
-        <v>8386.667339931269</v>
+        <v>2217.618581364153</v>
       </c>
       <c r="C177" t="n">
-        <v>1694.371215488655</v>
+        <v>2096.524316736547</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>51729</v>
+        <v>50997</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>51730</v>
+        <v>50998</v>
       </c>
       <c r="B178" t="n">
-        <v>9603.091550642604</v>
+        <v>11340.20569343944</v>
       </c>
       <c r="C178" t="n">
-        <v>2255.459081668909</v>
+        <v>1750.155130281763</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>51730</v>
+        <v>50998</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>51747.04912506295</v>
+        <v>50999</v>
       </c>
       <c r="B179" t="n">
-        <v>11962.03353547625</v>
+        <v>4384.749504158795</v>
       </c>
       <c r="C179" t="n">
-        <v>2576.640101658458</v>
+        <v>1651.155113152701</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>51747</v>
+        <v>50999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>51759.99999997443</v>
+        <v>51011.29490094929</v>
       </c>
       <c r="B180" t="n">
-        <v>9149.5894193731</v>
+        <v>1970.306025961567</v>
       </c>
       <c r="C180" t="n">
-        <v>1820.616279033955</v>
+        <v>2147.985921787038</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -3860,360 +3860,360 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>51759</v>
+        <v>51011</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>51760</v>
+        <v>51016.44866665116</v>
       </c>
       <c r="B181" t="n">
-        <v>5217.781460159387</v>
+        <v>10279.90934366252</v>
       </c>
       <c r="C181" t="n">
-        <v>1740.323955440265</v>
+        <v>1924.78564765378</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>51760</v>
+        <v>51016</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>51761.83360240843</v>
+        <v>51028.48802084431</v>
       </c>
       <c r="B182" t="n">
-        <v>11955.48384887483</v>
+        <v>11366.03409128407</v>
       </c>
       <c r="C182" t="n">
-        <v>2647.033489853027</v>
+        <v>1805.289709263106</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>51761</v>
+        <v>51028</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>51774.36679331094</v>
+        <v>51029</v>
       </c>
       <c r="B183" t="n">
-        <v>4959.499203369423</v>
+        <v>2257.433812141382</v>
       </c>
       <c r="C183" t="n">
-        <v>1841.758754749442</v>
+        <v>2237.352871344337</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>51774</v>
+        <v>51029</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>51789.9999999272</v>
+        <v>51036.6098084323</v>
       </c>
       <c r="B184" t="n">
-        <v>8701.851897132716</v>
+        <v>9824.374555234284</v>
       </c>
       <c r="C184" t="n">
-        <v>1812.700041785187</v>
+        <v>1729.868919660621</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>51789</v>
+        <v>51036</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>51791</v>
+        <v>51044.19548305994</v>
       </c>
       <c r="B185" t="n">
-        <v>5109.841622116415</v>
+        <v>5677.693325051729</v>
       </c>
       <c r="C185" t="n">
-        <v>2060.588057001461</v>
+        <v>2344.783369377573</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>51791</v>
+        <v>51044</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>51820.99999998031</v>
+        <v>51058.99999999948</v>
       </c>
       <c r="B186" t="n">
-        <v>8632.435231159749</v>
+        <v>7663.33484616197</v>
       </c>
       <c r="C186" t="n">
-        <v>1928.327733718712</v>
+        <v>2052.915523865457</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>51820</v>
+        <v>51058</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>51821</v>
+        <v>51060</v>
       </c>
       <c r="B187" t="n">
-        <v>5555.719344187441</v>
+        <v>3544.412487819436</v>
       </c>
       <c r="C187" t="n">
-        <v>2359.423833415058</v>
+        <v>2645.08074555508</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>51821</v>
+        <v>51060</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>51836.25539311618</v>
+        <v>51069.10026137706</v>
       </c>
       <c r="B188" t="n">
-        <v>8101.327848764682</v>
+        <v>6730.406105958034</v>
       </c>
       <c r="C188" t="n">
-        <v>1795.13517768021</v>
+        <v>2707.987221254765</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>51836</v>
+        <v>51069</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>51848.44907215003</v>
+        <v>51090</v>
       </c>
       <c r="B189" t="n">
-        <v>17947.89344728675</v>
+        <v>5657.110791458814</v>
       </c>
       <c r="C189" t="n">
-        <v>2180.610321908989</v>
+        <v>2671.03893029319</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>51848</v>
+        <v>51090</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>51850.99999999569</v>
+        <v>51119.99999999999</v>
       </c>
       <c r="B190" t="n">
-        <v>8302.85283539742</v>
+        <v>12147.09815144838</v>
       </c>
       <c r="C190" t="n">
-        <v>1884.475366379848</v>
+        <v>1484.060331592765</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>51850</v>
+        <v>51119</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>51852.0000008671</v>
+        <v>51120</v>
       </c>
       <c r="B191" t="n">
-        <v>8172.299834228948</v>
+        <v>15894.42561479096</v>
       </c>
       <c r="C191" t="n">
-        <v>1793.203126330457</v>
+        <v>2849.469970664437</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>51852</v>
+        <v>51120</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>51881.9999991588</v>
+        <v>51121.00000123936</v>
       </c>
       <c r="B192" t="n">
-        <v>8184.561488697273</v>
+        <v>10601.52856780689</v>
       </c>
       <c r="C192" t="n">
-        <v>1954.711375936169</v>
+        <v>2255.959917207415</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>51881</v>
+        <v>51121</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>51883.00000000004</v>
+        <v>51127.23397537271</v>
       </c>
       <c r="B193" t="n">
-        <v>6801.565396357986</v>
+        <v>12071.0963142543</v>
       </c>
       <c r="C193" t="n">
-        <v>2696.224711731692</v>
+        <v>1515.439451014626</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>51883</v>
+        <v>51127</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>51911</v>
+        <v>51151</v>
       </c>
       <c r="B194" t="n">
-        <v>10690.08752622132</v>
+        <v>10071.22019405535</v>
       </c>
       <c r="C194" t="n">
-        <v>1346.469347817178</v>
+        <v>2023.289853973595</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>51911</v>
+        <v>51151</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>51912.99999995486</v>
+        <v>51152.00000018143</v>
       </c>
       <c r="B195" t="n">
-        <v>8170.110263856261</v>
+        <v>11154.48227417286</v>
       </c>
       <c r="C195" t="n">
-        <v>2107.502407154942</v>
+        <v>1876.041014803024</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>51912</v>
+        <v>51152</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>51913</v>
+        <v>51176.22100097346</v>
       </c>
       <c r="B196" t="n">
-        <v>9002.132336029576</v>
+        <v>14368.57004452504</v>
       </c>
       <c r="C196" t="n">
-        <v>2404.091572796985</v>
+        <v>1263.445915302427</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>51913</v>
+        <v>51176</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>51940.99999980901</v>
+        <v>51181.99999999999</v>
       </c>
       <c r="B197" t="n">
-        <v>7063.264596286135</v>
+        <v>7983.122407120793</v>
       </c>
       <c r="C197" t="n">
-        <v>1678.720672300867</v>
+        <v>1941.527793650004</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>51940</v>
+        <v>51181</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>51942</v>
+        <v>51182</v>
       </c>
       <c r="B198" t="n">
-        <v>12732.04175631553</v>
+        <v>10127.27244379687</v>
       </c>
       <c r="C198" t="n">
-        <v>1873.953440938902</v>
+        <v>2357.127955893218</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>51942</v>
+        <v>51182</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>51965.13376976662</v>
+        <v>51206.33342933965</v>
       </c>
       <c r="B199" t="n">
-        <v>8985.930435077384</v>
+        <v>5764.511135484176</v>
       </c>
       <c r="C199" t="n">
-        <v>2154.350767216609</v>
+        <v>1913.464708496148</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -4221,18 +4221,18 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>51965</v>
+        <v>51206</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>51971.99999999859</v>
+        <v>51210.99999997632</v>
       </c>
       <c r="B200" t="n">
-        <v>4245.040192377093</v>
+        <v>6838.981769905186</v>
       </c>
       <c r="C200" t="n">
-        <v>1562.305014415081</v>
+        <v>1715.41481908141</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -4240,425 +4240,2667 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>51971</v>
+        <v>51210</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>51972.00000000037</v>
+        <v>51211</v>
       </c>
       <c r="B201" t="n">
-        <v>8996.077598308617</v>
+        <v>8780.377093500894</v>
       </c>
       <c r="C201" t="n">
-        <v>2196.026308181693</v>
+        <v>2378.269517524567</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>51972</v>
+        <v>51211</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>51989.17544566212</v>
+        <v>51212</v>
       </c>
       <c r="B202" t="n">
-        <v>6602.746473415586</v>
+        <v>5841.571117616584</v>
       </c>
       <c r="C202" t="n">
-        <v>2367.993808065424</v>
+        <v>1914.51759334634</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>51989</v>
+        <v>51212</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>52001.99999999181</v>
+        <v>51213.35111040805</v>
       </c>
       <c r="B203" t="n">
-        <v>3474.088463728765</v>
+        <v>11688.32501834102</v>
       </c>
       <c r="C203" t="n">
-        <v>1582.239134339926</v>
+        <v>1873.63602175968</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>52001</v>
+        <v>51213</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>52026.86578701993</v>
+        <v>51215.02113948088</v>
       </c>
       <c r="B204" t="n">
-        <v>5318.997219292112</v>
+        <v>6834.030789400924</v>
       </c>
       <c r="C204" t="n">
-        <v>2613.025891260736</v>
+        <v>1730.046319127933</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VVE</t>
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>52026</v>
+        <v>51215</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>52030.35334999394</v>
+        <v>51241.99102712394</v>
       </c>
       <c r="B205" t="n">
-        <v>3281.63139456409</v>
+        <v>9766.086771061404</v>
       </c>
       <c r="C205" t="n">
-        <v>1616.374875243894</v>
+        <v>2243.619927175167</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>52030</v>
+        <v>51241</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>52032.99999999999</v>
+        <v>51242</v>
       </c>
       <c r="B206" t="n">
-        <v>6248.994217109315</v>
+        <v>6041.691181437269</v>
       </c>
       <c r="C206" t="n">
-        <v>2335.021897195306</v>
+        <v>2268.633503687928</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>52032</v>
+        <v>51242</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>52033.00000174226</v>
+        <v>51248.39172176265</v>
       </c>
       <c r="B207" t="n">
-        <v>5460.419012866729</v>
+        <v>9752.028605911204</v>
       </c>
       <c r="C207" t="n">
-        <v>2607.507344891367</v>
+        <v>2240.037192751804</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>52033</v>
+        <v>51248</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>52062.99999999998</v>
+        <v>51261.82603209325</v>
       </c>
       <c r="B208" t="n">
-        <v>2662.762400757572</v>
+        <v>12385.15641945054</v>
       </c>
       <c r="C208" t="n">
-        <v>1453.27603483726</v>
+        <v>2206.445323019127</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>52062</v>
+        <v>51261</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>52063</v>
+        <v>51271.99999999988</v>
       </c>
       <c r="B209" t="n">
-        <v>12157.68494198515</v>
+        <v>8999.343024112595</v>
       </c>
       <c r="C209" t="n">
-        <v>1669.099467127853</v>
+        <v>2767.170753541317</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>52063</v>
+        <v>51271</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>52064</v>
+        <v>51272</v>
       </c>
       <c r="B210" t="n">
-        <v>9589.910969484126</v>
+        <v>2601.660276859529</v>
       </c>
       <c r="C210" t="n">
-        <v>2594.16229788462</v>
+        <v>3171.606676100217</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>52064</v>
+        <v>51272</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>52079.21925268078</v>
+        <v>51273.00000000001</v>
       </c>
       <c r="B211" t="n">
-        <v>2982.346290770933</v>
+        <v>12482.23503425442</v>
       </c>
       <c r="C211" t="n">
-        <v>1521.374395463072</v>
+        <v>2195.606203139389</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>52079</v>
+        <v>51273</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>52091.61032021913</v>
+        <v>51277.35747296921</v>
       </c>
       <c r="B212" t="n">
-        <v>5327.966029084346</v>
+        <v>7734.609112737289</v>
       </c>
       <c r="C212" t="n">
-        <v>2263.091849961549</v>
+        <v>2206.625097696483</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VVEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>52091</v>
+        <v>51277</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>52094</v>
+        <v>51280.25075181427</v>
       </c>
       <c r="B213" t="n">
-        <v>7060.364129485844</v>
+        <v>2599.083016588973</v>
       </c>
       <c r="C213" t="n">
-        <v>1690.777989434964</v>
+        <v>2932.082562040456</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>52094</v>
+        <v>51280</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>52095.00000000001</v>
+        <v>51291.31523088403</v>
       </c>
       <c r="B214" t="n">
-        <v>2754.266213292111</v>
+        <v>6085.499301724671</v>
       </c>
       <c r="C214" t="n">
-        <v>1394.445712241474</v>
+        <v>2056.691656881615</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>52095</v>
+        <v>51291</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>52125</v>
+        <v>51296.29163049991</v>
       </c>
       <c r="B215" t="n">
-        <v>4251.892339816433</v>
+        <v>10196.80320665508</v>
       </c>
       <c r="C215" t="n">
-        <v>1722.473549711632</v>
+        <v>2133.190763997608</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VEVE</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>52125</v>
+        <v>51296</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>52147.38634700987</v>
+        <v>51297.6406234313</v>
       </c>
       <c r="B216" t="n">
-        <v>2876.125446409285</v>
+        <v>4437.260464211735</v>
       </c>
       <c r="C216" t="n">
-        <v>1420.691732440396</v>
+        <v>1903.770259245576</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>52147</v>
+        <v>51297</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>52148.851923403</v>
+        <v>51302.99999999972</v>
       </c>
       <c r="B217" t="n">
-        <v>3797.821856234557</v>
+        <v>7745.327282133348</v>
       </c>
       <c r="C217" t="n">
-        <v>1728.052982365612</v>
+        <v>2906.838043117208</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>52148</v>
+        <v>51302</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>52156.00000000002</v>
+        <v>51303</v>
       </c>
       <c r="B218" t="n">
-        <v>2984.841193517434</v>
+        <v>2815.564844062854</v>
       </c>
       <c r="C218" t="n">
-        <v>1356.671507069931</v>
+        <v>2854.453825243724</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VVE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>52156</v>
+        <v>51303</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>52185.99999999988</v>
+        <v>51317.61762397609</v>
       </c>
       <c r="B219" t="n">
-        <v>13974.2104387975</v>
+        <v>8211.836128429884</v>
       </c>
       <c r="C219" t="n">
-        <v>1708.923615653014</v>
+        <v>1655.761470204968</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VEM</t>
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>52185</v>
+        <v>51317</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>52186</v>
+        <v>51332.99999977433</v>
       </c>
       <c r="B220" t="n">
-        <v>4871.403299368685</v>
+        <v>7094.944445968797</v>
       </c>
       <c r="C220" t="n">
-        <v>1744.167896890056</v>
+        <v>2863.615621671772</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>VVEE</t>
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>52186</v>
+        <v>51332</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>52201.13293847386</v>
+        <v>51334</v>
       </c>
       <c r="B221" t="n">
-        <v>13765.57767700441</v>
+        <v>4753.552564422771</v>
       </c>
       <c r="C221" t="n">
-        <v>1733.507453040056</v>
+        <v>2680.104467818155</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>52201</v>
+        <v>51334</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
+        <v>51351.88728898609</v>
+      </c>
+      <c r="B222" t="n">
+        <v>18469.50978507407</v>
+      </c>
+      <c r="C222" t="n">
+        <v>2109.481609855894</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>51351</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>51363.99999955993</v>
+      </c>
+      <c r="B223" t="n">
+        <v>5911.622384470073</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1819.916866058876</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>51363</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>51364</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4465.214398931872</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1733.667913607321</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>51364</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>51365.00000000002</v>
+      </c>
+      <c r="B225" t="n">
+        <v>14716.86750165837</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2702.968288957566</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>51365</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>51378.91951601095</v>
+      </c>
+      <c r="B226" t="n">
+        <v>7769.805440065897</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3301.618738034895</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>51378</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>51382.48178085611</v>
+      </c>
+      <c r="B227" t="n">
+        <v>3893.471959826318</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1900.715527992519</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>51382</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>51394.99999919424</v>
+      </c>
+      <c r="B228" t="n">
+        <v>5430.201724213552</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1824.395794517174</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>51394</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>51395</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8584.487311778679</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3584.647579346285</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>51395</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>51406.62837305725</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8673.523402327844</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1912.886113091268</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>51406</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>51424.99999995252</v>
+      </c>
+      <c r="B231" t="n">
+        <v>4925.629969372643</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1794.353813492281</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>51424</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>51425</v>
+      </c>
+      <c r="B232" t="n">
+        <v>4838.401851720791</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1497.051854036048</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>51425</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>51426</v>
+      </c>
+      <c r="B233" t="n">
+        <v>11546.67024959516</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3545.449090420582</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>51426</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>51448.5497201496</v>
+      </c>
+      <c r="B234" t="n">
+        <v>4747.815848525037</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1492.148476618927</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>51448</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>51451.37025626643</v>
+      </c>
+      <c r="B235" t="n">
+        <v>6673.66417421671</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3111.483151901069</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>51451</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>51455.99999993191</v>
+      </c>
+      <c r="B236" t="n">
+        <v>4359.614289158751</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1763.357256622755</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>51455</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>51456</v>
+      </c>
+      <c r="B237" t="n">
+        <v>5822.000010425669</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2249.061458277022</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>51456</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>51469.71754360322</v>
+      </c>
+      <c r="B238" t="n">
+        <v>4206.084386503846</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1760.696471569028</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>51469</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>51479.87413845906</v>
+      </c>
+      <c r="B239" t="n">
+        <v>16120.66824325093</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1881.662878942747</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>51479</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>51481.4991657808</v>
+      </c>
+      <c r="B240" t="n">
+        <v>4158.79451060994</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2291.944157574213</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>51481</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>51485.99999999764</v>
+      </c>
+      <c r="B241" t="n">
+        <v>7775.376842015268</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1820.303756623213</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>51485</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>51486</v>
+      </c>
+      <c r="B242" t="n">
+        <v>5414.696178860857</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2332.730057271642</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>51486</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>51487.00001134702</v>
+      </c>
+      <c r="B243" t="n">
+        <v>4402.253579838487</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1794.078508457931</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>51487</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>51490.52429342313</v>
+      </c>
+      <c r="B244" t="n">
+        <v>5407.099408225691</v>
+      </c>
+      <c r="C244" t="n">
+        <v>2370.235274319738</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>51490</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>51494.79703281376</v>
+      </c>
+      <c r="B245" t="n">
+        <v>4328.987903602823</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1433.875216269168</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>51494</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>51517</v>
+      </c>
+      <c r="B246" t="n">
+        <v>12921.62349544533</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3295.183493182617</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>51517</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>51518</v>
+      </c>
+      <c r="B247" t="n">
+        <v>4576.852752518196</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1447.981894652621</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>51518</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>51521.30134719607</v>
+      </c>
+      <c r="B248" t="n">
+        <v>5444.199735946797</v>
+      </c>
+      <c r="C248" t="n">
+        <v>2395.423306729977</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>51521</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>51533.69269643682</v>
+      </c>
+      <c r="B249" t="n">
+        <v>9091.995045373107</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2497.99240773169</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>51533</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>51539.08571754518</v>
+      </c>
+      <c r="B250" t="n">
+        <v>11822.14732327884</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3432.886231132477</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>51539</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>51546</v>
+      </c>
+      <c r="B251" t="n">
+        <v>5877.041605395849</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2453.062532695331</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>51546</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>51548</v>
+      </c>
+      <c r="B252" t="n">
+        <v>18077.09117576174</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1884.920895282944</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>51548</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>51549.21221250146</v>
+      </c>
+      <c r="B253" t="n">
+        <v>21574.68955744587</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1866.915402109033</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>51549</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>51565.67127000008</v>
+      </c>
+      <c r="B254" t="n">
+        <v>7687.808394090487</v>
+      </c>
+      <c r="C254" t="n">
+        <v>2987.847521297687</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>51565</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>51575.99999245147</v>
+      </c>
+      <c r="B255" t="n">
+        <v>13399.10763094579</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2273.468358554657</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>51575</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>51576</v>
+      </c>
+      <c r="B256" t="n">
+        <v>11352.53259835045</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3364.057777531623</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>51576</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>51577</v>
+      </c>
+      <c r="B257" t="n">
+        <v>6333.644871412651</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2602.662485126461</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>51577</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>51591.52047528767</v>
+      </c>
+      <c r="B258" t="n">
+        <v>10386.03364038973</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3444.94307444368</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>51591</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>51606.99999999999</v>
+      </c>
+      <c r="B259" t="n">
+        <v>10394.95244401122</v>
+      </c>
+      <c r="C259" t="n">
+        <v>2247.894433727507</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>51606</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>51607</v>
+      </c>
+      <c r="B260" t="n">
+        <v>10097.88598663628</v>
+      </c>
+      <c r="C260" t="n">
+        <v>2575.862294567002</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>51607</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>51636.99986125867</v>
+      </c>
+      <c r="B261" t="n">
+        <v>8989.567110167352</v>
+      </c>
+      <c r="C261" t="n">
+        <v>2263.96563027715</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>51636</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>51637</v>
+      </c>
+      <c r="B262" t="n">
+        <v>10232.17735575574</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3202.722077590188</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>51637</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>51638</v>
+      </c>
+      <c r="B263" t="n">
+        <v>14363.63060904171</v>
+      </c>
+      <c r="C263" t="n">
+        <v>2539.121671122115</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>51638</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>51664.19557300543</v>
+      </c>
+      <c r="B264" t="n">
+        <v>25533.10120873276</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1393.375761225942</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>51664</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>51667.99999999996</v>
+      </c>
+      <c r="B265" t="n">
+        <v>8215.160664647279</v>
+      </c>
+      <c r="C265" t="n">
+        <v>2204.619245117839</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>51667</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>51668</v>
+      </c>
+      <c r="B266" t="n">
+        <v>8595.854713828858</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2269.847351243972</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>51668</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>51676.488755925</v>
+      </c>
+      <c r="B267" t="n">
+        <v>8174.799290456387</v>
+      </c>
+      <c r="C267" t="n">
+        <v>2147.048345614171</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>51676</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>51697.9999748144</v>
+      </c>
+      <c r="B268" t="n">
+        <v>7604.41705569901</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2186.378629895595</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>51697</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>51698</v>
+      </c>
+      <c r="B269" t="n">
+        <v>8127.741603443928</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3542.415954714727</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>51698</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>51699.00000000001</v>
+      </c>
+      <c r="B270" t="n">
+        <v>8417.86957078581</v>
+      </c>
+      <c r="C270" t="n">
+        <v>2119.936475248867</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>51699</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>51702.6842051933</v>
+      </c>
+      <c r="B271" t="n">
+        <v>8097.109700921948</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3559.990749476544</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>51702</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>51715.03670010348</v>
+      </c>
+      <c r="B272" t="n">
+        <v>7303.642344142248</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2202.968728444823</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>51715</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>51728.9999999887</v>
+      </c>
+      <c r="B273" t="n">
+        <v>10307.17498628802</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1783.731604454192</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>51728</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>51729</v>
+      </c>
+      <c r="B274" t="n">
+        <v>8386.667339931269</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1694.371215488655</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>51729</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>51730</v>
+      </c>
+      <c r="B275" t="n">
+        <v>9603.091550642604</v>
+      </c>
+      <c r="C275" t="n">
+        <v>2255.459081668909</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>51730</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>51747.04912506295</v>
+      </c>
+      <c r="B276" t="n">
+        <v>11962.03353547625</v>
+      </c>
+      <c r="C276" t="n">
+        <v>2576.640101658458</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>51747</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>51759.99999999757</v>
+      </c>
+      <c r="B277" t="n">
+        <v>5716.476746838031</v>
+      </c>
+      <c r="C277" t="n">
+        <v>2224.700584390396</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>51759</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>51760</v>
+      </c>
+      <c r="B278" t="n">
+        <v>5217.781460159387</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1740.323955440265</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>51760</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>51761.83360240843</v>
+      </c>
+      <c r="B279" t="n">
+        <v>11955.48384887483</v>
+      </c>
+      <c r="C279" t="n">
+        <v>2647.033489853027</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>51761</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>51774.36679331094</v>
+      </c>
+      <c r="B280" t="n">
+        <v>4959.499203369423</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1841.758754749442</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>51774</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>51789.99895006714</v>
+      </c>
+      <c r="B281" t="n">
+        <v>4547.39892520634</v>
+      </c>
+      <c r="C281" t="n">
+        <v>2201.102499032465</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>51789</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>51790</v>
+      </c>
+      <c r="B282" t="n">
+        <v>11271.01691984918</v>
+      </c>
+      <c r="C282" t="n">
+        <v>2350.869783310839</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>51790</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>51791</v>
+      </c>
+      <c r="B283" t="n">
+        <v>5109.841622116415</v>
+      </c>
+      <c r="C283" t="n">
+        <v>2060.588057001461</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>51791</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>51796.07865963881</v>
+      </c>
+      <c r="B284" t="n">
+        <v>4524.206168178356</v>
+      </c>
+      <c r="C284" t="n">
+        <v>2213.805365949047</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>51796</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>51797.12499409592</v>
+      </c>
+      <c r="B285" t="n">
+        <v>5465.910084444233</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3634.09350280746</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>51797</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>51805.77432087082</v>
+      </c>
+      <c r="B286" t="n">
+        <v>12780.48604355373</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1689.098216706155</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>51805</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>51820.99999998031</v>
+      </c>
+      <c r="B287" t="n">
+        <v>8632.435231159749</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1928.327733718712</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="n">
+        <v>51820</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>51821</v>
+      </c>
+      <c r="B288" t="n">
+        <v>5555.719344187441</v>
+      </c>
+      <c r="C288" t="n">
+        <v>2359.423833415058</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>51821</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>51836.25539311618</v>
+      </c>
+      <c r="B289" t="n">
+        <v>8101.327848764682</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1795.13517768021</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="n">
+        <v>51836</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>51848.44907215003</v>
+      </c>
+      <c r="B290" t="n">
+        <v>17947.89344728675</v>
+      </c>
+      <c r="C290" t="n">
+        <v>2180.610321908989</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>51848</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>51850.99972479569</v>
+      </c>
+      <c r="B291" t="n">
+        <v>3972.360334575977</v>
+      </c>
+      <c r="C291" t="n">
+        <v>2141.310410513387</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="n">
+        <v>51850</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>51851</v>
+      </c>
+      <c r="B292" t="n">
+        <v>6842.750690750559</v>
+      </c>
+      <c r="C292" t="n">
+        <v>2552.566152004241</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>51851</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>51852</v>
+      </c>
+      <c r="B293" t="n">
+        <v>7698.062642626388</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3579.218496903391</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>51852</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>51866.79759349514</v>
+      </c>
+      <c r="B294" t="n">
+        <v>3803.622531928977</v>
+      </c>
+      <c r="C294" t="n">
+        <v>2143.183341271359</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>51866</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>51881.9999991588</v>
+      </c>
+      <c r="B295" t="n">
+        <v>8184.561488697273</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1954.711375936169</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>51881</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>51882</v>
+      </c>
+      <c r="B296" t="n">
+        <v>6185.420396398909</v>
+      </c>
+      <c r="C296" t="n">
+        <v>2528.248761836068</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>51882</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>51883.00000000004</v>
+      </c>
+      <c r="B297" t="n">
+        <v>6801.565396357986</v>
+      </c>
+      <c r="C297" t="n">
+        <v>2696.224711731692</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>51883</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>51899.71685866588</v>
+      </c>
+      <c r="B298" t="n">
+        <v>5989.488543142304</v>
+      </c>
+      <c r="C298" t="n">
+        <v>2520.376381939104</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>51899</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>51911</v>
+      </c>
+      <c r="B299" t="n">
+        <v>10690.08752622132</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1346.469347817178</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>51911</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>51912.99999995486</v>
+      </c>
+      <c r="B300" t="n">
+        <v>8170.110263856261</v>
+      </c>
+      <c r="C300" t="n">
+        <v>2107.502407154942</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>51912</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>51913</v>
+      </c>
+      <c r="B301" t="n">
+        <v>9002.132336029576</v>
+      </c>
+      <c r="C301" t="n">
+        <v>2404.091572796985</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>51913</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>51940.99999980901</v>
+      </c>
+      <c r="B302" t="n">
+        <v>7063.264596286135</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1678.720672300867</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>51940</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>51941</v>
+      </c>
+      <c r="B303" t="n">
+        <v>5373.235704849303</v>
+      </c>
+      <c r="C303" t="n">
+        <v>2473.511929624603</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>51941</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>51942</v>
+      </c>
+      <c r="B304" t="n">
+        <v>12732.04175631553</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1873.953440938902</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>51942</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>51965.13376976662</v>
+      </c>
+      <c r="B305" t="n">
+        <v>8985.930435077384</v>
+      </c>
+      <c r="C305" t="n">
+        <v>2154.350767216609</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>51965</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>51971.99999999859</v>
+      </c>
+      <c r="B306" t="n">
+        <v>4245.040192377093</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1562.305014415081</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>51971</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>51972</v>
+      </c>
+      <c r="B307" t="n">
+        <v>7739.445312199165</v>
+      </c>
+      <c r="C307" t="n">
+        <v>2168.45997946273</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>51972</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>51989.17544566212</v>
+      </c>
+      <c r="B308" t="n">
+        <v>6602.746473415586</v>
+      </c>
+      <c r="C308" t="n">
+        <v>2367.993808065424</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>51989</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>51994.38625412218</v>
+      </c>
+      <c r="B309" t="n">
+        <v>4992.466793653097</v>
+      </c>
+      <c r="C309" t="n">
+        <v>2424.783795268588</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>51994</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>52001.99999999181</v>
+      </c>
+      <c r="B310" t="n">
+        <v>3474.088463728765</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1582.239134339926</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>52001</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>52002</v>
+      </c>
+      <c r="B311" t="n">
+        <v>3289.571583665798</v>
+      </c>
+      <c r="C311" t="n">
+        <v>2202.135218271899</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>52002</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>52003.00000000004</v>
+      </c>
+      <c r="B312" t="n">
+        <v>5040.882868877396</v>
+      </c>
+      <c r="C312" t="n">
+        <v>2425.66271161978</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>52003</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>52025.43051316826</v>
+      </c>
+      <c r="B313" t="n">
+        <v>2783.301557998426</v>
+      </c>
+      <c r="C313" t="n">
+        <v>2184.564327743805</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>52025</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>52026.86578701993</v>
+      </c>
+      <c r="B314" t="n">
+        <v>5318.997219292112</v>
+      </c>
+      <c r="C314" t="n">
+        <v>2613.025891260736</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>52026</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>52030.35334999394</v>
+      </c>
+      <c r="B315" t="n">
+        <v>3281.63139456409</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1616.374875243894</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>52030</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>52032.99999999916</v>
+      </c>
+      <c r="B316" t="n">
+        <v>3847.069025827001</v>
+      </c>
+      <c r="C316" t="n">
+        <v>2911.720235282479</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>52032</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>52033</v>
+      </c>
+      <c r="B317" t="n">
+        <v>2825.003311116907</v>
+      </c>
+      <c r="C317" t="n">
+        <v>2176.979348775942</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>52033</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>52062.99999999998</v>
+      </c>
+      <c r="B318" t="n">
+        <v>2662.762400757572</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1453.27603483726</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>52062</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>52063</v>
+      </c>
+      <c r="B319" t="n">
+        <v>2455.416252575186</v>
+      </c>
+      <c r="C319" t="n">
+        <v>2869.264675350634</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>52063</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>52064</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3794.561976336801</v>
+      </c>
+      <c r="C320" t="n">
+        <v>2133.425325952671</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>52064</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>52067.29188878855</v>
+      </c>
+      <c r="B321" t="n">
+        <v>2416.243506723013</v>
+      </c>
+      <c r="C321" t="n">
+        <v>2928.517051613646</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>52067</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>52069.73104144946</v>
+      </c>
+      <c r="B322" t="n">
+        <v>7943.943713332195</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1915.045941437424</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>52069</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>52079.21925268078</v>
+      </c>
+      <c r="B323" t="n">
+        <v>2982.346290770933</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1521.374395463072</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>52079</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>52091.61032021913</v>
+      </c>
+      <c r="B324" t="n">
+        <v>5327.966029084346</v>
+      </c>
+      <c r="C324" t="n">
+        <v>2263.091849961549</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>52091</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>52093.99686291981</v>
+      </c>
+      <c r="B325" t="n">
+        <v>11275.54349692673</v>
+      </c>
+      <c r="C325" t="n">
+        <v>2499.331627818516</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>52093</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>52094</v>
+      </c>
+      <c r="B326" t="n">
+        <v>7060.364129485844</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1690.777989434964</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>52094</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>52095.00000000001</v>
+      </c>
+      <c r="B327" t="n">
+        <v>2754.266213292111</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1394.445712241474</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>52095</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>52115.47522402013</v>
+      </c>
+      <c r="B328" t="n">
+        <v>8275.473622972708</v>
+      </c>
+      <c r="C328" t="n">
+        <v>2100.343262655757</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>52115</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>52124.99999474423</v>
+      </c>
+      <c r="B329" t="n">
+        <v>9753.985414825853</v>
+      </c>
+      <c r="C329" t="n">
+        <v>2350.485880990207</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>52124</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>52125</v>
+      </c>
+      <c r="B330" t="n">
+        <v>4251.892339816433</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1722.473549711632</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>52125</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>52147.38634700987</v>
+      </c>
+      <c r="B331" t="n">
+        <v>2876.125446409285</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1420.691732440396</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>52147</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>52148.851923403</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3797.821856234557</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1728.052982365612</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>52148</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>52154.99832615253</v>
+      </c>
+      <c r="B333" t="n">
+        <v>8607.761795308599</v>
+      </c>
+      <c r="C333" t="n">
+        <v>2345.593773202741</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>52154</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>52156.00000000002</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2984.841193517434</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1356.671507069931</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>52156</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>52185.99999999993</v>
+      </c>
+      <c r="B335" t="n">
+        <v>6608.496771560163</v>
+      </c>
+      <c r="C335" t="n">
+        <v>2507.344710872978</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>52185</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>52186</v>
+      </c>
+      <c r="B336" t="n">
+        <v>4871.403299368685</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1744.167896890056</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>52186</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>52201.13293847386</v>
+      </c>
+      <c r="B337" t="n">
+        <v>13765.57767700441</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1733.507453040056</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>52201</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
         <v>52213.06879616943</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B338" t="n">
         <v>2398.934475802898</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C338" t="n">
         <v>2120.004128953637</v>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>VVE</t>
         </is>
       </c>
-      <c r="E222" s="3" t="n">
+      <c r="E338" s="3" t="n">
         <v>52213</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>52215.99999999992</v>
+      </c>
+      <c r="B339" t="n">
+        <v>4938.016100868139</v>
+      </c>
+      <c r="C339" t="n">
+        <v>2561.154957769438</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>52215</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>52216</v>
+      </c>
+      <c r="B340" t="n">
+        <v>20564.94978652876</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1226.661409043693</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>52216</v>
       </c>
     </row>
   </sheetData>

--- a/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
+++ b/GoingToJupiter/minimum_delta_v_trajectory_by_date.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Arrival date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Launch day</t>
         </is>
       </c>
@@ -477,7 +482,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="2" t="n">
+        <v>52209.1971734619</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>49660</v>
       </c>
     </row>
@@ -496,7 +504,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
+        <v>51837.54554149168</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>49689</v>
       </c>
     </row>
@@ -515,7 +526,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="2" t="n">
+        <v>51260.90393569593</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>49690</v>
       </c>
     </row>
@@ -534,7 +548,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
+        <v>52238.67665626743</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>49691</v>
       </c>
     </row>
@@ -553,7 +570,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="2" t="n">
+        <v>51916.93504530655</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>49710</v>
       </c>
     </row>
@@ -572,7 +592,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="2" t="n">
+        <v>52139.69472899658</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>49720</v>
       </c>
     </row>
@@ -591,7 +614,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="2" t="n">
+        <v>51565.14874740048</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>49721</v>
       </c>
     </row>
@@ -610,7 +636,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="2" t="n">
+        <v>52527.58249353885</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>49723</v>
       </c>
     </row>
@@ -629,7 +658,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="2" t="n">
+        <v>51896.66255552354</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>49731</v>
       </c>
     </row>
@@ -648,7 +680,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="2" t="n">
+        <v>51258.79112674057</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>49744</v>
       </c>
     </row>
@@ -667,7 +702,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="2" t="n">
+        <v>52171.17702067216</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>49749</v>
       </c>
     </row>
@@ -686,7 +724,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="2" t="n">
+        <v>51898.3554988231</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>49751</v>
       </c>
     </row>
@@ -705,7 +746,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="2" t="n">
+        <v>51771.30096554862</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>49757</v>
       </c>
     </row>
@@ -724,7 +768,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="2" t="n">
+        <v>52170.57912784041</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>49761</v>
       </c>
     </row>
@@ -743,7 +790,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="2" t="n">
+        <v>52574.53443611972</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>49766</v>
       </c>
     </row>
@@ -762,7 +812,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="2" t="n">
+        <v>51973.45748215986</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>49780</v>
       </c>
     </row>
@@ -781,7 +834,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="2" t="n">
+        <v>52162.87425132065</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>49781</v>
       </c>
     </row>
@@ -800,7 +856,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="2" t="n">
+        <v>51961.85662283742</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>49810</v>
       </c>
     </row>
@@ -819,7 +878,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="2" t="n">
+        <v>52003.15103620893</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>49811</v>
       </c>
     </row>
@@ -838,7 +900,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="2" t="n">
+        <v>51694.65767200937</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>49812</v>
       </c>
     </row>
@@ -857,7 +922,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="2" t="n">
+        <v>52064.13971491053</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>49813</v>
       </c>
     </row>
@@ -876,7 +944,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="2" t="n">
+        <v>53290.39524499442</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>49821</v>
       </c>
     </row>
@@ -895,7 +966,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="2" t="n">
+        <v>52072.96578986883</v>
+      </c>
+      <c r="F24" s="3" t="n">
         <v>49825</v>
       </c>
     </row>
@@ -914,7 +988,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="2" t="n">
+        <v>52099.49521635932</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>49839</v>
       </c>
     </row>
@@ -933,7 +1010,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="2" t="n">
+        <v>51551.61166641294</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>49841</v>
       </c>
     </row>
@@ -952,7 +1032,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="2" t="n">
+        <v>52110.73415453134</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>49842</v>
       </c>
     </row>
@@ -971,7 +1054,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="2" t="n">
+        <v>52039.97701573808</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>49853</v>
       </c>
     </row>
@@ -990,7 +1076,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="2" t="n">
+        <v>51574.94121895558</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>49872</v>
       </c>
     </row>
@@ -1009,7 +1098,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="2" t="n">
+        <v>52569.11557555058</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>49873</v>
       </c>
     </row>
@@ -1028,7 +1120,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="2" t="n">
+        <v>51773.68017809582</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>49891</v>
       </c>
     </row>
@@ -1047,7 +1142,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="2" t="n">
+        <v>52181.24110779043</v>
+      </c>
+      <c r="F32" s="3" t="n">
         <v>49902</v>
       </c>
     </row>
@@ -1066,7 +1164,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="2" t="n">
+        <v>53277.72389907633</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>49903</v>
       </c>
     </row>
@@ -1085,7 +1186,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="2" t="n">
+        <v>52563.15920949299</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>49904</v>
       </c>
     </row>
@@ -1104,7 +1208,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="2" t="n">
+        <v>52203.15786010838</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>49914</v>
       </c>
     </row>
@@ -1123,7 +1230,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="2" t="n">
+        <v>52155.32301130248</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>49934</v>
       </c>
     </row>
@@ -1142,7 +1252,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="2" t="n">
+        <v>52546.38602058694</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>49964</v>
       </c>
     </row>
@@ -1161,7 +1274,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="2" t="n">
+        <v>51897.61781642488</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>49965</v>
       </c>
     </row>
@@ -1180,7 +1296,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="2" t="n">
+        <v>52167.44536459792</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>49994</v>
       </c>
     </row>
@@ -1199,7 +1318,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="2" t="n">
+        <v>52527.59265740444</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>49995</v>
       </c>
     </row>
@@ -1218,7 +1340,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="2" t="n">
+        <v>52177.44010003767</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>50002</v>
       </c>
     </row>
@@ -1237,7 +1362,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="2" t="n">
+        <v>51880.97083236868</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>50005</v>
       </c>
     </row>
@@ -1256,7 +1384,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="2" t="n">
+        <v>52150.78261047802</v>
+      </c>
+      <c r="F43" s="3" t="n">
         <v>50015</v>
       </c>
     </row>
@@ -1275,7 +1406,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="2" t="n">
+        <v>52402.39144462728</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>50021</v>
       </c>
     </row>
@@ -1294,7 +1428,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="2" t="n">
+        <v>52226.5848112077</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>50023</v>
       </c>
     </row>
@@ -1313,7 +1450,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="2" t="n">
+        <v>52409.07991580077</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>50024</v>
       </c>
     </row>
@@ -1332,7 +1472,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="2" t="n">
+        <v>52404.2251071381</v>
+      </c>
+      <c r="F47" s="3" t="n">
         <v>50026</v>
       </c>
     </row>
@@ -1351,7 +1494,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="2" t="n">
+        <v>52421.63468275559</v>
+      </c>
+      <c r="F48" s="3" t="n">
         <v>50042</v>
       </c>
     </row>
@@ -1370,7 +1516,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="2" t="n">
+        <v>52234.41832523153</v>
+      </c>
+      <c r="F49" s="3" t="n">
         <v>50044</v>
       </c>
     </row>
@@ -1389,7 +1538,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="2" t="n">
+        <v>52119.0462454839</v>
+      </c>
+      <c r="F50" s="3" t="n">
         <v>50049</v>
       </c>
     </row>
@@ -1408,7 +1560,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="2" t="n">
+        <v>52622.34579426611</v>
+      </c>
+      <c r="F51" s="3" t="n">
         <v>50055</v>
       </c>
     </row>
@@ -1427,7 +1582,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="2" t="n">
+        <v>52266.14246376935</v>
+      </c>
+      <c r="F52" s="3" t="n">
         <v>50057</v>
       </c>
     </row>
@@ -1446,7 +1604,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="2" t="n">
+        <v>52364.9282354801</v>
+      </c>
+      <c r="F53" s="3" t="n">
         <v>50079</v>
       </c>
     </row>
@@ -1465,7 +1626,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="2" t="n">
+        <v>52999.53080662763</v>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>50086</v>
       </c>
     </row>
@@ -1484,7 +1648,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="2" t="n">
+        <v>52133.41998479626</v>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>50087</v>
       </c>
     </row>
@@ -1503,7 +1670,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="2" t="n">
+        <v>53862.95396243359</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>50093</v>
       </c>
     </row>
@@ -1522,7 +1692,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="2" t="n">
+        <v>52430.75749586045</v>
+      </c>
+      <c r="F57" s="3" t="n">
         <v>50103</v>
       </c>
     </row>
@@ -1541,7 +1714,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="2" t="n">
+        <v>52212.63064061462</v>
+      </c>
+      <c r="F58" s="3" t="n">
         <v>50110</v>
       </c>
     </row>
@@ -1560,7 +1736,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="2" t="n">
+        <v>52366.90335931102</v>
+      </c>
+      <c r="F59" s="3" t="n">
         <v>50114</v>
       </c>
     </row>
@@ -1579,7 +1758,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="2" t="n">
+        <v>52127.1949339057</v>
+      </c>
+      <c r="F60" s="3" t="n">
         <v>50115</v>
       </c>
     </row>
@@ -1598,7 +1780,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="2" t="n">
+        <v>52314.3723324821</v>
+      </c>
+      <c r="F61" s="3" t="n">
         <v>50116</v>
       </c>
     </row>
@@ -1617,7 +1802,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="2" t="n">
+        <v>52124.66166703793</v>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>50121</v>
       </c>
     </row>
@@ -1636,7 +1824,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="2" t="n">
+        <v>52370.67157603252</v>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>50126</v>
       </c>
     </row>
@@ -1655,7 +1846,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="2" t="n">
+        <v>52079.9027715272</v>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>50145</v>
       </c>
     </row>
@@ -1674,7 +1868,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="2" t="n">
+        <v>52486.21556835651</v>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>50146</v>
       </c>
     </row>
@@ -1693,7 +1890,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="2" t="n">
+        <v>52976.61236339779</v>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>50147</v>
       </c>
     </row>
@@ -1712,7 +1912,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="2" t="n">
+        <v>53862.11232564635</v>
+      </c>
+      <c r="F67" s="3" t="n">
         <v>50154</v>
       </c>
     </row>
@@ -1731,7 +1934,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="2" t="n">
+        <v>52117.76809529575</v>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>50175</v>
       </c>
     </row>
@@ -1750,7 +1956,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="2" t="n">
+        <v>51966.01084031045</v>
+      </c>
+      <c r="F69" s="3" t="n">
         <v>50176</v>
       </c>
     </row>
@@ -1769,7 +1978,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="2" t="n">
+        <v>52967.23979448689</v>
+      </c>
+      <c r="F70" s="3" t="n">
         <v>50177</v>
       </c>
     </row>
@@ -1788,7 +2000,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="2" t="n">
+        <v>52449.77337666508</v>
+      </c>
+      <c r="F71" s="3" t="n">
         <v>50206</v>
       </c>
     </row>
@@ -1807,7 +2022,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="2" t="n">
+        <v>52646.70138492192</v>
+      </c>
+      <c r="F72" s="3" t="n">
         <v>50207</v>
       </c>
     </row>
@@ -1826,7 +2044,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="2" t="n">
+        <v>52134.47943490245</v>
+      </c>
+      <c r="F73" s="3" t="n">
         <v>50209</v>
       </c>
     </row>
@@ -1845,7 +2066,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="2" t="n">
+        <v>52545.29514520297</v>
+      </c>
+      <c r="F74" s="3" t="n">
         <v>50236</v>
       </c>
     </row>
@@ -1864,7 +2088,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="2" t="n">
+        <v>52750.1357294554</v>
+      </c>
+      <c r="F75" s="3" t="n">
         <v>50237</v>
       </c>
     </row>
@@ -1883,7 +2110,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="2" t="n">
+        <v>52382.09973009708</v>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>50238</v>
       </c>
     </row>
@@ -1902,7 +2132,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="2" t="n">
+        <v>52209.61236434364</v>
+      </c>
+      <c r="F77" s="3" t="n">
         <v>50247</v>
       </c>
     </row>
@@ -1921,7 +2154,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="2" t="n">
+        <v>52051.7448940522</v>
+      </c>
+      <c r="F78" s="3" t="n">
         <v>50251</v>
       </c>
     </row>
@@ -1940,7 +2176,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="2" t="n">
+        <v>52590.37536817462</v>
+      </c>
+      <c r="F79" s="3" t="n">
         <v>50266</v>
       </c>
     </row>
@@ -1959,7 +2198,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="2" t="n">
+        <v>52767.18182547315</v>
+      </c>
+      <c r="F80" s="3" t="n">
         <v>50267</v>
       </c>
     </row>
@@ -1978,7 +2220,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="2" t="n">
+        <v>52842.58060007775</v>
+      </c>
+      <c r="F81" s="3" t="n">
         <v>50268</v>
       </c>
     </row>
@@ -1997,7 +2242,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="2" t="n">
+        <v>52574.07287710309</v>
+      </c>
+      <c r="F82" s="3" t="n">
         <v>50269</v>
       </c>
     </row>
@@ -2016,7 +2264,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="2" t="n">
+        <v>52861.34747226529</v>
+      </c>
+      <c r="F83" s="3" t="n">
         <v>50285</v>
       </c>
     </row>
@@ -2035,7 +2286,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="2" t="n">
+        <v>52872.84870674391</v>
+      </c>
+      <c r="F84" s="3" t="n">
         <v>50289</v>
       </c>
     </row>
@@ -2054,7 +2308,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="2" t="n">
+        <v>52803.47852136981</v>
+      </c>
+      <c r="F85" s="3" t="n">
         <v>50294</v>
       </c>
     </row>
@@ -2073,7 +2330,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="2" t="n">
+        <v>52562.21859103887</v>
+      </c>
+      <c r="F86" s="3" t="n">
         <v>50298</v>
       </c>
     </row>
@@ -2092,7 +2352,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="2" t="n">
+        <v>51992.77976571823</v>
+      </c>
+      <c r="F87" s="3" t="n">
         <v>50299</v>
       </c>
     </row>
@@ -2111,7 +2374,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="2" t="n">
+        <v>52000.3965753435</v>
+      </c>
+      <c r="F88" s="3" t="n">
         <v>50301</v>
       </c>
     </row>
@@ -2130,7 +2396,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="2" t="n">
+        <v>52559.27373151109</v>
+      </c>
+      <c r="F89" s="3" t="n">
         <v>50312</v>
       </c>
     </row>
@@ -2149,7 +2418,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="2" t="n">
+        <v>52861.26870766527</v>
+      </c>
+      <c r="F90" s="3" t="n">
         <v>50328</v>
       </c>
     </row>
@@ -2168,7 +2440,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="2" t="n">
+        <v>52599.40035548072</v>
+      </c>
+      <c r="F91" s="3" t="n">
         <v>50330</v>
       </c>
     </row>
@@ -2187,7 +2462,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="2" t="n">
+        <v>52064.60510522764</v>
+      </c>
+      <c r="F92" s="3" t="n">
         <v>50331</v>
       </c>
     </row>
@@ -2206,7 +2484,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n">
+      <c r="E93" s="2" t="n">
+        <v>52873.25602331909</v>
+      </c>
+      <c r="F93" s="3" t="n">
         <v>50346</v>
       </c>
     </row>
@@ -2225,7 +2506,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="2" t="n">
+        <v>52247.4621807503</v>
+      </c>
+      <c r="F94" s="3" t="n">
         <v>50359</v>
       </c>
     </row>
@@ -2244,7 +2528,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="2" t="n">
+        <v>52436.55113596525</v>
+      </c>
+      <c r="F95" s="3" t="n">
         <v>50360</v>
       </c>
     </row>
@@ -2263,7 +2550,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="2" t="n">
+        <v>52696.15408405932</v>
+      </c>
+      <c r="F96" s="3" t="n">
         <v>50389</v>
       </c>
     </row>
@@ -2282,7 +2572,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="2" t="n">
+        <v>52781.65276748715</v>
+      </c>
+      <c r="F97" s="3" t="n">
         <v>50390</v>
       </c>
     </row>
@@ -2301,7 +2594,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="2" t="n">
+        <v>52688.97268393984</v>
+      </c>
+      <c r="F98" s="3" t="n">
         <v>50391</v>
       </c>
     </row>
@@ -2320,7 +2616,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="2" t="n">
+        <v>52707.62781497127</v>
+      </c>
+      <c r="F99" s="3" t="n">
         <v>50420</v>
       </c>
     </row>
@@ -2339,7 +2638,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="2" t="n">
+        <v>52779.93915788193</v>
+      </c>
+      <c r="F100" s="3" t="n">
         <v>50421</v>
       </c>
     </row>
@@ -2358,7 +2660,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="E101" s="2" t="n">
+        <v>52200.96714812115</v>
+      </c>
+      <c r="F101" s="3" t="n">
         <v>50422</v>
       </c>
     </row>
@@ -2377,7 +2682,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="2" t="n">
+        <v>52586.34057749996</v>
+      </c>
+      <c r="F102" s="3" t="n">
         <v>50450</v>
       </c>
     </row>
@@ -2396,7 +2704,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E103" s="3" t="n">
+      <c r="E103" s="2" t="n">
+        <v>52759.56827074084</v>
+      </c>
+      <c r="F103" s="3" t="n">
         <v>50451</v>
       </c>
     </row>
@@ -2415,7 +2726,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E104" s="3" t="n">
+      <c r="E104" s="2" t="n">
+        <v>52800.2037025901</v>
+      </c>
+      <c r="F104" s="3" t="n">
         <v>50452</v>
       </c>
     </row>
@@ -2434,7 +2748,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E105" s="3" t="n">
+      <c r="E105" s="2" t="n">
+        <v>52202.44740669841</v>
+      </c>
+      <c r="F105" s="3" t="n">
         <v>50460</v>
       </c>
     </row>
@@ -2453,7 +2770,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E106" s="3" t="n">
+      <c r="E106" s="2" t="n">
+        <v>52801.66473717692</v>
+      </c>
+      <c r="F106" s="3" t="n">
         <v>50479</v>
       </c>
     </row>
@@ -2472,7 +2792,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E107" s="3" t="n">
+      <c r="E107" s="2" t="n">
+        <v>52763.19335509358</v>
+      </c>
+      <c r="F107" s="3" t="n">
         <v>50480</v>
       </c>
     </row>
@@ -2491,7 +2814,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E108" s="3" t="n">
+      <c r="E108" s="2" t="n">
+        <v>52217.3209253388</v>
+      </c>
+      <c r="F108" s="3" t="n">
         <v>50481</v>
       </c>
     </row>
@@ -2510,7 +2836,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E109" s="3" t="n">
+      <c r="E109" s="2" t="n">
+        <v>52700.16761493458</v>
+      </c>
+      <c r="F109" s="3" t="n">
         <v>50491</v>
       </c>
     </row>
@@ -2529,7 +2858,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E110" s="3" t="n">
+      <c r="E110" s="2" t="n">
+        <v>52884.67095850934</v>
+      </c>
+      <c r="F110" s="3" t="n">
         <v>50502</v>
       </c>
     </row>
@@ -2548,7 +2880,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E111" s="3" t="n">
+      <c r="E111" s="2" t="n">
+        <v>53540.36885060642</v>
+      </c>
+      <c r="F111" s="3" t="n">
         <v>50507</v>
       </c>
     </row>
@@ -2567,7 +2902,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E112" s="3" t="n">
+      <c r="E112" s="2" t="n">
+        <v>52841.89580579237</v>
+      </c>
+      <c r="F112" s="3" t="n">
         <v>50510</v>
       </c>
     </row>
@@ -2586,7 +2924,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E113" s="3" t="n">
+      <c r="E113" s="2" t="n">
+        <v>52267.45214053433</v>
+      </c>
+      <c r="F113" s="3" t="n">
         <v>50511</v>
       </c>
     </row>
@@ -2605,7 +2946,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E114" s="3" t="n">
+      <c r="E114" s="2" t="n">
+        <v>54006.38459425353</v>
+      </c>
+      <c r="F114" s="3" t="n">
         <v>50515</v>
       </c>
     </row>
@@ -2624,7 +2968,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E115" s="3" t="n">
+      <c r="E115" s="2" t="n">
+        <v>52871.38442209425</v>
+      </c>
+      <c r="F115" s="3" t="n">
         <v>50518</v>
       </c>
     </row>
@@ -2643,7 +2990,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E116" s="3" t="n">
+      <c r="E116" s="2" t="n">
+        <v>52975.42928178046</v>
+      </c>
+      <c r="F116" s="3" t="n">
         <v>50523</v>
       </c>
     </row>
@@ -2662,7 +3012,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E117" s="3" t="n">
+      <c r="E117" s="2" t="n">
+        <v>52767.43016429216</v>
+      </c>
+      <c r="F117" s="3" t="n">
         <v>50540</v>
       </c>
     </row>
@@ -2681,7 +3034,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n">
+      <c r="E118" s="2" t="n">
+        <v>52950.93892643536</v>
+      </c>
+      <c r="F118" s="3" t="n">
         <v>50541</v>
       </c>
     </row>
@@ -2700,7 +3056,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E119" s="3" t="n">
+      <c r="E119" s="2" t="n">
+        <v>54015.34729763318</v>
+      </c>
+      <c r="F119" s="3" t="n">
         <v>50542</v>
       </c>
     </row>
@@ -2719,7 +3078,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E120" s="3" t="n">
+      <c r="E120" s="2" t="n">
+        <v>52850.81718045034</v>
+      </c>
+      <c r="F120" s="3" t="n">
         <v>50566</v>
       </c>
     </row>
@@ -2738,7 +3100,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n">
+      <c r="E121" s="2" t="n">
+        <v>52554.75434476209</v>
+      </c>
+      <c r="F121" s="3" t="n">
         <v>50571</v>
       </c>
     </row>
@@ -2757,7 +3122,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E122" s="3" t="n">
+      <c r="E122" s="2" t="n">
+        <v>52440.19844205007</v>
+      </c>
+      <c r="F122" s="3" t="n">
         <v>50572</v>
       </c>
     </row>
@@ -2776,7 +3144,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E123" s="3" t="n">
+      <c r="E123" s="2" t="n">
+        <v>52489.09170761792</v>
+      </c>
+      <c r="F123" s="3" t="n">
         <v>50577</v>
       </c>
     </row>
@@ -2795,7 +3166,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E124" s="3" t="n">
+      <c r="E124" s="2" t="n">
+        <v>52869.73290148177</v>
+      </c>
+      <c r="F124" s="3" t="n">
         <v>50584</v>
       </c>
     </row>
@@ -2814,7 +3188,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E125" s="3" t="n">
+      <c r="E125" s="2" t="n">
+        <v>52794.79140846527</v>
+      </c>
+      <c r="F125" s="3" t="n">
         <v>50601</v>
       </c>
     </row>
@@ -2833,7 +3210,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E126" s="3" t="n">
+      <c r="E126" s="2" t="n">
+        <v>53338.42310817205</v>
+      </c>
+      <c r="F126" s="3" t="n">
         <v>50602</v>
       </c>
     </row>
@@ -2852,7 +3232,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E127" s="3" t="n">
+      <c r="E127" s="2" t="n">
+        <v>52937.57035273623</v>
+      </c>
+      <c r="F127" s="3" t="n">
         <v>50603</v>
       </c>
     </row>
@@ -2871,7 +3254,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E128" s="3" t="n">
+      <c r="E128" s="2" t="n">
+        <v>52219.82840561496</v>
+      </c>
+      <c r="F128" s="3" t="n">
         <v>50605</v>
       </c>
     </row>
@@ -2890,7 +3276,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E129" s="3" t="n">
+      <c r="E129" s="2" t="n">
+        <v>52791.76656283124</v>
+      </c>
+      <c r="F129" s="3" t="n">
         <v>50609</v>
       </c>
     </row>
@@ -2909,7 +3298,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E130" s="3" t="n">
+      <c r="E130" s="2" t="n">
+        <v>53679.28295715352</v>
+      </c>
+      <c r="F130" s="3" t="n">
         <v>50621</v>
       </c>
     </row>
@@ -2928,7 +3320,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E131" s="3" t="n">
+      <c r="E131" s="2" t="n">
+        <v>52605.03415622008</v>
+      </c>
+      <c r="F131" s="3" t="n">
         <v>50625</v>
       </c>
     </row>
@@ -2947,7 +3342,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E132" s="3" t="n">
+      <c r="E132" s="2" t="n">
+        <v>52787.93825979297</v>
+      </c>
+      <c r="F132" s="3" t="n">
         <v>50632</v>
       </c>
     </row>
@@ -2966,7 +3364,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E133" s="3" t="n">
+      <c r="E133" s="2" t="n">
+        <v>52055.77958536455</v>
+      </c>
+      <c r="F133" s="3" t="n">
         <v>50633</v>
       </c>
     </row>
@@ -2985,7 +3386,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E134" s="3" t="n">
+      <c r="E134" s="2" t="n">
+        <v>52640.61378712646</v>
+      </c>
+      <c r="F134" s="3" t="n">
         <v>50634</v>
       </c>
     </row>
@@ -3004,7 +3408,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E135" s="3" t="n">
+      <c r="E135" s="2" t="n">
+        <v>52872.32656822174</v>
+      </c>
+      <c r="F135" s="3" t="n">
         <v>50662</v>
       </c>
     </row>
@@ -3023,7 +3430,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E136" s="3" t="n">
+      <c r="E136" s="2" t="n">
+        <v>53338.11651374581</v>
+      </c>
+      <c r="F136" s="3" t="n">
         <v>50663</v>
       </c>
     </row>
@@ -3042,7 +3452,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E137" s="3" t="n">
+      <c r="E137" s="2" t="n">
+        <v>53320.52134876791</v>
+      </c>
+      <c r="F137" s="3" t="n">
         <v>50664</v>
       </c>
     </row>
@@ -3061,7 +3474,10 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E138" s="3" t="n">
+      <c r="E138" s="2" t="n">
+        <v>52568.47039672744</v>
+      </c>
+      <c r="F138" s="3" t="n">
         <v>50685</v>
       </c>
     </row>
@@ -3080,7 +3496,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E139" s="3" t="n">
+      <c r="E139" s="2" t="n">
+        <v>53602.95267258569</v>
+      </c>
+      <c r="F139" s="3" t="n">
         <v>50693</v>
       </c>
     </row>
@@ -3099,7 +3518,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E140" s="3" t="n">
+      <c r="E140" s="2" t="n">
+        <v>52975.46409750191</v>
+      </c>
+      <c r="F140" s="3" t="n">
         <v>50694</v>
       </c>
     </row>
@@ -3118,7 +3540,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E141" s="3" t="n">
+      <c r="E141" s="2" t="n">
+        <v>53381.37493346677</v>
+      </c>
+      <c r="F141" s="3" t="n">
         <v>50695</v>
       </c>
     </row>
@@ -3137,7 +3562,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E142" s="3" t="n">
+      <c r="E142" s="2" t="n">
+        <v>52142.23814654969</v>
+      </c>
+      <c r="F142" s="3" t="n">
         <v>50701</v>
       </c>
     </row>
@@ -3156,7 +3584,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E143" s="3" t="n">
+      <c r="E143" s="2" t="n">
+        <v>52919.7007457645</v>
+      </c>
+      <c r="F143" s="3" t="n">
         <v>50722</v>
       </c>
     </row>
@@ -3175,7 +3606,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E144" s="3" t="n">
+      <c r="E144" s="2" t="n">
+        <v>52534.36853420269</v>
+      </c>
+      <c r="F144" s="3" t="n">
         <v>50724</v>
       </c>
     </row>
@@ -3194,7 +3628,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E145" s="3" t="n">
+      <c r="E145" s="2" t="n">
+        <v>52938.35912738569</v>
+      </c>
+      <c r="F145" s="3" t="n">
         <v>50725</v>
       </c>
     </row>
@@ -3213,7 +3650,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E146" s="3" t="n">
+      <c r="E146" s="2" t="n">
+        <v>52600.44046386569</v>
+      </c>
+      <c r="F146" s="3" t="n">
         <v>50740</v>
       </c>
     </row>
@@ -3232,7 +3672,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E147" s="3" t="n">
+      <c r="E147" s="2" t="n">
+        <v>53113.28144684931</v>
+      </c>
+      <c r="F147" s="3" t="n">
         <v>50754</v>
       </c>
     </row>
@@ -3251,7 +3694,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E148" s="3" t="n">
+      <c r="E148" s="2" t="n">
+        <v>52999.44303958937</v>
+      </c>
+      <c r="F148" s="3" t="n">
         <v>50755</v>
       </c>
     </row>
@@ -3270,7 +3716,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E149" s="3" t="n">
+      <c r="E149" s="2" t="n">
+        <v>52634.85239239963</v>
+      </c>
+      <c r="F149" s="3" t="n">
         <v>50756</v>
       </c>
     </row>
@@ -3289,7 +3738,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E150" s="3" t="n">
+      <c r="E150" s="2" t="n">
+        <v>53022.23674335707</v>
+      </c>
+      <c r="F150" s="3" t="n">
         <v>50773</v>
       </c>
     </row>
@@ -3308,7 +3760,10 @@
           <t>MEE</t>
         </is>
       </c>
-      <c r="E151" s="3" t="n">
+      <c r="E151" s="2" t="n">
+        <v>53369.38500032239</v>
+      </c>
+      <c r="F151" s="3" t="n">
         <v>50781</v>
       </c>
     </row>
@@ -3327,7 +3782,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E152" s="3" t="n">
+      <c r="E152" s="2" t="n">
+        <v>53125.46748189825</v>
+      </c>
+      <c r="F152" s="3" t="n">
         <v>50785</v>
       </c>
     </row>
@@ -3346,7 +3804,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E153" s="3" t="n">
+      <c r="E153" s="2" t="n">
+        <v>53144.45820159718</v>
+      </c>
+      <c r="F153" s="3" t="n">
         <v>50786</v>
       </c>
     </row>
@@ -3365,7 +3826,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E154" s="3" t="n">
+      <c r="E154" s="2" t="n">
+        <v>53339.07014097561</v>
+      </c>
+      <c r="F154" s="3" t="n">
         <v>50787</v>
       </c>
     </row>
@@ -3384,7 +3848,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E155" s="3" t="n">
+      <c r="E155" s="2" t="n">
+        <v>52813.11080781551</v>
+      </c>
+      <c r="F155" s="3" t="n">
         <v>50815</v>
       </c>
     </row>
@@ -3403,7 +3870,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E156" s="3" t="n">
+      <c r="E156" s="2" t="n">
+        <v>53149.71702937175</v>
+      </c>
+      <c r="F156" s="3" t="n">
         <v>50816</v>
       </c>
     </row>
@@ -3422,7 +3892,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E157" s="3" t="n">
+      <c r="E157" s="2" t="n">
+        <v>53125.63515457</v>
+      </c>
+      <c r="F157" s="3" t="n">
         <v>50817</v>
       </c>
     </row>
@@ -3441,7 +3914,10 @@
           <t>VVEE</t>
         </is>
       </c>
-      <c r="E158" s="3" t="n">
+      <c r="E158" s="2" t="n">
+        <v>53129.55263681459</v>
+      </c>
+      <c r="F158" s="3" t="n">
         <v>50835</v>
       </c>
     </row>
@@ -3460,7 +3936,10 @@
           <t>VEVE</t>
         </is>
       </c>
-      <c r="E159" s="3" t="n">
+      <c r="E159" s="2" t="n">
+        <v>53258.81389576553</v>
+      </c>
+      <c r="F159" s="3" t="n">
         <v>50844</v>
       </c>
     </row>
@@ -3479,7 +3958,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E160" s="3" t="n">
+      <c r="E160" s="2" t="n">
+        <v>53341.13901951561</v>
+      </c>
+      <c r="F160" s="3" t="n">
         <v>50845</v>
       </c>
     </row>
@@ -3498,7 +3980,10 @@
           <t>VEE</t>
         </is>
       </c>
-      <c r="E161" s="3" t="n">
+      <c r="E161" s="2" t="n">
+        <v>53460.56919872217</v>
+      </c>
+      <c r="F161" s="3" t="n">
         <v>50853</v>
       </c>
     </row>
@@ -3517,7 +4002,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E162" s="3" t="n">
+      <c r="E162" s="2" t="n">
+        <v>53345.55455169536</v>
+      </c>
+      <c r="F162" s="3" t="n">
         <v>50857</v>
       </c>
     </row>
@@ -3536,7 +4024,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E163" s="3" t="n">
+      <c r="E163" s="2" t="n">
+        <v>52934.47993546928</v>
+      </c>
+      <c r="F163" s="3" t="n">
         <v>50875</v>
       </c>
     </row>
@@ -3555,7 +4046,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E164" s="3" t="n">
+      <c r="E164" s="2" t="n">
+        <v>52637.84468458551</v>
+      </c>
+      <c r="F164" s="3" t="n">
         <v>50876</v>
       </c>
     </row>
@@ -3574,7 +4068,10 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E165" s="3" t="n">
+      <c r="E165" s="2" t="n">
+        <v>53033.73936507614</v>
+      </c>
+      <c r="F165" s="3" t="n">
         <v>50905</v>
       </c>
     </row>
@@ -3593,7 +4090,10 @@
           <t>VE</t>
         </is>
       </c>
-      <c r="E166" s="3" t="n">
+      <c r="E166" s="2" t="n">
+        <v>52703.95349274326</v>
+      </c>
+      <c r="F166" s="3" t="n">
         <v>50906</v>
       </c>
     </row>
@@ -3612,7 +4112,10 @@
           <t>VEM</t>
         </is>
       </c>
-      <c r="E167" s="3" t="n">
+      <c r="E167" s="2" t="n">
+        <v>53418.56563370526</v>
+      </c>
+      <c r="F167" s="3" t="n">
         <v>50907</v>
       </c>
     </row>
@@ -3631,3275 +4134,3002 @@
           <t>VVE</t>
         </is>
       </c>
-      <c r="E168" s="3" t="n">
+      <c r="E168" s="2" t="n">
+        <v>53021.59191029978</v>
+      </c>
+      <c r="F168" s="3" t="n">
         <v>50914</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>50916.55651249287</v>
+        <v>50925.35648712025</v>
       </c>
       <c r="B169" t="n">
-        <v>8811.345255538041</v>
+        <v>3086.75257694494</v>
       </c>
       <c r="C169" t="n">
-        <v>3739.864962859613</v>
+        <v>2194.507348288722</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>50916</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>53119.86383540897</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>50925</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>50925.35648712025</v>
+        <v>50937</v>
       </c>
       <c r="B170" t="n">
-        <v>3086.75257694494</v>
+        <v>3067.572901237036</v>
       </c>
       <c r="C170" t="n">
-        <v>2194.507348288722</v>
+        <v>1849.279973934608</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>50925</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>52786.27997393461</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>50937</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>50937</v>
+        <v>50943.91832806184</v>
       </c>
       <c r="B171" t="n">
-        <v>3067.572901237036</v>
+        <v>3043.963355083282</v>
       </c>
       <c r="C171" t="n">
-        <v>1849.279973934608</v>
+        <v>1865.492957054876</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="E171" s="3" t="n">
-        <v>50937</v>
+      <c r="E171" s="2" t="n">
+        <v>52809.41128511672</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>50943</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>50943.91832806184</v>
+        <v>50966.99999999999</v>
       </c>
       <c r="B172" t="n">
-        <v>3043.963355083282</v>
+        <v>10862.80331378875</v>
       </c>
       <c r="C172" t="n">
-        <v>1865.492957054876</v>
+        <v>1959.0920236014</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>50943</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>52926.09202360138</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>50966</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>50966.99999999999</v>
+        <v>50967</v>
       </c>
       <c r="B173" t="n">
-        <v>10862.80331378875</v>
+        <v>15075.88493054071</v>
       </c>
       <c r="C173" t="n">
-        <v>1959.0920236014</v>
+        <v>1763.081728311062</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>50966</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>52730.08172831105</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>50967</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>50967</v>
+        <v>50968.00000000001</v>
       </c>
       <c r="B174" t="n">
-        <v>15075.88493054071</v>
+        <v>3294.552202643603</v>
       </c>
       <c r="C174" t="n">
-        <v>1763.081728311062</v>
+        <v>1908.095096532966</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>50967</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>52876.09509653298</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>50968</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>50968.00000000001</v>
+        <v>50982.81575939839</v>
       </c>
       <c r="B175" t="n">
-        <v>3294.552202643603</v>
+        <v>10459.20506504065</v>
       </c>
       <c r="C175" t="n">
-        <v>1908.095096532966</v>
+        <v>1954.854080764504</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>50968</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>52937.6698401629</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>50982</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>50982.81575939839</v>
+        <v>50997.99999999999</v>
       </c>
       <c r="B176" t="n">
-        <v>10459.20506504065</v>
+        <v>2217.618581364153</v>
       </c>
       <c r="C176" t="n">
-        <v>1954.854080764504</v>
+        <v>2096.524316736547</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>50982</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>53094.52431673653</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>50997</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>50997.99999999999</v>
+        <v>50998</v>
       </c>
       <c r="B177" t="n">
-        <v>2217.618581364153</v>
+        <v>11340.20569343944</v>
       </c>
       <c r="C177" t="n">
-        <v>2096.524316736547</v>
+        <v>1750.155130281763</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>50997</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>52748.15513028176</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>50998</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>50998</v>
+        <v>50999</v>
       </c>
       <c r="B178" t="n">
-        <v>11340.20569343944</v>
+        <v>4384.749504158795</v>
       </c>
       <c r="C178" t="n">
-        <v>1750.155130281763</v>
+        <v>1651.155113152701</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>50998</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>52650.15511315269</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>50999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>50999</v>
+        <v>51011.29490094929</v>
       </c>
       <c r="B179" t="n">
-        <v>4384.749504158795</v>
+        <v>1970.306025961567</v>
       </c>
       <c r="C179" t="n">
-        <v>1651.155113152701</v>
+        <v>2147.985921787038</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>50999</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>53159.28082273633</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>51011</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>51011.29490094929</v>
+        <v>51016.44866665116</v>
       </c>
       <c r="B180" t="n">
-        <v>1970.306025961567</v>
+        <v>10279.90934366252</v>
       </c>
       <c r="C180" t="n">
-        <v>2147.985921787038</v>
+        <v>1924.78564765378</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>51011</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>52941.23431430493</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>51016</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>51016.44866665116</v>
+        <v>51028.48802084431</v>
       </c>
       <c r="B181" t="n">
-        <v>10279.90934366252</v>
+        <v>11366.03409128407</v>
       </c>
       <c r="C181" t="n">
-        <v>1924.78564765378</v>
+        <v>1805.289709263106</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>51016</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>52833.77773010741</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>51028</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>51028.48802084431</v>
+        <v>51029</v>
       </c>
       <c r="B182" t="n">
-        <v>11366.03409128407</v>
+        <v>2257.433812141382</v>
       </c>
       <c r="C182" t="n">
-        <v>1805.289709263106</v>
+        <v>2237.352871344337</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>51028</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>53266.35287134433</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>51029</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>51029</v>
+        <v>51036.6098084323</v>
       </c>
       <c r="B183" t="n">
-        <v>2257.433812141382</v>
+        <v>9824.374555234284</v>
       </c>
       <c r="C183" t="n">
-        <v>2237.352871344337</v>
+        <v>1729.868919660621</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>51029</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>52766.47872809292</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>51036</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>51036.6098084323</v>
+        <v>51044.19548305994</v>
       </c>
       <c r="B184" t="n">
-        <v>9824.374555234284</v>
+        <v>5677.693325051729</v>
       </c>
       <c r="C184" t="n">
-        <v>1729.868919660621</v>
+        <v>2344.783369377573</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>51036</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>53388.97885243751</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>51044</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>51044.19548305994</v>
+        <v>51058.99999999948</v>
       </c>
       <c r="B185" t="n">
-        <v>5677.693325051729</v>
+        <v>7663.33484616197</v>
       </c>
       <c r="C185" t="n">
-        <v>2344.783369377573</v>
+        <v>2052.915523865457</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>51044</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>53111.91552386493</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>51058</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>51058.99999999948</v>
+        <v>51060</v>
       </c>
       <c r="B186" t="n">
-        <v>7663.33484616197</v>
+        <v>3544.412487819436</v>
       </c>
       <c r="C186" t="n">
-        <v>2052.915523865457</v>
+        <v>2645.08074555508</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>51058</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>53705.08074555507</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>51060</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>51060</v>
+        <v>51069.10026137706</v>
       </c>
       <c r="B187" t="n">
-        <v>3544.412487819436</v>
+        <v>6730.406105958034</v>
       </c>
       <c r="C187" t="n">
-        <v>2645.08074555508</v>
+        <v>2707.987221254765</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>51060</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>53777.08748263182</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>51069</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>51069.10026137706</v>
+        <v>51090</v>
       </c>
       <c r="B188" t="n">
-        <v>6730.406105958034</v>
+        <v>5657.110791458814</v>
       </c>
       <c r="C188" t="n">
-        <v>2707.987221254765</v>
+        <v>2671.03893029319</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>51069</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>53761.03893029318</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>51090</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>51090</v>
+        <v>51119.99999999999</v>
       </c>
       <c r="B189" t="n">
-        <v>5657.110791458814</v>
+        <v>12147.09815144838</v>
       </c>
       <c r="C189" t="n">
-        <v>2671.03893029319</v>
+        <v>1484.060331592765</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>51090</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>52604.06033159274</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>51119</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>51119.99999999999</v>
+        <v>51120</v>
       </c>
       <c r="B190" t="n">
-        <v>12147.09815144838</v>
+        <v>15894.42561479096</v>
       </c>
       <c r="C190" t="n">
-        <v>1484.060331592765</v>
+        <v>2849.469970664437</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>51119</v>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>53969.46997066443</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>51120</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>51120</v>
+        <v>51121.00000123936</v>
       </c>
       <c r="B191" t="n">
-        <v>15894.42561479096</v>
+        <v>10601.52856780689</v>
       </c>
       <c r="C191" t="n">
-        <v>2849.469970664437</v>
+        <v>2255.959917207415</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>51120</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>53376.95991844677</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>51121</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>51121.00000123936</v>
+        <v>51127.23397537271</v>
       </c>
       <c r="B192" t="n">
-        <v>10601.52856780689</v>
+        <v>12071.0963142543</v>
       </c>
       <c r="C192" t="n">
-        <v>2255.959917207415</v>
+        <v>1515.439451014626</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>51121</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>52642.67342638733</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>51127</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>51127.23397537271</v>
+        <v>51151</v>
       </c>
       <c r="B193" t="n">
-        <v>12071.0963142543</v>
+        <v>10071.22019405535</v>
       </c>
       <c r="C193" t="n">
-        <v>1515.439451014626</v>
+        <v>2023.289853973595</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="n">
-        <v>51127</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>53174.28985397359</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>51151</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>51151</v>
+        <v>51152.00000018143</v>
       </c>
       <c r="B194" t="n">
-        <v>10071.22019405535</v>
+        <v>11154.48227417286</v>
       </c>
       <c r="C194" t="n">
-        <v>2023.289853973595</v>
+        <v>1876.041014803024</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>51151</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>53028.04101498445</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>51152</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>51152.00000018143</v>
+        <v>51176.22100097346</v>
       </c>
       <c r="B195" t="n">
-        <v>11154.48227417286</v>
+        <v>14368.57004452504</v>
       </c>
       <c r="C195" t="n">
-        <v>1876.041014803024</v>
+        <v>1263.445915302427</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>51152</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>52439.66691627588</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>51176</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>51176.22100097346</v>
+        <v>51181.99999999999</v>
       </c>
       <c r="B196" t="n">
-        <v>14368.57004452504</v>
+        <v>7983.122407120793</v>
       </c>
       <c r="C196" t="n">
-        <v>1263.445915302427</v>
+        <v>1941.527793650004</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>51176</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>53123.52779364999</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>51181</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>51181.99999999999</v>
+        <v>51182</v>
       </c>
       <c r="B197" t="n">
-        <v>7983.122407120793</v>
+        <v>10127.27244379687</v>
       </c>
       <c r="C197" t="n">
-        <v>1941.527793650004</v>
+        <v>2357.127955893218</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>51181</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>53539.12795589321</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>51182</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>51182</v>
+        <v>51206.33342933965</v>
       </c>
       <c r="B198" t="n">
-        <v>10127.27244379687</v>
+        <v>5764.511135484176</v>
       </c>
       <c r="C198" t="n">
-        <v>2357.127955893218</v>
+        <v>1913.464708496148</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>51182</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>53119.7981378358</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>51206</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>51206.33342933965</v>
+        <v>51210.99999997632</v>
       </c>
       <c r="B199" t="n">
-        <v>5764.511135484176</v>
+        <v>6838.981769905186</v>
       </c>
       <c r="C199" t="n">
-        <v>1913.464708496148</v>
+        <v>1715.41481908141</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>51206</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>52926.41481905772</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>51210</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>51210.99999997632</v>
+        <v>51211</v>
       </c>
       <c r="B200" t="n">
-        <v>6838.981769905186</v>
+        <v>8780.377093500894</v>
       </c>
       <c r="C200" t="n">
-        <v>1715.41481908141</v>
+        <v>2378.269517524567</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>51210</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>53589.26951752456</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>51211</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>51211</v>
+        <v>51212</v>
       </c>
       <c r="B201" t="n">
-        <v>8780.377093500894</v>
+        <v>5841.571117616584</v>
       </c>
       <c r="C201" t="n">
-        <v>2378.269517524567</v>
+        <v>1914.51759334634</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>51211</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>53126.51759334633</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>51212</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>51212</v>
+        <v>51213.35111040805</v>
       </c>
       <c r="B202" t="n">
-        <v>5841.571117616584</v>
+        <v>11688.32501834102</v>
       </c>
       <c r="C202" t="n">
-        <v>1914.51759334634</v>
+        <v>1873.63602175968</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>51212</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>53086.98713216772</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>51213</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>51213.35111040805</v>
+        <v>51215.02113948088</v>
       </c>
       <c r="B203" t="n">
-        <v>11688.32501834102</v>
+        <v>6834.030789400924</v>
       </c>
       <c r="C203" t="n">
-        <v>1873.63602175968</v>
+        <v>1730.046319127933</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>51213</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>52945.06745860881</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>51215</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>51215.02113948088</v>
+        <v>51241.99102712394</v>
       </c>
       <c r="B204" t="n">
-        <v>6834.030789400924</v>
+        <v>9766.086771061404</v>
       </c>
       <c r="C204" t="n">
-        <v>1730.046319127933</v>
+        <v>2243.619927175167</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>51215</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>53485.6109542991</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>51241</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>51241.99102712394</v>
+        <v>51242</v>
       </c>
       <c r="B205" t="n">
-        <v>9766.086771061404</v>
+        <v>6041.691181437269</v>
       </c>
       <c r="C205" t="n">
-        <v>2243.619927175167</v>
+        <v>2268.633503687928</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>51241</v>
+          <t>MEE</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>53510.63350368792</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>51242</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>51242</v>
+        <v>51248.39172176265</v>
       </c>
       <c r="B206" t="n">
-        <v>6041.691181437269</v>
+        <v>9752.028605911204</v>
       </c>
       <c r="C206" t="n">
-        <v>2268.633503687928</v>
+        <v>2240.037192751804</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>51242</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>53488.42891451444</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>51248</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>51248.39172176265</v>
+        <v>51261.82603209325</v>
       </c>
       <c r="B207" t="n">
-        <v>9752.028605911204</v>
+        <v>12385.15641945054</v>
       </c>
       <c r="C207" t="n">
-        <v>2240.037192751804</v>
+        <v>2206.445323019127</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="n">
-        <v>51248</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>53468.27135511237</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>51261</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>51261.82603209325</v>
+        <v>51271.99999999988</v>
       </c>
       <c r="B208" t="n">
-        <v>12385.15641945054</v>
+        <v>8999.343024112595</v>
       </c>
       <c r="C208" t="n">
-        <v>2206.445323019127</v>
+        <v>2767.170753541317</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="n">
-        <v>51261</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>54039.17075354119</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>51271</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>51271.99999999988</v>
+        <v>51272</v>
       </c>
       <c r="B209" t="n">
-        <v>8999.343024112595</v>
+        <v>6160.902376060669</v>
       </c>
       <c r="C209" t="n">
-        <v>2767.170753541317</v>
+        <v>2077.232967848855</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="n">
-        <v>51271</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>53349.23296784885</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>51272</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>51272</v>
+        <v>51273.00000000001</v>
       </c>
       <c r="B210" t="n">
-        <v>2601.660276859529</v>
+        <v>12482.23503425442</v>
       </c>
       <c r="C210" t="n">
-        <v>3171.606676100217</v>
+        <v>2195.606203139389</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>51272</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>53468.6062031394</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>51273</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>51273.00000000001</v>
+        <v>51277.35747296921</v>
       </c>
       <c r="B211" t="n">
-        <v>12482.23503425442</v>
+        <v>7734.609112737289</v>
       </c>
       <c r="C211" t="n">
-        <v>2195.606203139389</v>
+        <v>2206.625097696483</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>51273</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>53483.98257066569</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>51277</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>51277.35747296921</v>
+        <v>51291.31523088403</v>
       </c>
       <c r="B212" t="n">
-        <v>7734.609112737289</v>
+        <v>6085.499301724671</v>
       </c>
       <c r="C212" t="n">
-        <v>2206.625097696483</v>
+        <v>2056.691656881615</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>51277</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>53348.00688776564</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>51291</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>51280.25075181427</v>
+        <v>51296.29163049991</v>
       </c>
       <c r="B213" t="n">
-        <v>2599.083016588973</v>
+        <v>10196.80320665508</v>
       </c>
       <c r="C213" t="n">
-        <v>2932.082562040456</v>
+        <v>2133.190763997608</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>51280</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>53429.48239449751</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>51296</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>51291.31523088403</v>
+        <v>51297.6406234313</v>
       </c>
       <c r="B214" t="n">
-        <v>6085.499301724671</v>
+        <v>4437.260464211735</v>
       </c>
       <c r="C214" t="n">
-        <v>2056.691656881615</v>
+        <v>1903.770259245576</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>51291</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>53201.41088267686</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>51297</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>51296.29163049991</v>
+        <v>51303</v>
       </c>
       <c r="B215" t="n">
-        <v>10196.80320665508</v>
+        <v>4482.402297961162</v>
       </c>
       <c r="C215" t="n">
-        <v>2133.190763997608</v>
+        <v>1993.749598666359</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="n">
-        <v>51296</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>53296.74959866636</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>51303</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>51297.6406234313</v>
+        <v>51317.61762397609</v>
       </c>
       <c r="B216" t="n">
-        <v>4437.260464211735</v>
+        <v>8211.836128429884</v>
       </c>
       <c r="C216" t="n">
-        <v>1903.770259245576</v>
+        <v>1655.761470204968</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>51297</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>52973.37909418105</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>51317</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>51302.99999999972</v>
+        <v>51332.99999994258</v>
       </c>
       <c r="B217" t="n">
-        <v>7745.327282133348</v>
+        <v>7129.302937860562</v>
       </c>
       <c r="C217" t="n">
-        <v>2906.838043117208</v>
+        <v>1796.786622053504</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>51302</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>53129.78662199608</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>51332</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>51303</v>
+        <v>51334</v>
       </c>
       <c r="B218" t="n">
-        <v>2815.564844062854</v>
+        <v>4753.552564422771</v>
       </c>
       <c r="C218" t="n">
-        <v>2854.453825243724</v>
+        <v>2680.104467818155</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
           <t>MEE</t>
         </is>
       </c>
-      <c r="E218" s="3" t="n">
-        <v>51303</v>
+      <c r="E218" s="2" t="n">
+        <v>54014.10446781815</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>51334</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>51317.61762397609</v>
+        <v>51351.88728898609</v>
       </c>
       <c r="B219" t="n">
-        <v>8211.836128429884</v>
+        <v>18469.50978507407</v>
       </c>
       <c r="C219" t="n">
-        <v>1655.761470204968</v>
+        <v>2109.481609855894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>51317</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>53461.36889884198</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>51351</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>51332.99999977433</v>
+        <v>51363.99999955993</v>
       </c>
       <c r="B220" t="n">
-        <v>7094.944445968797</v>
+        <v>5911.622384470073</v>
       </c>
       <c r="C220" t="n">
-        <v>2863.615621671772</v>
+        <v>1819.916866058876</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>51332</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>53183.9168656188</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>51363</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>51334</v>
+        <v>51364</v>
       </c>
       <c r="B221" t="n">
-        <v>4753.552564422771</v>
+        <v>4465.214398931872</v>
       </c>
       <c r="C221" t="n">
-        <v>2680.104467818155</v>
+        <v>1733.667913607321</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>51334</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>53097.66791360731</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>51364</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>51351.88728898609</v>
+        <v>51365</v>
       </c>
       <c r="B222" t="n">
-        <v>18469.50978507407</v>
+        <v>19659.74574764842</v>
       </c>
       <c r="C222" t="n">
-        <v>2109.481609855894</v>
+        <v>2098.749231758478</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
           <t>ME</t>
         </is>
       </c>
-      <c r="E222" s="3" t="n">
-        <v>51351</v>
+      <c r="E222" s="2" t="n">
+        <v>53463.74923175847</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>51365</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>51363.99999955993</v>
+        <v>51382.48178085611</v>
       </c>
       <c r="B223" t="n">
-        <v>5911.622384470073</v>
+        <v>3893.471959826318</v>
       </c>
       <c r="C223" t="n">
-        <v>1819.916866058876</v>
+        <v>1900.715527992519</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>51363</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>53283.19730884862</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>51382</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>51364</v>
+        <v>51394.99999919424</v>
       </c>
       <c r="B224" t="n">
-        <v>4465.214398931872</v>
+        <v>5430.201724213552</v>
       </c>
       <c r="C224" t="n">
-        <v>1733.667913607321</v>
+        <v>1824.395794517174</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>51364</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>53219.3957937114</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>51394</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>51365.00000000002</v>
+        <v>51395</v>
       </c>
       <c r="B225" t="n">
-        <v>14716.86750165837</v>
+        <v>9648.577073833978</v>
       </c>
       <c r="C225" t="n">
-        <v>2702.968288957566</v>
+        <v>2060.511369074058</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>51365</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>53455.51136907405</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>51395</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>51378.91951601095</v>
+        <v>51406.62837305725</v>
       </c>
       <c r="B226" t="n">
-        <v>7769.805440065897</v>
+        <v>8673.523402327844</v>
       </c>
       <c r="C226" t="n">
-        <v>3301.618738034895</v>
+        <v>1912.886113091268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>51378</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>53319.51448614852</v>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>51406</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>51382.48178085611</v>
+        <v>51424.99999995252</v>
       </c>
       <c r="B227" t="n">
-        <v>3893.471959826318</v>
+        <v>4925.629969372643</v>
       </c>
       <c r="C227" t="n">
-        <v>1900.715527992519</v>
+        <v>1794.353813492281</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="n">
-        <v>51382</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>53219.3538134448</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>51424</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>51394.99999919424</v>
+        <v>51425</v>
       </c>
       <c r="B228" t="n">
-        <v>5430.201724213552</v>
+        <v>4838.401851720791</v>
       </c>
       <c r="C228" t="n">
-        <v>1824.395794517174</v>
+        <v>1497.051854036048</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>51394</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>52922.05185403604</v>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>51425</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>51395</v>
+        <v>51448.5497201496</v>
       </c>
       <c r="B229" t="n">
-        <v>8584.487311778679</v>
+        <v>4747.815848525037</v>
       </c>
       <c r="C229" t="n">
-        <v>3584.647579346285</v>
+        <v>1492.148476618927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>51395</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>52940.69819676853</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>51448</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>51406.62837305725</v>
+        <v>51455.99999993191</v>
       </c>
       <c r="B230" t="n">
-        <v>8673.523402327844</v>
+        <v>4359.614289158751</v>
       </c>
       <c r="C230" t="n">
-        <v>1912.886113091268</v>
+        <v>1763.357256622755</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>51406</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>53219.35725655466</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>51455</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>51424.99999995252</v>
+        <v>51456</v>
       </c>
       <c r="B231" t="n">
-        <v>4925.629969372643</v>
+        <v>5822.000010425669</v>
       </c>
       <c r="C231" t="n">
-        <v>1794.353813492281</v>
+        <v>2249.061458277022</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>51424</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>53705.06145827701</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>51456</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>51425</v>
+        <v>51469.71754360322</v>
       </c>
       <c r="B232" t="n">
-        <v>4838.401851720791</v>
+        <v>4206.084386503846</v>
       </c>
       <c r="C232" t="n">
-        <v>1497.051854036048</v>
+        <v>1760.696471569028</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>51425</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>53230.41401517223</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>51469</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>51426</v>
+        <v>51479.87413845906</v>
       </c>
       <c r="B233" t="n">
-        <v>11546.67024959516</v>
+        <v>16120.66824325093</v>
       </c>
       <c r="C233" t="n">
-        <v>3545.449090420582</v>
+        <v>1881.662878942747</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>51426</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>53361.5370174018</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>51479</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>51448.5497201496</v>
+        <v>51481.4991657808</v>
       </c>
       <c r="B234" t="n">
-        <v>4747.815848525037</v>
+        <v>4158.79451060994</v>
       </c>
       <c r="C234" t="n">
-        <v>1492.148476618927</v>
+        <v>2291.944157574213</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="E234" s="3" t="n">
-        <v>51448</v>
+      <c r="E234" s="2" t="n">
+        <v>53773.44332335501</v>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>51481</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>51451.37025626643</v>
+        <v>51485.99999999764</v>
       </c>
       <c r="B235" t="n">
-        <v>6673.66417421671</v>
+        <v>7775.376842015268</v>
       </c>
       <c r="C235" t="n">
-        <v>3111.483151901069</v>
+        <v>1820.303756623213</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>51451</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>53306.30375662084</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>51485</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>51455.99999993191</v>
+        <v>51486</v>
       </c>
       <c r="B236" t="n">
-        <v>4359.614289158751</v>
+        <v>5414.696178860857</v>
       </c>
       <c r="C236" t="n">
-        <v>1763.357256622755</v>
+        <v>2332.730057271642</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>51455</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>53818.73005727163</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>51486</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>51456</v>
+        <v>51487.00001134702</v>
       </c>
       <c r="B237" t="n">
-        <v>5822.000010425669</v>
+        <v>4402.253579838487</v>
       </c>
       <c r="C237" t="n">
-        <v>2249.061458277022</v>
+        <v>1794.078508457931</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>51456</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>53281.07851980496</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>51487</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>51469.71754360322</v>
+        <v>51490.52429342313</v>
       </c>
       <c r="B238" t="n">
-        <v>4206.084386503846</v>
+        <v>5407.099408225691</v>
       </c>
       <c r="C238" t="n">
-        <v>1760.696471569028</v>
+        <v>2370.235274319738</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>51469</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>53860.75956774286</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>51490</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>51479.87413845906</v>
+        <v>51494.79703281376</v>
       </c>
       <c r="B239" t="n">
-        <v>16120.66824325093</v>
+        <v>4328.987903602823</v>
       </c>
       <c r="C239" t="n">
-        <v>1881.662878942747</v>
+        <v>1433.875216269168</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="n">
-        <v>51479</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>52928.67224908293</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>51494</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>51481.4991657808</v>
+        <v>51518</v>
       </c>
       <c r="B240" t="n">
-        <v>4158.79451060994</v>
+        <v>4576.852752518196</v>
       </c>
       <c r="C240" t="n">
-        <v>2291.944157574213</v>
+        <v>1447.981894652621</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="E240" s="3" t="n">
-        <v>51481</v>
+      <c r="E240" s="2" t="n">
+        <v>52965.98189465261</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>51518</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>51485.99999999764</v>
+        <v>51521.30134719607</v>
       </c>
       <c r="B241" t="n">
-        <v>7775.376842015268</v>
+        <v>5444.199735946797</v>
       </c>
       <c r="C241" t="n">
-        <v>1820.303756623213</v>
+        <v>2395.423306729977</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>51485</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>53916.72465392605</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>51521</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>51486</v>
+        <v>51533.69269643682</v>
       </c>
       <c r="B242" t="n">
-        <v>5414.696178860857</v>
+        <v>9091.995045373107</v>
       </c>
       <c r="C242" t="n">
-        <v>2332.730057271642</v>
+        <v>2497.99240773169</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>51486</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>54031.68510416849</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>51533</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>51487.00001134702</v>
+        <v>51546</v>
       </c>
       <c r="B243" t="n">
-        <v>4402.253579838487</v>
+        <v>5877.041605395849</v>
       </c>
       <c r="C243" t="n">
-        <v>1794.078508457931</v>
+        <v>2453.062532695331</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="n">
-        <v>51487</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>53999.06253269532</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>51546</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>51490.52429342313</v>
+        <v>51548</v>
       </c>
       <c r="B244" t="n">
-        <v>5407.099408225691</v>
+        <v>18077.09117576174</v>
       </c>
       <c r="C244" t="n">
-        <v>2370.235274319738</v>
+        <v>1884.920895282944</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="n">
-        <v>51490</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>53432.92089528294</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>51548</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>51494.79703281376</v>
+        <v>51549.21221250146</v>
       </c>
       <c r="B245" t="n">
-        <v>4328.987903602823</v>
+        <v>21574.68955744587</v>
       </c>
       <c r="C245" t="n">
-        <v>1433.875216269168</v>
+        <v>1866.915402109033</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="n">
-        <v>51494</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>53416.12761461049</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>51549</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>51517</v>
+        <v>51575.99999245147</v>
       </c>
       <c r="B246" t="n">
-        <v>12921.62349544533</v>
+        <v>13399.10763094579</v>
       </c>
       <c r="C246" t="n">
-        <v>3295.183493182617</v>
+        <v>2273.468358554657</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>51517</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>53849.46835100612</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>51575</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>51518</v>
+        <v>51577</v>
       </c>
       <c r="B247" t="n">
-        <v>4576.852752518196</v>
+        <v>11794.38567030492</v>
       </c>
       <c r="C247" t="n">
-        <v>1447.981894652621</v>
+        <v>1820.597571916417</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="E247" s="3" t="n">
-        <v>51518</v>
+      <c r="E247" s="2" t="n">
+        <v>53397.59757191641</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>51577</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>51521.30134719607</v>
+        <v>51606.99999999999</v>
       </c>
       <c r="B248" t="n">
-        <v>5444.199735946797</v>
+        <v>10394.95244401122</v>
       </c>
       <c r="C248" t="n">
-        <v>2395.423306729977</v>
+        <v>2247.894433727507</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="n">
-        <v>51521</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>53854.89443372749</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>51606</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>51533.69269643682</v>
+        <v>51607.00000001583</v>
       </c>
       <c r="B249" t="n">
-        <v>9091.995045373107</v>
+        <v>11174.07466119963</v>
       </c>
       <c r="C249" t="n">
-        <v>2497.99240773169</v>
+        <v>1727.75762192567</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="n">
-        <v>51533</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>53334.75762194149</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>51607</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>51539.08571754518</v>
+        <v>51636.99986125867</v>
       </c>
       <c r="B250" t="n">
-        <v>11822.14732327884</v>
+        <v>8989.567110167352</v>
       </c>
       <c r="C250" t="n">
-        <v>3432.886231132477</v>
+        <v>2263.96563027715</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="n">
-        <v>51539</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>53900.96549153581</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>51636</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>51546</v>
+        <v>51637</v>
       </c>
       <c r="B251" t="n">
-        <v>5877.041605395849</v>
+        <v>13400.82492276121</v>
       </c>
       <c r="C251" t="n">
-        <v>2453.062532695331</v>
+        <v>1855.37059417736</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="n">
-        <v>51546</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>53492.37059417735</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>51637</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>51548</v>
+        <v>51638.00000033309</v>
       </c>
       <c r="B252" t="n">
-        <v>18077.09117576174</v>
+        <v>14818.16816193844</v>
       </c>
       <c r="C252" t="n">
-        <v>1884.920895282944</v>
+        <v>2386.592059523776</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="n">
-        <v>51548</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>54024.59205985686</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>51638</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>51549.21221250146</v>
+        <v>51664.19557300543</v>
       </c>
       <c r="B253" t="n">
-        <v>21574.68955744587</v>
+        <v>25533.10120873276</v>
       </c>
       <c r="C253" t="n">
-        <v>1866.915402109033</v>
+        <v>1393.375761225942</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
           <t>ME</t>
         </is>
       </c>
-      <c r="E253" s="3" t="n">
-        <v>51549</v>
+      <c r="E253" s="2" t="n">
+        <v>53057.57133423137</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>51664</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>51565.67127000008</v>
+        <v>51667.99999999996</v>
       </c>
       <c r="B254" t="n">
-        <v>7687.808394090487</v>
+        <v>8215.160664647279</v>
       </c>
       <c r="C254" t="n">
-        <v>2987.847521297687</v>
+        <v>2204.619245117839</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="n">
-        <v>51565</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>53872.6192451178</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>51667</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>51575.99999245147</v>
+        <v>51668</v>
       </c>
       <c r="B255" t="n">
-        <v>13399.10763094579</v>
+        <v>8595.854713828858</v>
       </c>
       <c r="C255" t="n">
-        <v>2273.468358554657</v>
+        <v>2269.847351243972</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="n">
-        <v>51575</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>53937.84735124397</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>51668</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>51576</v>
+        <v>51676.488755925</v>
       </c>
       <c r="B256" t="n">
-        <v>11352.53259835045</v>
+        <v>8174.799290456387</v>
       </c>
       <c r="C256" t="n">
-        <v>3364.057777531623</v>
+        <v>2147.048345614171</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="n">
-        <v>51576</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>53823.53710153916</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>51676</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>51577</v>
+        <v>51697.9999748144</v>
       </c>
       <c r="B257" t="n">
-        <v>6333.644871412651</v>
+        <v>7604.41705569901</v>
       </c>
       <c r="C257" t="n">
-        <v>2602.662485126461</v>
+        <v>2186.378629895595</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>51577</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>53884.37860470999</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>51697</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>51591.52047528767</v>
+        <v>51698</v>
       </c>
       <c r="B258" t="n">
-        <v>10386.03364038973</v>
+        <v>13244.04560644157</v>
       </c>
       <c r="C258" t="n">
-        <v>3444.94307444368</v>
+        <v>1253.13956098957</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="n">
-        <v>51591</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>52951.13956098956</v>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>51698</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>51606.99999999999</v>
+        <v>51699.00000000001</v>
       </c>
       <c r="B259" t="n">
-        <v>10394.95244401122</v>
+        <v>8417.86957078581</v>
       </c>
       <c r="C259" t="n">
-        <v>2247.894433727507</v>
+        <v>2119.936475248867</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>51606</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>53818.93647524888</v>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>51699</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>51607</v>
+        <v>51715.03670010348</v>
       </c>
       <c r="B260" t="n">
-        <v>10097.88598663628</v>
+        <v>7303.642344142248</v>
       </c>
       <c r="C260" t="n">
-        <v>2575.862294567002</v>
+        <v>2202.968728444823</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="n">
-        <v>51607</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>53918.00542854828</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>51715</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>51636.99986125867</v>
+        <v>51728.9999999887</v>
       </c>
       <c r="B261" t="n">
-        <v>8989.567110167352</v>
+        <v>10307.17498628802</v>
       </c>
       <c r="C261" t="n">
-        <v>2263.96563027715</v>
+        <v>1783.731604454192</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>51636</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>53512.7316044429</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>51728</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>51637</v>
+        <v>51729</v>
       </c>
       <c r="B262" t="n">
-        <v>10232.17735575574</v>
+        <v>8386.667339931269</v>
       </c>
       <c r="C262" t="n">
-        <v>3202.722077590188</v>
+        <v>1694.371215488655</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>51637</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>53423.37121548865</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>51729</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>51638</v>
+        <v>51730</v>
       </c>
       <c r="B263" t="n">
-        <v>14363.63060904171</v>
+        <v>9603.091550642604</v>
       </c>
       <c r="C263" t="n">
-        <v>2539.121671122115</v>
+        <v>2255.459081668909</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>51638</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>53985.4590816689</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>51730</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>51664.19557300543</v>
+        <v>51759.99999999757</v>
       </c>
       <c r="B264" t="n">
-        <v>25533.10120873276</v>
+        <v>5716.476746838031</v>
       </c>
       <c r="C264" t="n">
-        <v>1393.375761225942</v>
+        <v>2224.700584390396</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>51664</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>53984.70058438796</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>51759</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>51667.99999999996</v>
+        <v>51760</v>
       </c>
       <c r="B265" t="n">
-        <v>8215.160664647279</v>
+        <v>5217.781460159387</v>
       </c>
       <c r="C265" t="n">
-        <v>2204.619245117839</v>
+        <v>1740.323955440265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="n">
-        <v>51667</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>53500.32395544025</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>51760</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>51668</v>
+        <v>51774.36679331094</v>
       </c>
       <c r="B266" t="n">
-        <v>8595.854713828858</v>
+        <v>4959.499203369423</v>
       </c>
       <c r="C266" t="n">
-        <v>2269.847351243972</v>
+        <v>1841.758754749442</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>51668</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>53616.12554806037</v>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>51774</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>51676.488755925</v>
+        <v>51789.99895006714</v>
       </c>
       <c r="B267" t="n">
-        <v>8174.799290456387</v>
+        <v>4547.39892520634</v>
       </c>
       <c r="C267" t="n">
-        <v>2147.048345614171</v>
+        <v>2201.102499032465</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>51676</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>53991.10144909959</v>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>51789</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>51697.9999748144</v>
+        <v>51790</v>
       </c>
       <c r="B268" t="n">
-        <v>7604.41705569901</v>
+        <v>13022.07440761554</v>
       </c>
       <c r="C268" t="n">
-        <v>2186.378629895595</v>
+        <v>1698.184887712245</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>51697</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>53488.18488771225</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>51790</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>51698</v>
+        <v>51791</v>
       </c>
       <c r="B269" t="n">
-        <v>8127.741603443928</v>
+        <v>5109.841622116415</v>
       </c>
       <c r="C269" t="n">
-        <v>3542.415954714727</v>
+        <v>2060.588057001461</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="n">
-        <v>51698</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>53851.58805700146</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>51791</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>51699.00000000001</v>
+        <v>51796.07865963881</v>
       </c>
       <c r="B270" t="n">
-        <v>8417.86957078581</v>
+        <v>4524.206168178356</v>
       </c>
       <c r="C270" t="n">
-        <v>2119.936475248867</v>
+        <v>2213.805365949047</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>51699</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>54009.88402558785</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>51796</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>51702.6842051933</v>
+        <v>51805.77432087082</v>
       </c>
       <c r="B271" t="n">
-        <v>8097.109700921948</v>
+        <v>12780.48604355373</v>
       </c>
       <c r="C271" t="n">
-        <v>3559.990749476544</v>
+        <v>1689.098216706155</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="n">
-        <v>51702</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>53494.87253757696</v>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>51805</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>51715.03670010348</v>
+        <v>51820.99999998031</v>
       </c>
       <c r="B272" t="n">
-        <v>7303.642344142248</v>
+        <v>8632.435231159749</v>
       </c>
       <c r="C272" t="n">
-        <v>2202.968728444823</v>
+        <v>1928.327733718712</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>51715</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>53749.32773369901</v>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>51820</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>51728.9999999887</v>
+        <v>51821.00000000001</v>
       </c>
       <c r="B273" t="n">
-        <v>10307.17498628802</v>
+        <v>13012.64004206009</v>
       </c>
       <c r="C273" t="n">
-        <v>1783.731604454192</v>
+        <v>1681.038002288425</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>51728</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>53502.03800228843</v>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>51821</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>51729</v>
+        <v>51836.25539311618</v>
       </c>
       <c r="B274" t="n">
-        <v>8386.667339931269</v>
+        <v>8101.327848764682</v>
       </c>
       <c r="C274" t="n">
-        <v>1694.371215488655</v>
+        <v>1795.13517768021</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>51729</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>53631.39057079639</v>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>51836</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>51730</v>
+        <v>51848.44907215003</v>
       </c>
       <c r="B275" t="n">
-        <v>9603.091550642604</v>
+        <v>17947.89344728675</v>
       </c>
       <c r="C275" t="n">
-        <v>2255.459081668909</v>
+        <v>2180.610321908989</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="n">
-        <v>51730</v>
+          <t>VVEE</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>54029.05939405902</v>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>51848</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>51747.04912506295</v>
+        <v>51850.99972479569</v>
       </c>
       <c r="B276" t="n">
-        <v>11962.03353547625</v>
+        <v>3972.360334575977</v>
       </c>
       <c r="C276" t="n">
-        <v>2576.640101658458</v>
+        <v>2141.310410513387</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>51747</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>53992.31013530906</v>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>51850</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>51759.99999999757</v>
+        <v>51852.0000008671</v>
       </c>
       <c r="B277" t="n">
-        <v>5716.476746838031</v>
+        <v>8172.299834228948</v>
       </c>
       <c r="C277" t="n">
-        <v>2224.700584390396</v>
+        <v>1793.203126330457</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>51759</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>53645.20312719756</v>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>51852</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>51760</v>
+        <v>51866.79759349514</v>
       </c>
       <c r="B278" t="n">
-        <v>5217.781460159387</v>
+        <v>3803.622531928977</v>
       </c>
       <c r="C278" t="n">
-        <v>1740.323955440265</v>
+        <v>2143.183341271359</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>51760</v>
+          <t>VEVE</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>54009.98093476649</v>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>51866</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>51761.83360240843</v>
+        <v>51881.9999991588</v>
       </c>
       <c r="B279" t="n">
-        <v>11955.48384887483</v>
+        <v>8184.561488697273</v>
       </c>
       <c r="C279" t="n">
-        <v>2647.033489853027</v>
+        <v>1954.711375936169</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="n">
-        <v>51761</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>53836.71137509496</v>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>51881</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>51774.36679331094</v>
+        <v>51882</v>
       </c>
       <c r="B280" t="n">
-        <v>4959.499203369423</v>
+        <v>14763.4838794869</v>
       </c>
       <c r="C280" t="n">
-        <v>1841.758754749442</v>
+        <v>1794.289251173203</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>51774</v>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>53676.28925117319</v>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>51882</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>51789.99895006714</v>
+        <v>51883.14413706891</v>
       </c>
       <c r="B281" t="n">
-        <v>4547.39892520634</v>
+        <v>9211.898891252426</v>
       </c>
       <c r="C281" t="n">
-        <v>2201.102499032465</v>
+        <v>1281.555916145765</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="n">
-        <v>51789</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>53164.70005321468</v>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>51883</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>51790</v>
+        <v>51911</v>
       </c>
       <c r="B282" t="n">
-        <v>11271.01691984918</v>
+        <v>10690.08752622132</v>
       </c>
       <c r="C282" t="n">
-        <v>2350.869783310839</v>
+        <v>1346.469347817178</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>51790</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>53257.46934781718</v>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>51911</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>51791</v>
+        <v>51912.99999995486</v>
       </c>
       <c r="B283" t="n">
-        <v>5109.841622116415</v>
+        <v>8170.110263856261</v>
       </c>
       <c r="C283" t="n">
-        <v>2060.588057001461</v>
+        <v>2107.502407154942</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="n">
-        <v>51791</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>54020.50240710979</v>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>51912</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>51796.07865963881</v>
+        <v>51940.99999980901</v>
       </c>
       <c r="B284" t="n">
-        <v>4524.206168178356</v>
+        <v>7063.264596286135</v>
       </c>
       <c r="C284" t="n">
-        <v>2213.805365949047</v>
+        <v>1678.720672300867</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>51796</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>53619.72067210987</v>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>51940</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>51797.12499409592</v>
+        <v>51942</v>
       </c>
       <c r="B285" t="n">
-        <v>5465.910084444233</v>
+        <v>12732.04175631553</v>
       </c>
       <c r="C285" t="n">
-        <v>3634.09350280746</v>
+        <v>1873.953440938902</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="n">
-        <v>51797</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>53815.9534409389</v>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>51942</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>51805.77432087082</v>
+        <v>51971.99999999859</v>
       </c>
       <c r="B286" t="n">
-        <v>12780.48604355373</v>
+        <v>4245.040192377093</v>
       </c>
       <c r="C286" t="n">
-        <v>1689.098216706155</v>
+        <v>1562.305014415081</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>51805</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>53534.30501441366</v>
+      </c>
+      <c r="F286" s="3" t="n">
+        <v>51971</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>51820.99999998031</v>
+        <v>51972</v>
       </c>
       <c r="B287" t="n">
-        <v>8632.435231159749</v>
+        <v>15583.95479874534</v>
       </c>
       <c r="C287" t="n">
-        <v>1928.327733718712</v>
+        <v>1858.996098587452</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="n">
-        <v>51820</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>53830.99609858744</v>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>51972</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>51821</v>
+        <v>52001.99999999181</v>
       </c>
       <c r="B288" t="n">
-        <v>5555.719344187441</v>
+        <v>3474.088463728765</v>
       </c>
       <c r="C288" t="n">
-        <v>2359.423833415058</v>
+        <v>1582.239134339926</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="n">
-        <v>51821</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>53584.23913433174</v>
+      </c>
+      <c r="F288" s="3" t="n">
+        <v>52001</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>51836.25539311618</v>
+        <v>52030.35334999394</v>
       </c>
       <c r="B289" t="n">
-        <v>8101.327848764682</v>
+        <v>3281.63139456409</v>
       </c>
       <c r="C289" t="n">
-        <v>1795.13517768021</v>
+        <v>1616.374875243894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
           <t>VVE</t>
         </is>
       </c>
-      <c r="E289" s="3" t="n">
-        <v>51836</v>
+      <c r="E289" s="2" t="n">
+        <v>53646.72822523782</v>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>52030</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>51848.44907215003</v>
+        <v>52033</v>
       </c>
       <c r="B290" t="n">
-        <v>17947.89344728675</v>
+        <v>16553.08407743271</v>
       </c>
       <c r="C290" t="n">
-        <v>2180.610321908989</v>
+        <v>1636.415842097045</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>51848</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>53669.41584209703</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>52033</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>51850.99972479569</v>
+        <v>52062.99999999998</v>
       </c>
       <c r="B291" t="n">
-        <v>3972.360334575977</v>
+        <v>2662.762400757572</v>
       </c>
       <c r="C291" t="n">
-        <v>2141.310410513387</v>
+        <v>1453.27603483726</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E291" s="3" t="n">
-        <v>51850</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>53516.27603483723</v>
+      </c>
+      <c r="F291" s="3" t="n">
+        <v>52062</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>51851</v>
+        <v>52063</v>
       </c>
       <c r="B292" t="n">
-        <v>6842.750690750559</v>
+        <v>7952.45649642175</v>
       </c>
       <c r="C292" t="n">
-        <v>2552.566152004241</v>
+        <v>1921.954870558589</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
           <t>VEM</t>
         </is>
       </c>
-      <c r="E292" s="3" t="n">
-        <v>51851</v>
+      <c r="E292" s="2" t="n">
+        <v>53984.95487055859</v>
+      </c>
+      <c r="F292" s="3" t="n">
+        <v>52063</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>51852</v>
+        <v>52069.73104144946</v>
       </c>
       <c r="B293" t="n">
-        <v>7698.062642626388</v>
+        <v>7943.943713332195</v>
       </c>
       <c r="C293" t="n">
-        <v>3579.218496903391</v>
+        <v>1915.045941437424</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E293" s="3" t="n">
-        <v>51852</v>
+          <t>VEM</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>53984.77698288688</v>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>52069</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>51866.79759349514</v>
+        <v>52079.21925268078</v>
       </c>
       <c r="B294" t="n">
-        <v>3803.622531928977</v>
+        <v>2982.346290770933</v>
       </c>
       <c r="C294" t="n">
-        <v>2143.183341271359</v>
+        <v>1521.374395463072</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>51866</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>53600.59364814385</v>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>52079</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
-        <v>51881.9999991588</v>
+        <v>52094</v>
       </c>
       <c r="B295" t="n">
-        <v>8184.561488697273</v>
+        <v>7060.364129485844</v>
       </c>
       <c r="C295" t="n">
-        <v>1954.711375936169</v>
+        <v>1690.777989434964</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>51881</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>53784.77798943495</v>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>52094</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
-        <v>51882</v>
+        <v>52095.00000000001</v>
       </c>
       <c r="B296" t="n">
-        <v>6185.420396398909</v>
+        <v>2754.266213292111</v>
       </c>
       <c r="C296" t="n">
-        <v>2528.248761836068</v>
+        <v>1394.445712241474</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="n">
-        <v>51882</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>53489.44571224148</v>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>52095</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
-        <v>51883.00000000004</v>
+        <v>52125</v>
       </c>
       <c r="B297" t="n">
-        <v>6801.565396357986</v>
+        <v>4251.892339816433</v>
       </c>
       <c r="C297" t="n">
-        <v>2696.224711731692</v>
+        <v>1722.473549711632</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E297" s="3" t="n">
-        <v>51883</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>53847.47354971162</v>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>52125</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>51899.71685866588</v>
+        <v>52147.38634700987</v>
       </c>
       <c r="B298" t="n">
-        <v>5989.488543142304</v>
+        <v>2876.125446409285</v>
       </c>
       <c r="C298" t="n">
-        <v>2520.376381939104</v>
+        <v>1420.691732440396</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E298" s="3" t="n">
-        <v>51899</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>53568.07807945026</v>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>52147</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>51911</v>
+        <v>52148.851923403</v>
       </c>
       <c r="B299" t="n">
-        <v>10690.08752622132</v>
+        <v>3797.821856234557</v>
       </c>
       <c r="C299" t="n">
-        <v>1346.469347817178</v>
+        <v>1728.052982365612</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="E299" s="3" t="n">
-        <v>51911</v>
+      <c r="E299" s="2" t="n">
+        <v>53876.9049057686</v>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>52148</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
-        <v>51912.99999995486</v>
+        <v>52156.00000000002</v>
       </c>
       <c r="B300" t="n">
-        <v>8170.110263856261</v>
+        <v>2984.841193517434</v>
       </c>
       <c r="C300" t="n">
-        <v>2107.502407154942</v>
+        <v>1356.671507069931</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E300" s="3" t="n">
-        <v>51912</v>
+          <t>VVE</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>53512.67150706995</v>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>52156</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
-        <v>51913</v>
+        <v>52185.99999999988</v>
       </c>
       <c r="B301" t="n">
-        <v>9002.132336029576</v>
+        <v>13974.2104387975</v>
       </c>
       <c r="C301" t="n">
-        <v>2404.091572796985</v>
+        <v>1708.923615653014</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E301" s="3" t="n">
-        <v>51913</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>53894.92361565289</v>
+      </c>
+      <c r="F301" s="3" t="n">
+        <v>52185</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>51940.99999980901</v>
+        <v>52186</v>
       </c>
       <c r="B302" t="n">
-        <v>7063.264596286135</v>
+        <v>4871.403299368685</v>
       </c>
       <c r="C302" t="n">
-        <v>1678.720672300867</v>
+        <v>1744.167896890056</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E302" s="3" t="n">
-        <v>51940</v>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>53930.16789689005</v>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>52186</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>51941</v>
+        <v>52201.13293847386</v>
       </c>
       <c r="B303" t="n">
-        <v>5373.235704849303</v>
+        <v>13765.57767700441</v>
       </c>
       <c r="C303" t="n">
-        <v>2473.511929624603</v>
+        <v>1733.507453040056</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E303" s="3" t="n">
-        <v>51941</v>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>53934.6403915139</v>
+      </c>
+      <c r="F303" s="3" t="n">
+        <v>52201</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
-        <v>51942</v>
+        <v>52216</v>
       </c>
       <c r="B304" t="n">
-        <v>12732.04175631553</v>
+        <v>20564.94978652876</v>
       </c>
       <c r="C304" t="n">
-        <v>1873.953440938902</v>
+        <v>1226.661409043693</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>51942</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="n">
-        <v>51965.13376976662</v>
-      </c>
-      <c r="B305" t="n">
-        <v>8985.930435077384</v>
-      </c>
-      <c r="C305" t="n">
-        <v>2154.350767216609</v>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E305" s="3" t="n">
-        <v>51965</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="n">
-        <v>51971.99999999859</v>
-      </c>
-      <c r="B306" t="n">
-        <v>4245.040192377093</v>
-      </c>
-      <c r="C306" t="n">
-        <v>1562.305014415081</v>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E306" s="3" t="n">
-        <v>51971</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
-        <v>51972</v>
-      </c>
-      <c r="B307" t="n">
-        <v>7739.445312199165</v>
-      </c>
-      <c r="C307" t="n">
-        <v>2168.45997946273</v>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
           <t>ME</t>
         </is>
       </c>
-      <c r="E307" s="3" t="n">
-        <v>51972</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
-        <v>51989.17544566212</v>
-      </c>
-      <c r="B308" t="n">
-        <v>6602.746473415586</v>
-      </c>
-      <c r="C308" t="n">
-        <v>2367.993808065424</v>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E308" s="3" t="n">
-        <v>51989</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
-        <v>51994.38625412218</v>
-      </c>
-      <c r="B309" t="n">
-        <v>4992.466793653097</v>
-      </c>
-      <c r="C309" t="n">
-        <v>2424.783795268588</v>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E309" s="3" t="n">
-        <v>51994</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
-        <v>52001.99999999181</v>
-      </c>
-      <c r="B310" t="n">
-        <v>3474.088463728765</v>
-      </c>
-      <c r="C310" t="n">
-        <v>1582.239134339926</v>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E310" s="3" t="n">
-        <v>52001</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
-        <v>52002</v>
-      </c>
-      <c r="B311" t="n">
-        <v>3289.571583665798</v>
-      </c>
-      <c r="C311" t="n">
-        <v>2202.135218271899</v>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E311" s="3" t="n">
-        <v>52002</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
-        <v>52003.00000000004</v>
-      </c>
-      <c r="B312" t="n">
-        <v>5040.882868877396</v>
-      </c>
-      <c r="C312" t="n">
-        <v>2425.66271161978</v>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>52003</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
-        <v>52025.43051316826</v>
-      </c>
-      <c r="B313" t="n">
-        <v>2783.301557998426</v>
-      </c>
-      <c r="C313" t="n">
-        <v>2184.564327743805</v>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E313" s="3" t="n">
-        <v>52025</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
-        <v>52026.86578701993</v>
-      </c>
-      <c r="B314" t="n">
-        <v>5318.997219292112</v>
-      </c>
-      <c r="C314" t="n">
-        <v>2613.025891260736</v>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E314" s="3" t="n">
-        <v>52026</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
-        <v>52030.35334999394</v>
-      </c>
-      <c r="B315" t="n">
-        <v>3281.63139456409</v>
-      </c>
-      <c r="C315" t="n">
-        <v>1616.374875243894</v>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E315" s="3" t="n">
-        <v>52030</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
-        <v>52032.99999999916</v>
-      </c>
-      <c r="B316" t="n">
-        <v>3847.069025827001</v>
-      </c>
-      <c r="C316" t="n">
-        <v>2911.720235282479</v>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E316" s="3" t="n">
-        <v>52032</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>52033</v>
-      </c>
-      <c r="B317" t="n">
-        <v>2825.003311116907</v>
-      </c>
-      <c r="C317" t="n">
-        <v>2176.979348775942</v>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E317" s="3" t="n">
-        <v>52033</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="n">
-        <v>52062.99999999998</v>
-      </c>
-      <c r="B318" t="n">
-        <v>2662.762400757572</v>
-      </c>
-      <c r="C318" t="n">
-        <v>1453.27603483726</v>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E318" s="3" t="n">
-        <v>52062</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="n">
-        <v>52063</v>
-      </c>
-      <c r="B319" t="n">
-        <v>2455.416252575186</v>
-      </c>
-      <c r="C319" t="n">
-        <v>2869.264675350634</v>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E319" s="3" t="n">
-        <v>52063</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="n">
-        <v>52064</v>
-      </c>
-      <c r="B320" t="n">
-        <v>3794.561976336801</v>
-      </c>
-      <c r="C320" t="n">
-        <v>2133.425325952671</v>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E320" s="3" t="n">
-        <v>52064</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="n">
-        <v>52067.29188878855</v>
-      </c>
-      <c r="B321" t="n">
-        <v>2416.243506723013</v>
-      </c>
-      <c r="C321" t="n">
-        <v>2928.517051613646</v>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>MEE</t>
-        </is>
-      </c>
-      <c r="E321" s="3" t="n">
-        <v>52067</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="n">
-        <v>52069.73104144946</v>
-      </c>
-      <c r="B322" t="n">
-        <v>7943.943713332195</v>
-      </c>
-      <c r="C322" t="n">
-        <v>1915.045941437424</v>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>VEM</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>52069</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="n">
-        <v>52079.21925268078</v>
-      </c>
-      <c r="B323" t="n">
-        <v>2982.346290770933</v>
-      </c>
-      <c r="C323" t="n">
-        <v>1521.374395463072</v>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="n">
-        <v>52079</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="n">
-        <v>52091.61032021913</v>
-      </c>
-      <c r="B324" t="n">
-        <v>5327.966029084346</v>
-      </c>
-      <c r="C324" t="n">
-        <v>2263.091849961549</v>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>VVEE</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>52091</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>52093.99686291981</v>
-      </c>
-      <c r="B325" t="n">
-        <v>11275.54349692673</v>
-      </c>
-      <c r="C325" t="n">
-        <v>2499.331627818516</v>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n">
-        <v>52093</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>52094</v>
-      </c>
-      <c r="B326" t="n">
-        <v>7060.364129485844</v>
-      </c>
-      <c r="C326" t="n">
-        <v>1690.777989434964</v>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>52094</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="n">
-        <v>52095.00000000001</v>
-      </c>
-      <c r="B327" t="n">
-        <v>2754.266213292111</v>
-      </c>
-      <c r="C327" t="n">
-        <v>1394.445712241474</v>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="n">
-        <v>52095</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="n">
-        <v>52115.47522402013</v>
-      </c>
-      <c r="B328" t="n">
-        <v>8275.473622972708</v>
-      </c>
-      <c r="C328" t="n">
-        <v>2100.343262655757</v>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="n">
-        <v>52115</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="n">
-        <v>52124.99999474423</v>
-      </c>
-      <c r="B329" t="n">
-        <v>9753.985414825853</v>
-      </c>
-      <c r="C329" t="n">
-        <v>2350.485880990207</v>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="n">
-        <v>52124</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="n">
-        <v>52125</v>
-      </c>
-      <c r="B330" t="n">
-        <v>4251.892339816433</v>
-      </c>
-      <c r="C330" t="n">
-        <v>1722.473549711632</v>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E330" s="3" t="n">
-        <v>52125</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>52147.38634700987</v>
-      </c>
-      <c r="B331" t="n">
-        <v>2876.125446409285</v>
-      </c>
-      <c r="C331" t="n">
-        <v>1420.691732440396</v>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E331" s="3" t="n">
-        <v>52147</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
-        <v>52148.851923403</v>
-      </c>
-      <c r="B332" t="n">
-        <v>3797.821856234557</v>
-      </c>
-      <c r="C332" t="n">
-        <v>1728.052982365612</v>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="n">
-        <v>52148</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
-        <v>52154.99832615253</v>
-      </c>
-      <c r="B333" t="n">
-        <v>8607.761795308599</v>
-      </c>
-      <c r="C333" t="n">
-        <v>2345.593773202741</v>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E333" s="3" t="n">
-        <v>52154</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
-        <v>52156.00000000002</v>
-      </c>
-      <c r="B334" t="n">
-        <v>2984.841193517434</v>
-      </c>
-      <c r="C334" t="n">
-        <v>1356.671507069931</v>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E334" s="3" t="n">
-        <v>52156</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
-        <v>52185.99999999993</v>
-      </c>
-      <c r="B335" t="n">
-        <v>6608.496771560163</v>
-      </c>
-      <c r="C335" t="n">
-        <v>2507.344710872978</v>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E335" s="3" t="n">
-        <v>52185</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="n">
-        <v>52186</v>
-      </c>
-      <c r="B336" t="n">
-        <v>4871.403299368685</v>
-      </c>
-      <c r="C336" t="n">
-        <v>1744.167896890056</v>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>52186</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="n">
-        <v>52201.13293847386</v>
-      </c>
-      <c r="B337" t="n">
-        <v>13765.57767700441</v>
-      </c>
-      <c r="C337" t="n">
-        <v>1733.507453040056</v>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="E337" s="3" t="n">
-        <v>52201</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="n">
-        <v>52213.06879616943</v>
-      </c>
-      <c r="B338" t="n">
-        <v>2398.934475802898</v>
-      </c>
-      <c r="C338" t="n">
-        <v>2120.004128953637</v>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>VVE</t>
-        </is>
-      </c>
-      <c r="E338" s="3" t="n">
-        <v>52213</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="n">
-        <v>52215.99999999992</v>
-      </c>
-      <c r="B339" t="n">
-        <v>4938.016100868139</v>
-      </c>
-      <c r="C339" t="n">
-        <v>2561.154957769438</v>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>VEVE</t>
-        </is>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>52215</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="n">
-        <v>52216</v>
-      </c>
-      <c r="B340" t="n">
-        <v>20564.94978652876</v>
-      </c>
-      <c r="C340" t="n">
-        <v>1226.661409043693</v>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E340" s="3" t="n">
+      <c r="E304" s="2" t="n">
+        <v>53442.66140904369</v>
+      </c>
+      <c r="F304" s="3" t="n">
         <v>52216</v>
       </c>
     </row>
